--- a/Financial Analysis/AMD.xlsx
+++ b/Financial Analysis/AMD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77E5C72-DFFD-4E78-9AD1-8500DCEA0DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90592336-7628-436E-A184-C7AEEF03C703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9151AF15-9D45-44A9-8CA3-26C538A98864}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9151AF15-9D45-44A9-8CA3-26C538A98864}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="70">
   <si>
     <t>AMD</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>Restructuring</t>
+  </si>
+  <si>
+    <t>Q225 8K</t>
   </si>
   <si>
     <t>Slightly undervalued</t>
@@ -332,16 +335,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
+      <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -356,7 +359,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11879580" y="7620"/>
+          <a:off x="13106400" y="0"/>
           <a:ext cx="0" cy="6499860"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -756,17 +759,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>93.62</v>
+        <v>150.74</v>
       </c>
       <c r="E3" s="2">
-        <v>45751</v>
+        <v>45918</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45751</v>
+        <v>45918</v>
       </c>
       <c r="G3" s="2">
-        <v>45783</v>
+        <v>45967</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -774,11 +777,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>1620.5</f>
-        <v>1620.5</v>
+        <f>1623</f>
+        <v>1623</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -787,7 +790,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>151711.21000000002</v>
+        <v>244651.02000000002</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -795,11 +798,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>3787+1345+149</f>
-        <v>5281</v>
+        <f>4442+1425</f>
+        <v>5867</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -807,11 +810,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>1721</f>
-        <v>1721</v>
+        <f>3218</f>
+        <v>3218</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -820,7 +823,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>3560</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -829,7 +832,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>148151.21000000002</v>
+        <v>242002.02000000002</v>
       </c>
     </row>
   </sheetData>
@@ -1015,20 +1018,17 @@
         <v>7658</v>
       </c>
       <c r="S3" s="8">
-        <f>O3*1.25</f>
-        <v>6841.25</v>
+        <v>7438</v>
       </c>
       <c r="T3" s="8">
-        <f>P3*1.23</f>
-        <v>7177.05</v>
+        <v>7685</v>
       </c>
       <c r="U3" s="8">
-        <f>Q3*1.15</f>
-        <v>7841.8499999999995</v>
+        <v>8700</v>
       </c>
       <c r="V3" s="8">
-        <f>R3*1.15</f>
-        <v>8806.6999999999989</v>
+        <f>R3*1.25</f>
+        <v>9572.5</v>
       </c>
       <c r="Y3" s="8">
         <v>6731</v>
@@ -1053,47 +1053,47 @@
       </c>
       <c r="AE3" s="8">
         <f>SUM(S3:V3)</f>
-        <v>30666.85</v>
+        <v>33395.5</v>
       </c>
       <c r="AF3" s="8">
-        <f>AE3*1.16</f>
-        <v>35573.545999999995</v>
+        <f>AE3*1.2</f>
+        <v>40074.6</v>
       </c>
       <c r="AG3" s="8">
-        <f>AF3*1.12</f>
-        <v>39842.371520000001</v>
+        <f>AF3*1.15</f>
+        <v>46085.789999999994</v>
       </c>
       <c r="AH3" s="8">
-        <f>AG3*1.09</f>
-        <v>43428.184956800003</v>
+        <f>AG3*1.1</f>
+        <v>50694.368999999999</v>
       </c>
       <c r="AI3" s="8">
-        <f>AH3*1.06</f>
-        <v>46033.876054208005</v>
+        <f>AH3*1.09</f>
+        <v>55256.862209999999</v>
       </c>
       <c r="AJ3" s="8">
-        <f>AI3*1.04</f>
-        <v>47875.23109637633</v>
+        <f>AI3*1.07</f>
+        <v>59124.842564700004</v>
       </c>
       <c r="AK3" s="8">
-        <f>AJ3*1.03</f>
-        <v>49311.488029267624</v>
+        <f>AJ3*1.05</f>
+        <v>62081.084692935008</v>
       </c>
       <c r="AL3" s="8">
-        <f t="shared" ref="AL3:AO3" si="0">AK3*1.03</f>
-        <v>50790.832670145654</v>
+        <f t="shared" ref="AL3:AO3" si="0">AK3*1.05</f>
+        <v>65185.138927581764</v>
       </c>
       <c r="AM3" s="8">
         <f t="shared" si="0"/>
-        <v>52314.557650250026</v>
+        <v>68444.39587396085</v>
       </c>
       <c r="AN3" s="8">
         <f t="shared" si="0"/>
-        <v>53883.994379757525</v>
+        <v>71866.615667658902</v>
       </c>
       <c r="AO3" s="8">
         <f t="shared" si="0"/>
-        <v>55500.51421115025</v>
+        <v>75459.946451041847</v>
       </c>
     </row>
     <row r="4" spans="2:41" x14ac:dyDescent="0.3">
@@ -1149,8 +1149,12 @@
       <c r="R4" s="5">
         <v>3524</v>
       </c>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
+      <c r="S4" s="5">
+        <v>3451</v>
+      </c>
+      <c r="T4" s="5">
+        <v>4366</v>
+      </c>
       <c r="U4" s="5"/>
       <c r="V4" s="5"/>
       <c r="Y4" s="5">
@@ -1239,8 +1243,12 @@
       <c r="R5" s="5">
         <v>252</v>
       </c>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
+      <c r="S5" s="5">
+        <v>251</v>
+      </c>
+      <c r="T5" s="5">
+        <v>260</v>
+      </c>
       <c r="U5" s="5"/>
       <c r="V5" s="5"/>
       <c r="Y5" s="5"/>
@@ -1275,7 +1283,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="5">
-        <f t="shared" ref="C6:R6" si="1">SUM(C4:C5)</f>
+        <f t="shared" ref="C6:T6" si="1">SUM(C4:C5)</f>
         <v>1858</v>
       </c>
       <c r="D6" s="5">
@@ -1339,20 +1347,20 @@
         <v>3776</v>
       </c>
       <c r="S6" s="5">
-        <f>S3-S7</f>
-        <v>3283.7999999999997</v>
+        <f t="shared" si="1"/>
+        <v>3702</v>
       </c>
       <c r="T6" s="5">
-        <f t="shared" ref="T6:V6" si="2">T3-T7</f>
-        <v>3444.9839999999999</v>
+        <f t="shared" si="1"/>
+        <v>4626</v>
       </c>
       <c r="U6" s="5">
-        <f t="shared" si="2"/>
-        <v>3685.6695</v>
+        <f t="shared" ref="U6:V6" si="2">U3-U7</f>
+        <v>4089</v>
       </c>
       <c r="V6" s="5">
         <f t="shared" si="2"/>
-        <v>4051.0819999999994</v>
+        <v>4403.3499999999995</v>
       </c>
       <c r="Y6" s="5">
         <f t="shared" ref="Y6:AD6" si="3">SUM(Y4:Y5)</f>
@@ -1380,47 +1388,47 @@
       </c>
       <c r="AE6" s="5">
         <f>SUM(S6:V6)</f>
-        <v>14465.535499999998</v>
+        <v>16820.349999999999</v>
       </c>
       <c r="AF6" s="5">
         <f>AF3-AF7</f>
-        <v>16008.095699999994</v>
+        <v>18033.569999999996</v>
       </c>
       <c r="AG6" s="5">
         <f t="shared" ref="AG6:AO6" si="4">AG3-AG7</f>
-        <v>17132.219753600002</v>
+        <v>19816.8897</v>
       </c>
       <c r="AH6" s="5">
         <f t="shared" si="4"/>
-        <v>17805.555832288002</v>
+        <v>20784.691290000002</v>
       </c>
       <c r="AI6" s="5">
         <f t="shared" si="4"/>
-        <v>18413.550421683201</v>
+        <v>22102.744884</v>
       </c>
       <c r="AJ6" s="5">
         <f t="shared" si="4"/>
-        <v>18671.340127586769</v>
+        <v>23058.688600232999</v>
       </c>
       <c r="AK6" s="5">
         <f t="shared" si="4"/>
-        <v>18738.365451121699</v>
+        <v>23590.812183315305</v>
       </c>
       <c r="AL6" s="5">
         <f t="shared" si="4"/>
-        <v>18792.608087953893</v>
+        <v>24770.35279248107</v>
       </c>
       <c r="AM6" s="5">
         <f t="shared" si="4"/>
-        <v>18833.240754090009</v>
+        <v>26008.870432105126</v>
       </c>
       <c r="AN6" s="5">
         <f t="shared" si="4"/>
-        <v>18859.398032915131</v>
+        <v>27309.313953710385</v>
       </c>
       <c r="AO6" s="5">
         <f t="shared" si="4"/>
-        <v>19425.179973902588</v>
+        <v>28674.779651395904</v>
       </c>
     </row>
     <row r="7" spans="2:41" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1428,7 +1436,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="8">
-        <f t="shared" ref="C7:R7" si="5">C3-C6</f>
+        <f t="shared" ref="C7:T7" si="5">C3-C6</f>
         <v>1587</v>
       </c>
       <c r="D7" s="8">
@@ -1492,88 +1500,88 @@
         <v>3882</v>
       </c>
       <c r="S7" s="8">
-        <f>S3*0.52</f>
-        <v>3557.4500000000003</v>
+        <f t="shared" si="5"/>
+        <v>3736</v>
       </c>
       <c r="T7" s="8">
-        <f t="shared" ref="T7" si="6">T3*0.52</f>
-        <v>3732.0660000000003</v>
+        <f t="shared" si="5"/>
+        <v>3059</v>
       </c>
       <c r="U7" s="8">
         <f>U3*0.53</f>
-        <v>4156.1804999999995</v>
+        <v>4611</v>
       </c>
       <c r="V7" s="8">
         <f>V3*0.54</f>
-        <v>4755.6179999999995</v>
+        <v>5169.1500000000005</v>
       </c>
       <c r="Y7" s="8">
-        <f t="shared" ref="Y7:AE7" si="7">Y3-Y6</f>
+        <f t="shared" ref="Y7:AE7" si="6">Y3-Y6</f>
         <v>2868</v>
       </c>
       <c r="Z7" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>4347</v>
       </c>
       <c r="AA7" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>7929</v>
       </c>
       <c r="AB7" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>10603</v>
       </c>
       <c r="AC7" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>10460</v>
       </c>
       <c r="AD7" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>12725</v>
       </c>
       <c r="AE7" s="8">
-        <f t="shared" si="7"/>
-        <v>16201.3145</v>
+        <f t="shared" si="6"/>
+        <v>16575.150000000001</v>
       </c>
       <c r="AF7" s="8">
         <f>AF3*0.55</f>
-        <v>19565.4503</v>
+        <v>22041.030000000002</v>
       </c>
       <c r="AG7" s="8">
         <f>AG3*0.57</f>
-        <v>22710.151766399998</v>
+        <v>26268.900299999994</v>
       </c>
       <c r="AH7" s="8">
         <f>AH3*0.59</f>
-        <v>25622.629124512001</v>
+        <v>29909.677709999996</v>
       </c>
       <c r="AI7" s="8">
         <f>AI3*0.6</f>
-        <v>27620.325632524804</v>
+        <v>33154.117326</v>
       </c>
       <c r="AJ7" s="8">
         <f>AJ3*0.61</f>
-        <v>29203.890968789561</v>
+        <v>36066.153964467005</v>
       </c>
       <c r="AK7" s="8">
         <f>AK3*0.62</f>
-        <v>30573.122578145925</v>
+        <v>38490.272509619703</v>
       </c>
       <c r="AL7" s="8">
-        <f>AL3*0.63</f>
-        <v>31998.22458219176</v>
+        <f t="shared" ref="AL7:AO7" si="7">AL3*0.62</f>
+        <v>40414.786135100694</v>
       </c>
       <c r="AM7" s="8">
-        <f>AM3*0.64</f>
-        <v>33481.316896160017</v>
+        <f t="shared" si="7"/>
+        <v>42435.525441855723</v>
       </c>
       <c r="AN7" s="8">
-        <f>AN3*0.65</f>
-        <v>35024.596346842394</v>
+        <f t="shared" si="7"/>
+        <v>44557.301713948516</v>
       </c>
       <c r="AO7" s="8">
-        <f t="shared" ref="AO7" si="8">AO3*0.65</f>
-        <v>36075.334237247662</v>
+        <f t="shared" si="7"/>
+        <v>46785.166799645944</v>
       </c>
     </row>
     <row r="8" spans="2:41" x14ac:dyDescent="0.3">
@@ -1630,20 +1638,18 @@
         <v>1712</v>
       </c>
       <c r="S8" s="5">
-        <f>O8*1.14</f>
-        <v>1738.4999999999998</v>
+        <v>1728</v>
       </c>
       <c r="T8" s="5">
-        <f t="shared" ref="T8:U8" si="9">P8*1.12</f>
-        <v>1772.9600000000003</v>
+        <v>1894</v>
       </c>
       <c r="U8" s="5">
-        <f t="shared" si="9"/>
-        <v>1832.3200000000002</v>
+        <f>Q8*1.22</f>
+        <v>1995.9199999999998</v>
       </c>
       <c r="V8" s="5">
-        <f>R8*1.1</f>
-        <v>1883.2</v>
+        <f>R8*1.2</f>
+        <v>2054.4</v>
       </c>
       <c r="Y8" s="5">
         <v>1547</v>
@@ -1668,47 +1674,47 @@
       </c>
       <c r="AE8" s="5">
         <f>SUM(S8:V8)</f>
-        <v>7226.9800000000005</v>
+        <v>7672.32</v>
       </c>
       <c r="AF8" s="5">
-        <f>AE8*1.1</f>
-        <v>7949.6780000000008</v>
+        <f>AE8*1.13</f>
+        <v>8669.7215999999989</v>
       </c>
       <c r="AG8" s="5">
         <f>AF8*1.08</f>
-        <v>8585.6522400000013</v>
+        <v>9363.2993279999992</v>
       </c>
       <c r="AH8" s="5">
         <f>AG8*1.06</f>
-        <v>9100.7913744000016</v>
+        <v>9925.0972876799988</v>
       </c>
       <c r="AI8" s="5">
         <f>AH8*1.04</f>
-        <v>9464.8230293760025</v>
+        <v>10322.101179187199</v>
       </c>
       <c r="AJ8" s="5">
         <f>AI8*1.03</f>
-        <v>9748.7677202572831</v>
+        <v>10631.764214562814</v>
       </c>
       <c r="AK8" s="5">
-        <f>AJ8*1.01</f>
-        <v>9846.2553974598559</v>
+        <f t="shared" ref="AK8:AO8" si="8">AJ8*1.03</f>
+        <v>10950.717140999699</v>
       </c>
       <c r="AL8" s="5">
-        <f t="shared" ref="AL8:AO8" si="10">AK8*1.01</f>
-        <v>9944.7179514344552</v>
+        <f t="shared" si="8"/>
+        <v>11279.23865522969</v>
       </c>
       <c r="AM8" s="5">
-        <f t="shared" si="10"/>
-        <v>10044.165130948801</v>
+        <f t="shared" si="8"/>
+        <v>11617.615814886582</v>
       </c>
       <c r="AN8" s="5">
-        <f t="shared" si="10"/>
-        <v>10144.606782258288</v>
+        <f t="shared" si="8"/>
+        <v>11966.144289333179</v>
       </c>
       <c r="AO8" s="5">
-        <f t="shared" si="10"/>
-        <v>10246.05285008087</v>
+        <f t="shared" si="8"/>
+        <v>12325.128618013174</v>
       </c>
     </row>
     <row r="9" spans="2:41" x14ac:dyDescent="0.3">
@@ -1765,20 +1771,18 @@
         <v>792</v>
       </c>
       <c r="S9" s="5">
-        <f>O9*1.27</f>
-        <v>787.4</v>
+        <v>886</v>
       </c>
       <c r="T9" s="5">
-        <f t="shared" ref="T9" si="11">P9*1.25</f>
-        <v>812.5</v>
+        <v>991</v>
       </c>
       <c r="U9" s="5">
-        <f>Q9*1.2</f>
-        <v>865.19999999999993</v>
+        <f>Q9*1.45</f>
+        <v>1045.45</v>
       </c>
       <c r="V9" s="5">
-        <f>R9*1.15</f>
-        <v>910.8</v>
+        <f>R9*1.4</f>
+        <v>1108.8</v>
       </c>
       <c r="Y9" s="5">
         <v>750</v>
@@ -1803,47 +1807,47 @@
       </c>
       <c r="AE9" s="5">
         <f>SUM(S9:V9)</f>
-        <v>3375.8999999999996</v>
+        <v>4031.25</v>
       </c>
       <c r="AF9" s="5">
-        <f>AE9*1.15</f>
-        <v>3882.2849999999994</v>
+        <f>AE9*1.18</f>
+        <v>4756.875</v>
       </c>
       <c r="AG9" s="5">
         <f>AF9*1.09</f>
-        <v>4231.6906499999996</v>
+        <v>5184.9937500000005</v>
       </c>
       <c r="AH9" s="5">
         <f>AG9*1.06</f>
-        <v>4485.5920889999998</v>
+        <v>5496.0933750000013</v>
       </c>
       <c r="AI9" s="5">
         <f>AH9*1.04</f>
-        <v>4665.0157725600002</v>
+        <v>5715.9371100000017</v>
       </c>
       <c r="AJ9" s="5">
         <f>AI9*1.04</f>
-        <v>4851.6164034624007</v>
+        <v>5944.5745944000018</v>
       </c>
       <c r="AK9" s="5">
-        <f>AJ9*1.04</f>
-        <v>5045.6810596008972</v>
+        <f t="shared" ref="AK9:AO9" si="9">AJ9*1.04</f>
+        <v>6182.3575781760019</v>
       </c>
       <c r="AL9" s="5">
-        <f>AK9*1.03</f>
-        <v>5197.0514913889247</v>
+        <f t="shared" si="9"/>
+        <v>6429.6518813030425</v>
       </c>
       <c r="AM9" s="5">
-        <f t="shared" ref="AM9:AO9" si="12">AL9*1.03</f>
-        <v>5352.9630361305926</v>
+        <f t="shared" si="9"/>
+        <v>6686.8379565551641</v>
       </c>
       <c r="AN9" s="5">
-        <f t="shared" si="12"/>
-        <v>5513.5519272145102</v>
+        <f t="shared" si="9"/>
+        <v>6954.3114748173712</v>
       </c>
       <c r="AO9" s="5">
-        <f t="shared" si="12"/>
-        <v>5678.9584850309457</v>
+        <f t="shared" si="9"/>
+        <v>7232.4839338100664</v>
       </c>
     </row>
     <row r="10" spans="2:41" x14ac:dyDescent="0.3">
@@ -1900,19 +1904,17 @@
         <v>332</v>
       </c>
       <c r="S10" s="5">
-        <f>O10*0.98</f>
-        <v>384.15999999999997</v>
+        <v>316</v>
       </c>
       <c r="T10" s="5">
-        <f t="shared" ref="T10:V10" si="13">P10*0.98</f>
-        <v>364.56</v>
+        <v>308</v>
       </c>
       <c r="U10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="U10:V10" si="10">Q10*0.98</f>
         <v>344.96</v>
       </c>
       <c r="V10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>325.36</v>
       </c>
       <c r="Y10" s="5"/>
@@ -1932,48 +1934,18 @@
       </c>
       <c r="AE10" s="5">
         <f>SUM(S10:V10)</f>
-        <v>1419.04</v>
-      </c>
-      <c r="AF10" s="5">
-        <f>AE10*0.95</f>
-        <v>1348.088</v>
-      </c>
-      <c r="AG10" s="5">
-        <f t="shared" ref="AG10:AO10" si="14">AF10*0.95</f>
-        <v>1280.6835999999998</v>
-      </c>
-      <c r="AH10" s="5">
-        <f t="shared" si="14"/>
-        <v>1216.6494199999997</v>
-      </c>
-      <c r="AI10" s="5">
-        <f t="shared" si="14"/>
-        <v>1155.8169489999998</v>
-      </c>
-      <c r="AJ10" s="5">
-        <f t="shared" si="14"/>
-        <v>1098.0261015499998</v>
-      </c>
-      <c r="AK10" s="5">
-        <f t="shared" si="14"/>
-        <v>1043.1247964724998</v>
-      </c>
-      <c r="AL10" s="5">
-        <f t="shared" si="14"/>
-        <v>990.96855664887482</v>
-      </c>
-      <c r="AM10" s="5">
-        <f t="shared" si="14"/>
-        <v>941.42012881643109</v>
-      </c>
-      <c r="AN10" s="5">
-        <f t="shared" si="14"/>
-        <v>894.34912237560945</v>
-      </c>
-      <c r="AO10" s="5">
-        <f t="shared" si="14"/>
-        <v>849.63166625682891</v>
-      </c>
+        <v>1294.3200000000002</v>
+      </c>
+      <c r="AF10" s="5"/>
+      <c r="AG10" s="5"/>
+      <c r="AH10" s="5"/>
+      <c r="AI10" s="5"/>
+      <c r="AJ10" s="5"/>
+      <c r="AK10" s="5"/>
+      <c r="AL10" s="5"/>
+      <c r="AM10" s="5"/>
+      <c r="AN10" s="5"/>
+      <c r="AO10" s="5"/>
     </row>
     <row r="11" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
@@ -2029,20 +2001,16 @@
         <v>-11</v>
       </c>
       <c r="S11" s="5">
-        <f>O11*1.15</f>
-        <v>-14.95</v>
+        <v>0</v>
       </c>
       <c r="T11" s="5">
-        <f t="shared" ref="T11:V11" si="15">P11*1.15</f>
-        <v>-11.5</v>
+        <v>0</v>
       </c>
       <c r="U11" s="5">
-        <f t="shared" si="15"/>
-        <v>-16.099999999999998</v>
+        <v>0</v>
       </c>
       <c r="V11" s="5">
-        <f t="shared" si="15"/>
-        <v>-12.649999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y11" s="5">
         <v>-60</v>
@@ -2067,47 +2035,47 @@
       </c>
       <c r="AE11" s="5">
         <f>SUM(S11:V11)</f>
-        <v>-55.199999999999996</v>
+        <v>0</v>
       </c>
       <c r="AF11" s="5">
-        <f t="shared" ref="AF11:AO11" si="16">-AF3*0.002</f>
-        <v>-71.147091999999986</v>
+        <f t="shared" ref="AF11:AO11" si="11">-AF3*0.002</f>
+        <v>-80.149199999999993</v>
       </c>
       <c r="AG11" s="5">
-        <f t="shared" si="16"/>
-        <v>-79.684743040000001</v>
+        <f t="shared" si="11"/>
+        <v>-92.171579999999992</v>
       </c>
       <c r="AH11" s="5">
-        <f t="shared" si="16"/>
-        <v>-86.856369913600005</v>
+        <f t="shared" si="11"/>
+        <v>-101.388738</v>
       </c>
       <c r="AI11" s="5">
-        <f t="shared" si="16"/>
-        <v>-92.067752108416016</v>
+        <f t="shared" si="11"/>
+        <v>-110.51372442</v>
       </c>
       <c r="AJ11" s="5">
-        <f t="shared" si="16"/>
-        <v>-95.750462192752664</v>
+        <f t="shared" si="11"/>
+        <v>-118.24968512940001</v>
       </c>
       <c r="AK11" s="5">
-        <f t="shared" si="16"/>
-        <v>-98.622976058535244</v>
+        <f t="shared" si="11"/>
+        <v>-124.16216938587002</v>
       </c>
       <c r="AL11" s="5">
-        <f t="shared" si="16"/>
-        <v>-101.58166534029131</v>
+        <f t="shared" si="11"/>
+        <v>-130.37027785516352</v>
       </c>
       <c r="AM11" s="5">
-        <f t="shared" si="16"/>
-        <v>-104.62911530050006</v>
+        <f t="shared" si="11"/>
+        <v>-136.88879174792172</v>
       </c>
       <c r="AN11" s="5">
-        <f t="shared" si="16"/>
-        <v>-107.76798875951505</v>
+        <f t="shared" si="11"/>
+        <v>-143.73323133531781</v>
       </c>
       <c r="AO11" s="5">
-        <f t="shared" si="16"/>
-        <v>-111.00102842230051</v>
+        <f t="shared" si="11"/>
+        <v>-150.91989290208369</v>
       </c>
     </row>
     <row r="12" spans="2:41" x14ac:dyDescent="0.3">
@@ -2133,13 +2101,13 @@
         <v>186</v>
       </c>
       <c r="S12" s="5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T12" s="5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U12" s="5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="V12" s="5">
         <v>0</v>
@@ -2155,7 +2123,7 @@
       </c>
       <c r="AE12" s="5">
         <f>SUM(S12:V12)</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AF12" s="5"/>
       <c r="AG12" s="5"/>
@@ -2173,63 +2141,63 @@
         <v>22</v>
       </c>
       <c r="C13" s="5">
-        <f t="shared" ref="C13:Q13" si="17">SUM(C8:C11)</f>
+        <f t="shared" ref="C13:Q13" si="12">SUM(C8:C11)</f>
         <v>925</v>
       </c>
       <c r="D13" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>999</v>
       </c>
       <c r="E13" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>1138</v>
       </c>
       <c r="F13" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>1219</v>
       </c>
       <c r="G13" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>1867</v>
       </c>
       <c r="H13" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>2502</v>
       </c>
       <c r="I13" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>2418</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>2552</v>
       </c>
       <c r="K13" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>2504</v>
       </c>
       <c r="L13" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>2463</v>
       </c>
       <c r="M13" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>2523</v>
       </c>
       <c r="N13" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>2569</v>
       </c>
       <c r="O13" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>2524</v>
       </c>
       <c r="P13" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>2595</v>
       </c>
       <c r="Q13" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>2695</v>
       </c>
       <c r="R13" s="5">
@@ -2237,39 +2205,39 @@
         <v>3011</v>
       </c>
       <c r="S13" s="5">
-        <f t="shared" ref="S13:V13" si="18">SUM(S8:S12)</f>
-        <v>2995.1099999999997</v>
+        <f t="shared" ref="S13:V13" si="13">SUM(S8:S12)</f>
+        <v>2930</v>
       </c>
       <c r="T13" s="5">
-        <f t="shared" si="18"/>
-        <v>2988.52</v>
+        <f t="shared" si="13"/>
+        <v>3193</v>
       </c>
       <c r="U13" s="5">
-        <f t="shared" si="18"/>
-        <v>3076.38</v>
+        <f t="shared" si="13"/>
+        <v>3386.33</v>
       </c>
       <c r="V13" s="5">
-        <f t="shared" si="18"/>
-        <v>3106.71</v>
+        <f t="shared" si="13"/>
+        <v>3488.56</v>
       </c>
       <c r="Y13" s="5">
-        <f t="shared" ref="Y13:AC13" si="19">SUM(Y8:Y11)</f>
+        <f t="shared" ref="Y13:AC13" si="14">SUM(Y8:Y11)</f>
         <v>2237</v>
       </c>
       <c r="Z13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v>2978</v>
       </c>
       <c r="AA13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v>4281</v>
       </c>
       <c r="AB13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v>9339</v>
       </c>
       <c r="AC13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v>10059</v>
       </c>
       <c r="AD13" s="5">
@@ -2277,48 +2245,48 @@
         <v>10825</v>
       </c>
       <c r="AE13" s="5">
-        <f t="shared" ref="AE13:AO13" si="20">SUM(AE8:AE12)</f>
-        <v>12166.720000000001</v>
+        <f t="shared" ref="AE13:AO13" si="15">SUM(AE8:AE12)</f>
+        <v>12997.89</v>
       </c>
       <c r="AF13" s="5">
-        <f t="shared" si="20"/>
-        <v>13108.903908</v>
+        <f t="shared" si="15"/>
+        <v>13346.447399999999</v>
       </c>
       <c r="AG13" s="5">
-        <f t="shared" si="20"/>
-        <v>14018.341746960001</v>
+        <f t="shared" si="15"/>
+        <v>14456.121497999999</v>
       </c>
       <c r="AH13" s="5">
-        <f t="shared" si="20"/>
-        <v>14716.176513486402</v>
+        <f t="shared" si="15"/>
+        <v>15319.801924680001</v>
       </c>
       <c r="AI13" s="5">
-        <f t="shared" si="20"/>
-        <v>15193.587998827586</v>
+        <f t="shared" si="15"/>
+        <v>15927.5245647672</v>
       </c>
       <c r="AJ13" s="5">
-        <f t="shared" si="20"/>
-        <v>15602.65976307693</v>
+        <f t="shared" si="15"/>
+        <v>16458.089123833415</v>
       </c>
       <c r="AK13" s="5">
-        <f t="shared" si="20"/>
-        <v>15836.438277474719</v>
+        <f t="shared" si="15"/>
+        <v>17008.912549789831</v>
       </c>
       <c r="AL13" s="5">
-        <f t="shared" si="20"/>
-        <v>16031.156334131965</v>
+        <f t="shared" si="15"/>
+        <v>17578.52025867757</v>
       </c>
       <c r="AM13" s="5">
-        <f t="shared" si="20"/>
-        <v>16233.919180595325</v>
+        <f t="shared" si="15"/>
+        <v>18167.564979693823</v>
       </c>
       <c r="AN13" s="5">
-        <f t="shared" si="20"/>
-        <v>16444.739843088893</v>
+        <f t="shared" si="15"/>
+        <v>18776.722532815231</v>
       </c>
       <c r="AO13" s="5">
-        <f t="shared" si="20"/>
-        <v>16663.641972946345</v>
+        <f t="shared" si="15"/>
+        <v>19406.692658921158</v>
       </c>
     </row>
     <row r="14" spans="2:41" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -2326,152 +2294,152 @@
         <v>23</v>
       </c>
       <c r="C14" s="8">
-        <f t="shared" ref="C14:R14" si="21">C7-C13</f>
+        <f t="shared" ref="C14:R14" si="16">C7-C13</f>
         <v>662</v>
       </c>
       <c r="D14" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>831</v>
       </c>
       <c r="E14" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>948</v>
       </c>
       <c r="F14" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>1207</v>
       </c>
       <c r="G14" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>951</v>
       </c>
       <c r="H14" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>526</v>
       </c>
       <c r="I14" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>-64</v>
       </c>
       <c r="J14" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>-149</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>-145</v>
       </c>
       <c r="L14" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>-20</v>
       </c>
       <c r="M14" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>224</v>
       </c>
       <c r="N14" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>342</v>
       </c>
       <c r="O14" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>36</v>
       </c>
       <c r="P14" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>269</v>
       </c>
       <c r="Q14" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>724</v>
       </c>
       <c r="R14" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>871</v>
       </c>
       <c r="S14" s="8">
-        <f t="shared" ref="S14:V14" si="22">S7-S13</f>
-        <v>562.3400000000006</v>
+        <f t="shared" ref="S14:V14" si="17">S7-S13</f>
+        <v>806</v>
       </c>
       <c r="T14" s="8">
-        <f t="shared" si="22"/>
-        <v>743.54600000000028</v>
+        <f t="shared" si="17"/>
+        <v>-134</v>
       </c>
       <c r="U14" s="8">
-        <f t="shared" si="22"/>
-        <v>1079.8004999999994</v>
+        <f t="shared" si="17"/>
+        <v>1224.67</v>
       </c>
       <c r="V14" s="8">
-        <f t="shared" si="22"/>
-        <v>1648.9079999999994</v>
+        <f t="shared" si="17"/>
+        <v>1680.5900000000006</v>
       </c>
       <c r="Y14" s="8">
-        <f t="shared" ref="Y14:AD14" si="23">Y7-Y13</f>
+        <f t="shared" ref="Y14:AD14" si="18">Y7-Y13</f>
         <v>631</v>
       </c>
       <c r="Z14" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="18"/>
         <v>1369</v>
       </c>
       <c r="AA14" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="18"/>
         <v>3648</v>
       </c>
       <c r="AB14" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="18"/>
         <v>1264</v>
       </c>
       <c r="AC14" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="18"/>
         <v>401</v>
       </c>
       <c r="AD14" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="18"/>
         <v>1900</v>
       </c>
       <c r="AE14" s="8">
-        <f t="shared" ref="AE14:AO14" si="24">AE7-AE13</f>
-        <v>4034.5944999999992</v>
+        <f t="shared" ref="AE14:AO14" si="19">AE7-AE13</f>
+        <v>3577.260000000002</v>
       </c>
       <c r="AF14" s="8">
-        <f t="shared" si="24"/>
-        <v>6456.5463920000002</v>
+        <f t="shared" si="19"/>
+        <v>8694.5826000000034</v>
       </c>
       <c r="AG14" s="8">
-        <f t="shared" si="24"/>
-        <v>8691.8100194399976</v>
+        <f t="shared" si="19"/>
+        <v>11812.778801999995</v>
       </c>
       <c r="AH14" s="8">
-        <f t="shared" si="24"/>
-        <v>10906.452611025599</v>
+        <f t="shared" si="19"/>
+        <v>14589.875785319995</v>
       </c>
       <c r="AI14" s="8">
-        <f t="shared" si="24"/>
-        <v>12426.737633697217</v>
+        <f t="shared" si="19"/>
+        <v>17226.592761232801</v>
       </c>
       <c r="AJ14" s="8">
-        <f t="shared" si="24"/>
-        <v>13601.231205712631</v>
+        <f t="shared" si="19"/>
+        <v>19608.064840633589</v>
       </c>
       <c r="AK14" s="8">
-        <f t="shared" si="24"/>
-        <v>14736.684300671206</v>
+        <f t="shared" si="19"/>
+        <v>21481.359959829872</v>
       </c>
       <c r="AL14" s="8">
-        <f t="shared" si="24"/>
-        <v>15967.068248059795</v>
+        <f t="shared" si="19"/>
+        <v>22836.265876423124</v>
       </c>
       <c r="AM14" s="8">
-        <f t="shared" si="24"/>
-        <v>17247.397715564693</v>
+        <f t="shared" si="19"/>
+        <v>24267.9604621619</v>
       </c>
       <c r="AN14" s="8">
-        <f t="shared" si="24"/>
-        <v>18579.856503753501</v>
+        <f t="shared" si="19"/>
+        <v>25780.579181133286</v>
       </c>
       <c r="AO14" s="8">
-        <f t="shared" si="24"/>
-        <v>19411.692264301317</v>
+        <f t="shared" si="19"/>
+        <v>27378.474140724786</v>
       </c>
     </row>
     <row r="15" spans="2:41" x14ac:dyDescent="0.3">
@@ -2528,10 +2496,10 @@
         <v>19</v>
       </c>
       <c r="S15" s="5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T15" s="5">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="U15" s="5">
         <v>22</v>
@@ -2562,47 +2530,47 @@
       </c>
       <c r="AE15" s="5">
         <f>SUM(S15:V15)</f>
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="AF15" s="5">
-        <f t="shared" ref="AF15:AO15" si="25">AE15*1.02</f>
-        <v>89.76</v>
+        <f t="shared" ref="AF15:AO15" si="20">AE15*1.02</f>
+        <v>104.04</v>
       </c>
       <c r="AG15" s="5">
-        <f t="shared" si="25"/>
-        <v>91.555200000000013</v>
+        <f t="shared" si="20"/>
+        <v>106.1208</v>
       </c>
       <c r="AH15" s="5">
-        <f t="shared" si="25"/>
-        <v>93.38630400000001</v>
+        <f t="shared" si="20"/>
+        <v>108.243216</v>
       </c>
       <c r="AI15" s="5">
-        <f t="shared" si="25"/>
-        <v>95.254030080000007</v>
+        <f t="shared" si="20"/>
+        <v>110.40808032000001</v>
       </c>
       <c r="AJ15" s="5">
-        <f t="shared" si="25"/>
-        <v>97.159110681600012</v>
+        <f t="shared" si="20"/>
+        <v>112.61624192640001</v>
       </c>
       <c r="AK15" s="5">
-        <f t="shared" si="25"/>
-        <v>99.102292895232011</v>
+        <f t="shared" si="20"/>
+        <v>114.868566764928</v>
       </c>
       <c r="AL15" s="5">
-        <f t="shared" si="25"/>
-        <v>101.08433875313665</v>
+        <f t="shared" si="20"/>
+        <v>117.16593810022657</v>
       </c>
       <c r="AM15" s="5">
-        <f t="shared" si="25"/>
-        <v>103.10602552819938</v>
+        <f t="shared" si="20"/>
+        <v>119.5092568622311</v>
       </c>
       <c r="AN15" s="5">
-        <f t="shared" si="25"/>
-        <v>105.16814603876337</v>
+        <f t="shared" si="20"/>
+        <v>121.89944199947573</v>
       </c>
       <c r="AO15" s="5">
-        <f t="shared" si="25"/>
-        <v>107.27150895953864</v>
+        <f t="shared" si="20"/>
+        <v>124.33743083946524</v>
       </c>
     </row>
     <row r="16" spans="2:41" x14ac:dyDescent="0.3">
@@ -2659,10 +2627,10 @@
         <v>-37</v>
       </c>
       <c r="S16" s="5">
-        <v>-45</v>
+        <v>-39</v>
       </c>
       <c r="T16" s="5">
-        <v>-45</v>
+        <v>-98</v>
       </c>
       <c r="U16" s="5">
         <v>-45</v>
@@ -2693,47 +2661,47 @@
       </c>
       <c r="AE16" s="5">
         <f>SUM(S16:V16)</f>
-        <v>-180</v>
+        <v>-227</v>
       </c>
       <c r="AF16" s="5">
-        <f t="shared" ref="AF16:AO16" si="26">AE16*1.01</f>
-        <v>-181.8</v>
+        <f t="shared" ref="AF16:AO16" si="21">AE16*1.01</f>
+        <v>-229.27</v>
       </c>
       <c r="AG16" s="5">
-        <f t="shared" si="26"/>
-        <v>-183.61800000000002</v>
+        <f t="shared" si="21"/>
+        <v>-231.56270000000001</v>
       </c>
       <c r="AH16" s="5">
-        <f t="shared" si="26"/>
-        <v>-185.45418000000004</v>
+        <f t="shared" si="21"/>
+        <v>-233.87832700000001</v>
       </c>
       <c r="AI16" s="5">
-        <f t="shared" si="26"/>
-        <v>-187.30872180000003</v>
+        <f t="shared" si="21"/>
+        <v>-236.21711027000001</v>
       </c>
       <c r="AJ16" s="5">
-        <f t="shared" si="26"/>
-        <v>-189.18180901800002</v>
+        <f t="shared" si="21"/>
+        <v>-238.5792813727</v>
       </c>
       <c r="AK16" s="5">
-        <f t="shared" si="26"/>
-        <v>-191.07362710818003</v>
+        <f t="shared" si="21"/>
+        <v>-240.96507418642699</v>
       </c>
       <c r="AL16" s="5">
-        <f t="shared" si="26"/>
-        <v>-192.98436337926182</v>
+        <f t="shared" si="21"/>
+        <v>-243.37472492829127</v>
       </c>
       <c r="AM16" s="5">
-        <f t="shared" si="26"/>
-        <v>-194.91420701305444</v>
+        <f t="shared" si="21"/>
+        <v>-245.80847217757417</v>
       </c>
       <c r="AN16" s="5">
-        <f t="shared" si="26"/>
-        <v>-196.86334908318497</v>
+        <f t="shared" si="21"/>
+        <v>-248.26655689934992</v>
       </c>
       <c r="AO16" s="5">
-        <f t="shared" si="26"/>
-        <v>-198.83198257401682</v>
+        <f t="shared" si="21"/>
+        <v>-250.74922246834342</v>
       </c>
     </row>
     <row r="17" spans="2:142" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -2741,152 +2709,152 @@
         <v>26</v>
       </c>
       <c r="C17" s="8">
-        <f t="shared" ref="C17:V17" si="27">C14-SUM(C15:C16)</f>
+        <f t="shared" ref="C17:V17" si="22">C14-SUM(C15:C16)</f>
         <v>642</v>
       </c>
       <c r="D17" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="22"/>
         <v>821</v>
       </c>
       <c r="E17" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="22"/>
         <v>1003</v>
       </c>
       <c r="F17" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="22"/>
         <v>1203</v>
       </c>
       <c r="G17" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="22"/>
         <v>896</v>
       </c>
       <c r="H17" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="22"/>
         <v>497</v>
       </c>
       <c r="I17" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="22"/>
         <v>-73</v>
       </c>
       <c r="J17" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="22"/>
         <v>-136</v>
       </c>
       <c r="K17" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="22"/>
         <v>-127</v>
       </c>
       <c r="L17" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="22"/>
         <v>-2</v>
       </c>
       <c r="M17" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="22"/>
         <v>257</v>
       </c>
       <c r="N17" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="22"/>
         <v>364</v>
       </c>
       <c r="O17" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="22"/>
         <v>64</v>
       </c>
       <c r="P17" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="22"/>
         <v>299</v>
       </c>
       <c r="Q17" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="22"/>
         <v>737</v>
       </c>
       <c r="R17" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="22"/>
         <v>889</v>
       </c>
       <c r="S17" s="8">
-        <f t="shared" si="27"/>
-        <v>585.3400000000006</v>
+        <f t="shared" si="22"/>
+        <v>825</v>
       </c>
       <c r="T17" s="8">
-        <f t="shared" si="27"/>
-        <v>766.54600000000028</v>
+        <f t="shared" si="22"/>
+        <v>-74</v>
       </c>
       <c r="U17" s="8">
-        <f t="shared" si="27"/>
-        <v>1102.8004999999994</v>
+        <f t="shared" si="22"/>
+        <v>1247.67</v>
       </c>
       <c r="V17" s="8">
-        <f t="shared" si="27"/>
-        <v>1671.9079999999994</v>
+        <f t="shared" si="22"/>
+        <v>1703.5900000000006</v>
       </c>
       <c r="Y17" s="8">
-        <f t="shared" ref="Y17:AD17" si="28">Y14-SUM(Y15:Y16)</f>
+        <f t="shared" ref="Y17:AD17" si="23">Y14-SUM(Y15:Y16)</f>
         <v>372</v>
       </c>
       <c r="Z17" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="23"/>
         <v>1275</v>
       </c>
       <c r="AA17" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="23"/>
         <v>3669</v>
       </c>
       <c r="AB17" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="23"/>
         <v>1184</v>
       </c>
       <c r="AC17" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="23"/>
         <v>492</v>
       </c>
       <c r="AD17" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="23"/>
         <v>1989</v>
       </c>
       <c r="AE17" s="8">
-        <f t="shared" ref="AE17:AO17" si="29">AE14-SUM(AE15:AE16)</f>
-        <v>4126.5944999999992</v>
+        <f t="shared" ref="AE17:AO17" si="24">AE14-SUM(AE15:AE16)</f>
+        <v>3702.260000000002</v>
       </c>
       <c r="AF17" s="8">
-        <f t="shared" si="29"/>
-        <v>6548.5863920000002</v>
+        <f t="shared" si="24"/>
+        <v>8819.8126000000029</v>
       </c>
       <c r="AG17" s="8">
-        <f t="shared" si="29"/>
-        <v>8783.8728194399973</v>
+        <f t="shared" si="24"/>
+        <v>11938.220701999995</v>
       </c>
       <c r="AH17" s="8">
-        <f t="shared" si="29"/>
-        <v>10998.520487025598</v>
+        <f t="shared" si="24"/>
+        <v>14715.510896319995</v>
       </c>
       <c r="AI17" s="8">
-        <f t="shared" si="29"/>
-        <v>12518.792325417218</v>
+        <f t="shared" si="24"/>
+        <v>17352.401791182801</v>
       </c>
       <c r="AJ17" s="8">
-        <f t="shared" si="29"/>
-        <v>13693.25390404903</v>
+        <f t="shared" si="24"/>
+        <v>19734.027880079888</v>
       </c>
       <c r="AK17" s="8">
-        <f t="shared" si="29"/>
-        <v>14828.655634884155</v>
+        <f t="shared" si="24"/>
+        <v>21607.45646725137</v>
       </c>
       <c r="AL17" s="8">
-        <f t="shared" si="29"/>
-        <v>16058.968272685921</v>
+        <f t="shared" si="24"/>
+        <v>22962.474663251189</v>
       </c>
       <c r="AM17" s="8">
-        <f t="shared" si="29"/>
-        <v>17339.205897049549</v>
+        <f t="shared" si="24"/>
+        <v>24394.259677477243</v>
       </c>
       <c r="AN17" s="8">
-        <f t="shared" si="29"/>
-        <v>18671.551706797924</v>
+        <f t="shared" si="24"/>
+        <v>25906.946296033158</v>
       </c>
       <c r="AO17" s="8">
-        <f t="shared" si="29"/>
-        <v>19503.252737915795</v>
+        <f t="shared" si="24"/>
+        <v>27504.885932353664</v>
       </c>
     </row>
     <row r="18" spans="2:142" x14ac:dyDescent="0.3">
@@ -2943,20 +2911,18 @@
         <v>419</v>
       </c>
       <c r="S18" s="5">
-        <f>S17*0.18</f>
-        <v>105.36120000000011</v>
+        <v>123</v>
       </c>
       <c r="T18" s="5">
-        <f t="shared" ref="T18:V18" si="30">T17*0.18</f>
-        <v>137.97828000000004</v>
+        <v>-834</v>
       </c>
       <c r="U18" s="5">
-        <f t="shared" si="30"/>
-        <v>198.50408999999988</v>
+        <f t="shared" ref="U18:V18" si="25">U17*0.18</f>
+        <v>224.5806</v>
       </c>
       <c r="V18" s="5">
-        <f t="shared" si="30"/>
-        <v>300.9434399999999</v>
+        <f t="shared" si="25"/>
+        <v>306.64620000000008</v>
       </c>
       <c r="Y18" s="5">
         <v>31</v>
@@ -2981,47 +2947,47 @@
       </c>
       <c r="AE18" s="5">
         <f>SUM(S18:V18)</f>
-        <v>742.7870099999999</v>
+        <v>-179.77319999999992</v>
       </c>
       <c r="AF18" s="5">
-        <f t="shared" ref="AF18:AO18" si="31">AF17*0.12</f>
-        <v>785.83036703999994</v>
+        <f t="shared" ref="AF18:AO18" si="26">AF17*0.12</f>
+        <v>1058.3775120000003</v>
       </c>
       <c r="AG18" s="5">
-        <f t="shared" si="31"/>
-        <v>1054.0647383327996</v>
+        <f t="shared" si="26"/>
+        <v>1432.5864842399994</v>
       </c>
       <c r="AH18" s="5">
-        <f t="shared" si="31"/>
-        <v>1319.8224584430718</v>
+        <f t="shared" si="26"/>
+        <v>1765.8613075583992</v>
       </c>
       <c r="AI18" s="5">
-        <f t="shared" si="31"/>
-        <v>1502.2550790500661</v>
+        <f t="shared" si="26"/>
+        <v>2082.2882149419361</v>
       </c>
       <c r="AJ18" s="5">
-        <f t="shared" si="31"/>
-        <v>1643.1904684858835</v>
+        <f t="shared" si="26"/>
+        <v>2368.0833456095866</v>
       </c>
       <c r="AK18" s="5">
-        <f t="shared" si="31"/>
-        <v>1779.4386761860985</v>
+        <f t="shared" si="26"/>
+        <v>2592.8947760701644</v>
       </c>
       <c r="AL18" s="5">
-        <f t="shared" si="31"/>
-        <v>1927.0761927223105</v>
+        <f t="shared" si="26"/>
+        <v>2755.4969595901425</v>
       </c>
       <c r="AM18" s="5">
-        <f t="shared" si="31"/>
-        <v>2080.7047076459457</v>
+        <f t="shared" si="26"/>
+        <v>2927.3111612972689</v>
       </c>
       <c r="AN18" s="5">
-        <f t="shared" si="31"/>
-        <v>2240.5862048157505</v>
+        <f t="shared" si="26"/>
+        <v>3108.8335555239787</v>
       </c>
       <c r="AO18" s="5">
-        <f t="shared" si="31"/>
-        <v>2340.3903285498955</v>
+        <f t="shared" si="26"/>
+        <v>3300.5863118824395</v>
       </c>
     </row>
     <row r="19" spans="2:142" x14ac:dyDescent="0.3">
@@ -3078,20 +3044,18 @@
         <v>-12</v>
       </c>
       <c r="S19" s="5">
-        <f>-S17*0.01</f>
-        <v>-5.8534000000000059</v>
+        <v>-7</v>
       </c>
       <c r="T19" s="5">
-        <f t="shared" ref="T19:V19" si="32">-T17*0.01</f>
-        <v>-7.665460000000003</v>
+        <v>-8</v>
       </c>
       <c r="U19" s="5">
-        <f t="shared" si="32"/>
-        <v>-11.028004999999993</v>
+        <f t="shared" ref="U19:V19" si="27">-U17*0.01</f>
+        <v>-12.476700000000001</v>
       </c>
       <c r="V19" s="5">
-        <f t="shared" si="32"/>
-        <v>-16.719079999999995</v>
+        <f t="shared" si="27"/>
+        <v>-17.035900000000005</v>
       </c>
       <c r="Y19" s="5">
         <v>0</v>
@@ -3116,47 +3080,47 @@
       </c>
       <c r="AE19" s="5">
         <f>SUM(S19:V19)</f>
-        <v>-41.265945000000002</v>
+        <v>-44.512600000000006</v>
       </c>
       <c r="AF19" s="5">
         <f>-AF17*0.01</f>
-        <v>-65.48586392</v>
+        <v>-88.19812600000003</v>
       </c>
       <c r="AG19" s="5">
-        <f t="shared" ref="AG19:AO19" si="33">-AG17*0.01</f>
-        <v>-87.838728194399977</v>
+        <f t="shared" ref="AG19:AO19" si="28">-AG17*0.01</f>
+        <v>-119.38220701999995</v>
       </c>
       <c r="AH19" s="5">
-        <f t="shared" si="33"/>
-        <v>-109.98520487025598</v>
+        <f t="shared" si="28"/>
+        <v>-147.15510896319995</v>
       </c>
       <c r="AI19" s="5">
-        <f t="shared" si="33"/>
-        <v>-125.18792325417219</v>
+        <f t="shared" si="28"/>
+        <v>-173.52401791182803</v>
       </c>
       <c r="AJ19" s="5">
-        <f t="shared" si="33"/>
-        <v>-136.9325390404903</v>
+        <f t="shared" si="28"/>
+        <v>-197.34027880079887</v>
       </c>
       <c r="AK19" s="5">
-        <f t="shared" si="33"/>
-        <v>-148.28655634884154</v>
+        <f t="shared" si="28"/>
+        <v>-216.0745646725137</v>
       </c>
       <c r="AL19" s="5">
-        <f t="shared" si="33"/>
-        <v>-160.58968272685922</v>
+        <f t="shared" si="28"/>
+        <v>-229.62474663251189</v>
       </c>
       <c r="AM19" s="5">
-        <f t="shared" si="33"/>
-        <v>-173.3920589704955</v>
+        <f t="shared" si="28"/>
+        <v>-243.94259677477243</v>
       </c>
       <c r="AN19" s="5">
-        <f t="shared" si="33"/>
-        <v>-186.71551706797925</v>
+        <f t="shared" si="28"/>
+        <v>-259.06946296033158</v>
       </c>
       <c r="AO19" s="5">
-        <f t="shared" si="33"/>
-        <v>-195.03252737915795</v>
+        <f t="shared" si="28"/>
+        <v>-275.04885932353665</v>
       </c>
     </row>
     <row r="20" spans="2:142" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -3164,556 +3128,556 @@
         <v>29</v>
       </c>
       <c r="C20" s="8">
-        <f t="shared" ref="C20:Q20" si="34">C17-C18-C19</f>
+        <f t="shared" ref="C20:Q20" si="29">C17-C18-C19</f>
         <v>555</v>
       </c>
       <c r="D20" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>710</v>
       </c>
       <c r="E20" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>923</v>
       </c>
       <c r="F20" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>974</v>
       </c>
       <c r="G20" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>786</v>
       </c>
       <c r="H20" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>447</v>
       </c>
       <c r="I20" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>66</v>
       </c>
       <c r="J20" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>21</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>-139</v>
       </c>
       <c r="L20" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>27</v>
       </c>
       <c r="M20" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>299</v>
       </c>
       <c r="N20" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>667</v>
       </c>
       <c r="O20" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>123</v>
       </c>
       <c r="P20" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>265</v>
       </c>
       <c r="Q20" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>771</v>
       </c>
       <c r="R20" s="8">
-        <f t="shared" ref="R20:V20" si="35">R17-R18-R19</f>
+        <f t="shared" ref="R20:V20" si="30">R17-R18-R19</f>
         <v>482</v>
       </c>
       <c r="S20" s="8">
-        <f t="shared" si="35"/>
-        <v>485.83220000000051</v>
+        <f t="shared" si="30"/>
+        <v>709</v>
       </c>
       <c r="T20" s="8">
-        <f t="shared" si="35"/>
-        <v>636.23318000000029</v>
+        <f t="shared" si="30"/>
+        <v>768</v>
       </c>
       <c r="U20" s="8">
-        <f t="shared" si="35"/>
-        <v>915.32441499999948</v>
+        <f t="shared" si="30"/>
+        <v>1035.5661</v>
       </c>
       <c r="V20" s="8">
-        <f t="shared" si="35"/>
-        <v>1387.6836399999995</v>
+        <f t="shared" si="30"/>
+        <v>1413.9797000000005</v>
       </c>
       <c r="Y20" s="8">
-        <f t="shared" ref="Y20:AD20" si="36">Y17-Y18-Y19</f>
+        <f t="shared" ref="Y20:AD20" si="31">Y17-Y18-Y19</f>
         <v>341</v>
       </c>
       <c r="Z20" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>2490</v>
       </c>
       <c r="AA20" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>3162</v>
       </c>
       <c r="AB20" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>1320</v>
       </c>
       <c r="AC20" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>854</v>
       </c>
       <c r="AD20" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>1641</v>
       </c>
       <c r="AE20" s="8">
-        <f t="shared" ref="AE20:AO20" si="37">AE17-AE18-AE19</f>
-        <v>3425.0734349999993</v>
+        <f t="shared" ref="AE20:AO20" si="32">AE17-AE18-AE19</f>
+        <v>3926.5458000000021</v>
       </c>
       <c r="AF20" s="8">
-        <f t="shared" si="37"/>
-        <v>5828.2418888800003</v>
+        <f t="shared" si="32"/>
+        <v>7849.6332140000031</v>
       </c>
       <c r="AG20" s="8">
-        <f t="shared" si="37"/>
-        <v>7817.6468093015974</v>
+        <f t="shared" si="32"/>
+        <v>10625.016424779997</v>
       </c>
       <c r="AH20" s="8">
-        <f t="shared" si="37"/>
-        <v>9788.6832334527826</v>
+        <f t="shared" si="32"/>
+        <v>13096.804697724794</v>
       </c>
       <c r="AI20" s="8">
-        <f t="shared" si="37"/>
-        <v>11141.725169621324</v>
+        <f t="shared" si="32"/>
+        <v>15443.637594152693</v>
       </c>
       <c r="AJ20" s="8">
-        <f t="shared" si="37"/>
-        <v>12186.995974603637</v>
+        <f t="shared" si="32"/>
+        <v>17563.284813271101</v>
       </c>
       <c r="AK20" s="8">
-        <f t="shared" si="37"/>
-        <v>13197.503515046898</v>
+        <f t="shared" si="32"/>
+        <v>19230.636255853722</v>
       </c>
       <c r="AL20" s="8">
-        <f t="shared" si="37"/>
-        <v>14292.48176269047</v>
+        <f t="shared" si="32"/>
+        <v>20436.602450293558</v>
       </c>
       <c r="AM20" s="8">
-        <f t="shared" si="37"/>
-        <v>15431.893248374099</v>
+        <f t="shared" si="32"/>
+        <v>21710.891112954749</v>
       </c>
       <c r="AN20" s="8">
-        <f t="shared" si="37"/>
-        <v>16617.681019050153</v>
+        <f t="shared" si="32"/>
+        <v>23057.182203469511</v>
       </c>
       <c r="AO20" s="8">
-        <f t="shared" si="37"/>
-        <v>17357.894936745055</v>
+        <f t="shared" si="32"/>
+        <v>24479.34847979476</v>
       </c>
       <c r="AP20" s="3">
         <f>AO20*(1+$AR$25)</f>
-        <v>17184.315987377606</v>
+        <v>24234.554994996812</v>
       </c>
       <c r="AQ20" s="3">
-        <f t="shared" ref="AQ20:DB20" si="38">AP20*(1+$AR$25)</f>
-        <v>17012.472827503829</v>
+        <f t="shared" ref="AQ20:DB20" si="33">AP20*(1+$AR$25)</f>
+        <v>23992.209445046843</v>
       </c>
       <c r="AR20" s="3">
-        <f t="shared" si="38"/>
-        <v>16842.348099228791</v>
+        <f t="shared" si="33"/>
+        <v>23752.287350596376</v>
       </c>
       <c r="AS20" s="3">
-        <f t="shared" si="38"/>
-        <v>16673.924618236502</v>
+        <f t="shared" si="33"/>
+        <v>23514.764477090412</v>
       </c>
       <c r="AT20" s="3">
-        <f t="shared" si="38"/>
-        <v>16507.185372054137</v>
+        <f t="shared" si="33"/>
+        <v>23279.616832319509</v>
       </c>
       <c r="AU20" s="3">
-        <f t="shared" si="38"/>
-        <v>16342.113518333595</v>
+        <f t="shared" si="33"/>
+        <v>23046.820663996314</v>
       </c>
       <c r="AV20" s="3">
-        <f t="shared" si="38"/>
-        <v>16178.692383150259</v>
+        <f t="shared" si="33"/>
+        <v>22816.352457356352</v>
       </c>
       <c r="AW20" s="3">
-        <f t="shared" si="38"/>
-        <v>16016.905459318756</v>
+        <f t="shared" si="33"/>
+        <v>22588.188932782788</v>
       </c>
       <c r="AX20" s="3">
-        <f t="shared" si="38"/>
-        <v>15856.736404725569</v>
+        <f t="shared" si="33"/>
+        <v>22362.307043454959</v>
       </c>
       <c r="AY20" s="3">
-        <f t="shared" si="38"/>
-        <v>15698.169040678313</v>
+        <f t="shared" si="33"/>
+        <v>22138.683973020408</v>
       </c>
       <c r="AZ20" s="3">
-        <f t="shared" si="38"/>
-        <v>15541.18735027153</v>
+        <f t="shared" si="33"/>
+        <v>21917.297133290205</v>
       </c>
       <c r="BA20" s="3">
-        <f t="shared" si="38"/>
-        <v>15385.775476768815</v>
+        <f t="shared" si="33"/>
+        <v>21698.124161957305</v>
       </c>
       <c r="BB20" s="3">
-        <f t="shared" si="38"/>
-        <v>15231.917722001126</v>
+        <f t="shared" si="33"/>
+        <v>21481.14292033773</v>
       </c>
       <c r="BC20" s="3">
-        <f t="shared" si="38"/>
-        <v>15079.598544781114</v>
+        <f t="shared" si="33"/>
+        <v>21266.331491134351</v>
       </c>
       <c r="BD20" s="3">
-        <f t="shared" si="38"/>
-        <v>14928.802559333304</v>
+        <f t="shared" si="33"/>
+        <v>21053.668176223007</v>
       </c>
       <c r="BE20" s="3">
-        <f t="shared" si="38"/>
-        <v>14779.514533739972</v>
+        <f t="shared" si="33"/>
+        <v>20843.131494460777</v>
       </c>
       <c r="BF20" s="3">
-        <f t="shared" si="38"/>
-        <v>14631.719388402571</v>
+        <f t="shared" si="33"/>
+        <v>20634.700179516167</v>
       </c>
       <c r="BG20" s="3">
-        <f t="shared" si="38"/>
-        <v>14485.402194518545</v>
+        <f t="shared" si="33"/>
+        <v>20428.353177721005</v>
       </c>
       <c r="BH20" s="3">
-        <f t="shared" si="38"/>
-        <v>14340.548172573359</v>
+        <f t="shared" si="33"/>
+        <v>20224.069645943793</v>
       </c>
       <c r="BI20" s="3">
-        <f t="shared" si="38"/>
-        <v>14197.142690847626</v>
+        <f t="shared" si="33"/>
+        <v>20021.828949484356</v>
       </c>
       <c r="BJ20" s="3">
-        <f t="shared" si="38"/>
-        <v>14055.17126393915</v>
+        <f t="shared" si="33"/>
+        <v>19821.61065998951</v>
       </c>
       <c r="BK20" s="3">
-        <f t="shared" si="38"/>
-        <v>13914.619551299758</v>
+        <f t="shared" si="33"/>
+        <v>19623.394553389615</v>
       </c>
       <c r="BL20" s="3">
-        <f t="shared" si="38"/>
-        <v>13775.47335578676</v>
+        <f t="shared" si="33"/>
+        <v>19427.16060785572</v>
       </c>
       <c r="BM20" s="3">
-        <f t="shared" si="38"/>
-        <v>13637.718622228893</v>
+        <f t="shared" si="33"/>
+        <v>19232.889001777163</v>
       </c>
       <c r="BN20" s="3">
-        <f t="shared" si="38"/>
-        <v>13501.341436006604</v>
+        <f t="shared" si="33"/>
+        <v>19040.560111759391</v>
       </c>
       <c r="BO20" s="3">
-        <f t="shared" si="38"/>
-        <v>13366.328021646537</v>
+        <f t="shared" si="33"/>
+        <v>18850.154510641798</v>
       </c>
       <c r="BP20" s="3">
-        <f t="shared" si="38"/>
-        <v>13232.664741430071</v>
+        <f t="shared" si="33"/>
+        <v>18661.652965535381</v>
       </c>
       <c r="BQ20" s="3">
-        <f t="shared" si="38"/>
-        <v>13100.338094015771</v>
+        <f t="shared" si="33"/>
+        <v>18475.036435880025</v>
       </c>
       <c r="BR20" s="3">
-        <f t="shared" si="38"/>
-        <v>12969.334713075614</v>
+        <f t="shared" si="33"/>
+        <v>18290.286071521226</v>
       </c>
       <c r="BS20" s="3">
-        <f t="shared" si="38"/>
-        <v>12839.641365944857</v>
+        <f t="shared" si="33"/>
+        <v>18107.383210806012</v>
       </c>
       <c r="BT20" s="3">
-        <f t="shared" si="38"/>
-        <v>12711.244952285408</v>
+        <f t="shared" si="33"/>
+        <v>17926.309378697952</v>
       </c>
       <c r="BU20" s="3">
-        <f t="shared" si="38"/>
-        <v>12584.132502762553</v>
+        <f t="shared" si="33"/>
+        <v>17747.046284910972</v>
       </c>
       <c r="BV20" s="3">
-        <f t="shared" si="38"/>
-        <v>12458.291177734927</v>
+        <f t="shared" si="33"/>
+        <v>17569.575822061863</v>
       </c>
       <c r="BW20" s="3">
-        <f t="shared" si="38"/>
-        <v>12333.708265957577</v>
+        <f t="shared" si="33"/>
+        <v>17393.880063841243</v>
       </c>
       <c r="BX20" s="3">
-        <f t="shared" si="38"/>
-        <v>12210.371183298001</v>
+        <f t="shared" si="33"/>
+        <v>17219.941263202829</v>
       </c>
       <c r="BY20" s="3">
-        <f t="shared" si="38"/>
-        <v>12088.26747146502</v>
+        <f t="shared" si="33"/>
+        <v>17047.741850570801</v>
       </c>
       <c r="BZ20" s="3">
-        <f t="shared" si="38"/>
-        <v>11967.38479675037</v>
+        <f t="shared" si="33"/>
+        <v>16877.264432065094</v>
       </c>
       <c r="CA20" s="3">
-        <f t="shared" si="38"/>
-        <v>11847.710948782866</v>
+        <f t="shared" si="33"/>
+        <v>16708.491787744442</v>
       </c>
       <c r="CB20" s="3">
-        <f t="shared" si="38"/>
-        <v>11729.233839295037</v>
+        <f t="shared" si="33"/>
+        <v>16541.406869866998</v>
       </c>
       <c r="CC20" s="3">
-        <f t="shared" si="38"/>
-        <v>11611.941500902087</v>
+        <f t="shared" si="33"/>
+        <v>16375.992801168328</v>
       </c>
       <c r="CD20" s="3">
-        <f t="shared" si="38"/>
-        <v>11495.822085893065</v>
+        <f t="shared" si="33"/>
+        <v>16212.232873156645</v>
       </c>
       <c r="CE20" s="3">
-        <f t="shared" si="38"/>
-        <v>11380.863865034135</v>
+        <f t="shared" si="33"/>
+        <v>16050.110544425079</v>
       </c>
       <c r="CF20" s="3">
-        <f t="shared" si="38"/>
-        <v>11267.055226383793</v>
+        <f t="shared" si="33"/>
+        <v>15889.609438980828</v>
       </c>
       <c r="CG20" s="3">
-        <f t="shared" si="38"/>
-        <v>11154.384674119954</v>
+        <f t="shared" si="33"/>
+        <v>15730.713344591019</v>
       </c>
       <c r="CH20" s="3">
-        <f t="shared" si="38"/>
-        <v>11042.840827378754</v>
+        <f t="shared" si="33"/>
+        <v>15573.406211145108</v>
       </c>
       <c r="CI20" s="3">
-        <f t="shared" si="38"/>
-        <v>10932.412419104967</v>
+        <f t="shared" si="33"/>
+        <v>15417.672149033657</v>
       </c>
       <c r="CJ20" s="3">
-        <f t="shared" si="38"/>
-        <v>10823.088294913918</v>
+        <f t="shared" si="33"/>
+        <v>15263.495427543319</v>
       </c>
       <c r="CK20" s="3">
-        <f t="shared" si="38"/>
-        <v>10714.857411964778</v>
+        <f t="shared" si="33"/>
+        <v>15110.860473267885</v>
       </c>
       <c r="CL20" s="3">
-        <f t="shared" si="38"/>
-        <v>10607.70883784513</v>
+        <f t="shared" si="33"/>
+        <v>14959.751868535206</v>
       </c>
       <c r="CM20" s="3">
-        <f t="shared" si="38"/>
-        <v>10501.631749466678</v>
+        <f t="shared" si="33"/>
+        <v>14810.154349849854</v>
       </c>
       <c r="CN20" s="3">
-        <f t="shared" si="38"/>
-        <v>10396.615431972012</v>
+        <f t="shared" si="33"/>
+        <v>14662.052806351356</v>
       </c>
       <c r="CO20" s="3">
-        <f t="shared" si="38"/>
-        <v>10292.649277652292</v>
+        <f t="shared" si="33"/>
+        <v>14515.432278287843</v>
       </c>
       <c r="CP20" s="3">
-        <f t="shared" si="38"/>
-        <v>10189.722784875768</v>
+        <f t="shared" si="33"/>
+        <v>14370.277955504964</v>
       </c>
       <c r="CQ20" s="3">
-        <f t="shared" si="38"/>
-        <v>10087.82555702701</v>
+        <f t="shared" si="33"/>
+        <v>14226.575175949914</v>
       </c>
       <c r="CR20" s="3">
-        <f t="shared" si="38"/>
-        <v>9986.9473014567393</v>
+        <f t="shared" si="33"/>
+        <v>14084.309424190415</v>
       </c>
       <c r="CS20" s="3">
-        <f t="shared" si="38"/>
-        <v>9887.0778284421722</v>
+        <f t="shared" si="33"/>
+        <v>13943.466329948511</v>
       </c>
       <c r="CT20" s="3">
-        <f t="shared" si="38"/>
-        <v>9788.2070501577509</v>
+        <f t="shared" si="33"/>
+        <v>13804.031666649025</v>
       </c>
       <c r="CU20" s="3">
-        <f t="shared" si="38"/>
-        <v>9690.324979656174</v>
+        <f t="shared" si="33"/>
+        <v>13665.991349982534</v>
       </c>
       <c r="CV20" s="3">
-        <f t="shared" si="38"/>
-        <v>9593.4217298596122</v>
+        <f t="shared" si="33"/>
+        <v>13529.331436482709</v>
       </c>
       <c r="CW20" s="3">
-        <f t="shared" si="38"/>
-        <v>9497.487512561016</v>
+        <f t="shared" si="33"/>
+        <v>13394.038122117881</v>
       </c>
       <c r="CX20" s="3">
-        <f t="shared" si="38"/>
-        <v>9402.5126374354058</v>
+        <f t="shared" si="33"/>
+        <v>13260.097740896703</v>
       </c>
       <c r="CY20" s="3">
-        <f t="shared" si="38"/>
-        <v>9308.4875110610519</v>
+        <f t="shared" si="33"/>
+        <v>13127.496763487736</v>
       </c>
       <c r="CZ20" s="3">
-        <f t="shared" si="38"/>
-        <v>9215.4026359504405</v>
+        <f t="shared" si="33"/>
+        <v>12996.221795852858</v>
       </c>
       <c r="DA20" s="3">
-        <f t="shared" si="38"/>
-        <v>9123.2486095909353</v>
+        <f t="shared" si="33"/>
+        <v>12866.259577894329</v>
       </c>
       <c r="DB20" s="3">
-        <f t="shared" si="38"/>
-        <v>9032.0161234950265</v>
+        <f t="shared" si="33"/>
+        <v>12737.596982115385</v>
       </c>
       <c r="DC20" s="3">
-        <f t="shared" ref="DC20:EL20" si="39">DB20*(1+$AR$25)</f>
-        <v>8941.6959622600752</v>
+        <f t="shared" ref="DC20:EL20" si="34">DB20*(1+$AR$25)</f>
+        <v>12610.221012294231</v>
       </c>
       <c r="DD20" s="3">
-        <f t="shared" si="39"/>
-        <v>8852.2790026374751</v>
+        <f t="shared" si="34"/>
+        <v>12484.118802171288</v>
       </c>
       <c r="DE20" s="3">
-        <f t="shared" si="39"/>
-        <v>8763.7562126111006</v>
+        <f t="shared" si="34"/>
+        <v>12359.277614149574</v>
       </c>
       <c r="DF20" s="3">
-        <f t="shared" si="39"/>
-        <v>8676.1186504849902</v>
+        <f t="shared" si="34"/>
+        <v>12235.684838008079</v>
       </c>
       <c r="DG20" s="3">
-        <f t="shared" si="39"/>
-        <v>8589.3574639801409</v>
+        <f t="shared" si="34"/>
+        <v>12113.327989627998</v>
       </c>
       <c r="DH20" s="3">
-        <f t="shared" si="39"/>
-        <v>8503.4638893403389</v>
+        <f t="shared" si="34"/>
+        <v>11992.194709731719</v>
       </c>
       <c r="DI20" s="3">
-        <f t="shared" si="39"/>
-        <v>8418.4292504469358</v>
+        <f t="shared" si="34"/>
+        <v>11872.272762634402</v>
       </c>
       <c r="DJ20" s="3">
-        <f t="shared" si="39"/>
-        <v>8334.2449579424665</v>
+        <f t="shared" si="34"/>
+        <v>11753.550035008058</v>
       </c>
       <c r="DK20" s="3">
-        <f t="shared" si="39"/>
-        <v>8250.9025083630422</v>
+        <f t="shared" si="34"/>
+        <v>11636.014534657977</v>
       </c>
       <c r="DL20" s="3">
-        <f t="shared" si="39"/>
-        <v>8168.3934832794121</v>
+        <f t="shared" si="34"/>
+        <v>11519.654389311398</v>
       </c>
       <c r="DM20" s="3">
-        <f t="shared" si="39"/>
-        <v>8086.7095484466181</v>
+        <f t="shared" si="34"/>
+        <v>11404.457845418283</v>
       </c>
       <c r="DN20" s="3">
-        <f t="shared" si="39"/>
-        <v>8005.8424529621516</v>
+        <f t="shared" si="34"/>
+        <v>11290.4132669641</v>
       </c>
       <c r="DO20" s="3">
-        <f t="shared" si="39"/>
-        <v>7925.7840284325302</v>
+        <f t="shared" si="34"/>
+        <v>11177.50913429446</v>
       </c>
       <c r="DP20" s="3">
-        <f t="shared" si="39"/>
-        <v>7846.5261881482047</v>
+        <f t="shared" si="34"/>
+        <v>11065.734042951515</v>
       </c>
       <c r="DQ20" s="3">
-        <f t="shared" si="39"/>
-        <v>7768.0609262667222</v>
+        <f t="shared" si="34"/>
+        <v>10955.076702521999</v>
       </c>
       <c r="DR20" s="3">
-        <f t="shared" si="39"/>
-        <v>7690.3803170040546</v>
+        <f t="shared" si="34"/>
+        <v>10845.525935496778</v>
       </c>
       <c r="DS20" s="3">
-        <f t="shared" si="39"/>
-        <v>7613.4765138340144</v>
+        <f t="shared" si="34"/>
+        <v>10737.070676141811</v>
       </c>
       <c r="DT20" s="3">
-        <f t="shared" si="39"/>
-        <v>7537.3417486956741</v>
+        <f t="shared" si="34"/>
+        <v>10629.699969380394</v>
       </c>
       <c r="DU20" s="3">
-        <f t="shared" si="39"/>
-        <v>7461.9683312087172</v>
+        <f t="shared" si="34"/>
+        <v>10523.402969686589</v>
       </c>
       <c r="DV20" s="3">
-        <f t="shared" si="39"/>
-        <v>7387.3486478966297</v>
+        <f t="shared" si="34"/>
+        <v>10418.168939989722</v>
       </c>
       <c r="DW20" s="3">
-        <f t="shared" si="39"/>
-        <v>7313.475161417663</v>
+        <f t="shared" si="34"/>
+        <v>10313.987250589826</v>
       </c>
       <c r="DX20" s="3">
-        <f t="shared" si="39"/>
-        <v>7240.3404098034862</v>
+        <f t="shared" si="34"/>
+        <v>10210.847378083927</v>
       </c>
       <c r="DY20" s="3">
-        <f t="shared" si="39"/>
-        <v>7167.9370057054512</v>
+        <f t="shared" si="34"/>
+        <v>10108.738904303087</v>
       </c>
       <c r="DZ20" s="3">
-        <f t="shared" si="39"/>
-        <v>7096.2576356483969</v>
+        <f t="shared" si="34"/>
+        <v>10007.651515260057</v>
       </c>
       <c r="EA20" s="3">
-        <f t="shared" si="39"/>
-        <v>7025.2950592919133</v>
+        <f t="shared" si="34"/>
+        <v>9907.5750001074557</v>
       </c>
       <c r="EB20" s="3">
-        <f t="shared" si="39"/>
-        <v>6955.0421086989945</v>
+        <f t="shared" si="34"/>
+        <v>9808.4992501063807</v>
       </c>
       <c r="EC20" s="3">
-        <f t="shared" si="39"/>
-        <v>6885.4916876120042</v>
+        <f t="shared" si="34"/>
+        <v>9710.4142576053164</v>
       </c>
       <c r="ED20" s="3">
-        <f t="shared" si="39"/>
-        <v>6816.6367707358841</v>
+        <f t="shared" si="34"/>
+        <v>9613.3101150292623</v>
       </c>
       <c r="EE20" s="3">
-        <f t="shared" si="39"/>
-        <v>6748.4704030285247</v>
+        <f t="shared" si="34"/>
+        <v>9517.1770138789689</v>
       </c>
       <c r="EF20" s="3">
-        <f t="shared" si="39"/>
-        <v>6680.9856989982391</v>
+        <f t="shared" si="34"/>
+        <v>9422.0052437401791</v>
       </c>
       <c r="EG20" s="3">
-        <f t="shared" si="39"/>
-        <v>6614.175842008257</v>
+        <f t="shared" si="34"/>
+        <v>9327.7851913027771</v>
       </c>
       <c r="EH20" s="3">
-        <f t="shared" si="39"/>
-        <v>6548.0340835881743</v>
+        <f t="shared" si="34"/>
+        <v>9234.5073393897492</v>
       </c>
       <c r="EI20" s="3">
-        <f t="shared" si="39"/>
-        <v>6482.5537427522922</v>
+        <f t="shared" si="34"/>
+        <v>9142.1622659958521</v>
       </c>
       <c r="EJ20" s="3">
-        <f t="shared" si="39"/>
-        <v>6417.7282053247691</v>
+        <f t="shared" si="34"/>
+        <v>9050.7406433358938</v>
       </c>
       <c r="EK20" s="3">
-        <f t="shared" si="39"/>
-        <v>6353.5509232715212</v>
+        <f t="shared" si="34"/>
+        <v>8960.2332369025353</v>
       </c>
       <c r="EL20" s="3">
-        <f t="shared" si="39"/>
-        <v>6290.0154140388058</v>
+        <f t="shared" si="34"/>
+        <v>8870.6309045335092</v>
       </c>
     </row>
     <row r="21" spans="2:142" x14ac:dyDescent="0.3">
@@ -3770,20 +3734,20 @@
         <v>1620.5</v>
       </c>
       <c r="S21" s="5">
-        <f t="shared" ref="S21:V21" si="40">1620.5</f>
+        <f>1620.5</f>
         <v>1620.5</v>
       </c>
       <c r="T21" s="5">
-        <f t="shared" si="40"/>
-        <v>1620.5</v>
+        <f>1623</f>
+        <v>1623</v>
       </c>
       <c r="U21" s="5">
-        <f t="shared" si="40"/>
-        <v>1620.5</v>
+        <f>1623</f>
+        <v>1623</v>
       </c>
       <c r="V21" s="5">
-        <f t="shared" si="40"/>
-        <v>1620.5</v>
+        <f>1623</f>
+        <v>1623</v>
       </c>
       <c r="Y21" s="5">
         <v>1622.8</v>
@@ -3801,52 +3765,52 @@
         <v>1622.8</v>
       </c>
       <c r="AD21" s="5">
-        <f t="shared" ref="AD21:AO21" si="41">1620.5</f>
+        <f t="shared" ref="AD21" si="35">1620.5</f>
         <v>1620.5</v>
       </c>
       <c r="AE21" s="5">
-        <f t="shared" si="41"/>
-        <v>1620.5</v>
+        <f>1623</f>
+        <v>1623</v>
       </c>
       <c r="AF21" s="5">
-        <f t="shared" si="41"/>
-        <v>1620.5</v>
+        <f>1623</f>
+        <v>1623</v>
       </c>
       <c r="AG21" s="5">
-        <f t="shared" si="41"/>
-        <v>1620.5</v>
+        <f>1623</f>
+        <v>1623</v>
       </c>
       <c r="AH21" s="5">
-        <f t="shared" si="41"/>
-        <v>1620.5</v>
+        <f>1623</f>
+        <v>1623</v>
       </c>
       <c r="AI21" s="5">
-        <f t="shared" si="41"/>
-        <v>1620.5</v>
+        <f>1623</f>
+        <v>1623</v>
       </c>
       <c r="AJ21" s="5">
-        <f t="shared" si="41"/>
-        <v>1620.5</v>
+        <f>1623</f>
+        <v>1623</v>
       </c>
       <c r="AK21" s="5">
-        <f t="shared" si="41"/>
-        <v>1620.5</v>
+        <f>1623</f>
+        <v>1623</v>
       </c>
       <c r="AL21" s="5">
-        <f t="shared" si="41"/>
-        <v>1620.5</v>
+        <f>1623</f>
+        <v>1623</v>
       </c>
       <c r="AM21" s="5">
-        <f t="shared" si="41"/>
-        <v>1620.5</v>
+        <f>1623</f>
+        <v>1623</v>
       </c>
       <c r="AN21" s="5">
-        <f t="shared" si="41"/>
-        <v>1620.5</v>
+        <f>1623</f>
+        <v>1623</v>
       </c>
       <c r="AO21" s="5">
-        <f t="shared" si="41"/>
-        <v>1620.5</v>
+        <f>1623</f>
+        <v>1623</v>
       </c>
     </row>
     <row r="22" spans="2:142" x14ac:dyDescent="0.3">
@@ -3854,152 +3818,152 @@
         <v>30</v>
       </c>
       <c r="C22" s="7">
-        <f t="shared" ref="C22:Q22" si="42">C20/C21</f>
+        <f t="shared" ref="C22:Q22" si="36">C20/C21</f>
         <v>0.3420014789253143</v>
       </c>
       <c r="D22" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="36"/>
         <v>0.43751540547202367</v>
       </c>
       <c r="E22" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="36"/>
         <v>0.56877002711363078</v>
       </c>
       <c r="F22" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="36"/>
         <v>0.60019719004190286</v>
       </c>
       <c r="G22" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="36"/>
         <v>0.48434804042395863</v>
       </c>
       <c r="H22" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="36"/>
         <v>0.27544983978309096</v>
       </c>
       <c r="I22" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="36"/>
         <v>4.0670446142469806E-2</v>
       </c>
       <c r="J22" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="36"/>
         <v>1.2940596499876757E-2</v>
       </c>
       <c r="K22" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="36"/>
         <v>-8.5654424451565195E-2</v>
       </c>
       <c r="L22" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="36"/>
         <v>1.6637909785555832E-2</v>
       </c>
       <c r="M22" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="36"/>
         <v>0.18424944540300717</v>
       </c>
       <c r="N22" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="36"/>
         <v>0.41101799359132363</v>
       </c>
       <c r="O22" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="36"/>
         <v>7.5794922356421005E-2</v>
       </c>
       <c r="P22" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="36"/>
         <v>0.16329800345082573</v>
       </c>
       <c r="Q22" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="36"/>
         <v>0.47510475720976092</v>
       </c>
       <c r="R22" s="7">
-        <f t="shared" ref="R22:V22" si="43">R20/R21</f>
+        <f t="shared" ref="R22:V22" si="37">R20/R21</f>
         <v>0.29743906201789572</v>
       </c>
       <c r="S22" s="7">
-        <f t="shared" si="43"/>
-        <v>0.29980388768898519</v>
+        <f t="shared" si="37"/>
+        <v>0.437519284171552</v>
       </c>
       <c r="T22" s="7">
-        <f t="shared" si="43"/>
-        <v>0.39261535328602298</v>
+        <f t="shared" si="37"/>
+        <v>0.47319778188539741</v>
       </c>
       <c r="U22" s="7">
-        <f t="shared" si="43"/>
-        <v>0.56484073742671981</v>
+        <f t="shared" si="37"/>
+        <v>0.63805674676524959</v>
       </c>
       <c r="V22" s="7">
-        <f t="shared" si="43"/>
-        <v>0.85633053995680319</v>
+        <f t="shared" si="37"/>
+        <v>0.87121361675908848</v>
       </c>
       <c r="Y22" s="7">
-        <f t="shared" ref="Y22:AD22" si="44">Y20/Y21</f>
+        <f t="shared" ref="Y22:AD22" si="38">Y20/Y21</f>
         <v>0.21013063840276067</v>
       </c>
       <c r="Z22" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>1.5343850135568153</v>
       </c>
       <c r="AA22" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>1.9484841015528716</v>
       </c>
       <c r="AB22" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>0.81340892284939614</v>
       </c>
       <c r="AC22" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>0.52625092432832143</v>
       </c>
       <c r="AD22" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>1.0126504165381056</v>
       </c>
       <c r="AE22" s="7">
-        <f t="shared" ref="AE22:AO22" si="45">AE20/AE21</f>
-        <v>2.1135905183585311</v>
+        <f t="shared" ref="AE22:AO22" si="39">AE20/AE21</f>
+        <v>2.4193134935305003</v>
       </c>
       <c r="AF22" s="7">
-        <f t="shared" si="45"/>
-        <v>3.5965701258130207</v>
+        <f t="shared" si="39"/>
+        <v>4.8364961269254483</v>
       </c>
       <c r="AG22" s="7">
-        <f t="shared" si="45"/>
-        <v>4.8242189505100876</v>
+        <f t="shared" si="39"/>
+        <v>6.546528912372148</v>
       </c>
       <c r="AH22" s="7">
-        <f t="shared" si="45"/>
-        <v>6.0405326957437717</v>
+        <f t="shared" si="39"/>
+        <v>8.0695038186844084</v>
       </c>
       <c r="AI22" s="7">
-        <f t="shared" si="45"/>
-        <v>6.8754860657953252</v>
+        <f t="shared" si="39"/>
+        <v>9.5154883512955593</v>
       </c>
       <c r="AJ22" s="7">
-        <f t="shared" si="45"/>
-        <v>7.5205158744854286</v>
+        <f t="shared" si="39"/>
+        <v>10.821494031590326</v>
       </c>
       <c r="AK22" s="7">
-        <f t="shared" si="45"/>
-        <v>8.1440934989490259</v>
+        <f t="shared" si="39"/>
+        <v>11.848820860045423</v>
       </c>
       <c r="AL22" s="7">
-        <f t="shared" si="45"/>
-        <v>8.8197974468932241</v>
+        <f t="shared" si="39"/>
+        <v>12.591868422854935</v>
       </c>
       <c r="AM22" s="7">
-        <f t="shared" si="45"/>
-        <v>9.5229208567566186</v>
+        <f t="shared" si="39"/>
+        <v>13.377012392455175</v>
       </c>
       <c r="AN22" s="7">
-        <f t="shared" si="45"/>
-        <v>10.254662770163623</v>
+        <f t="shared" si="39"/>
+        <v>14.206520150012022</v>
       </c>
       <c r="AO22" s="7">
-        <f t="shared" si="45"/>
-        <v>10.711443959731598</v>
+        <f t="shared" si="39"/>
+        <v>15.082777868018953</v>
       </c>
     </row>
     <row r="24" spans="2:142" x14ac:dyDescent="0.3">
@@ -4015,64 +3979,64 @@
         <v>0.70885341074020314</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" ref="H24:R24" si="46">H3/D3-1</f>
+        <f t="shared" ref="H24:R24" si="40">H3/D3-1</f>
         <v>0.70129870129870131</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="40"/>
         <v>0.29028518432645489</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="40"/>
         <v>0.16017405719021971</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="40"/>
         <v>-9.0708340411075228E-2</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="40"/>
         <v>-0.18183206106870231</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="40"/>
         <v>4.2228212039532753E-2</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="40"/>
         <v>0.10162529023039824</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="40"/>
         <v>2.2417336073230043E-2</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="40"/>
         <v>8.882254151894009E-2</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="40"/>
         <v>0.17568965517241386</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="40"/>
         <v>0.24156939040207526</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" ref="S24" si="47">S3/O3-1</f>
+        <f t="shared" ref="S24" si="41">S3/O3-1</f>
+        <v>0.35903526402338759</v>
+      </c>
+      <c r="T24" s="9">
+        <f t="shared" ref="T24" si="42">T3/P3-1</f>
+        <v>0.31705227077977716</v>
+      </c>
+      <c r="U24" s="9">
+        <f t="shared" ref="U24" si="43">U3/Q3-1</f>
+        <v>0.27584689837219534</v>
+      </c>
+      <c r="V24" s="9">
+        <f t="shared" ref="V24" si="44">V3/R3-1</f>
         <v>0.25</v>
-      </c>
-      <c r="T24" s="9">
-        <f t="shared" ref="T24" si="48">T3/P3-1</f>
-        <v>0.22999999999999998</v>
-      </c>
-      <c r="U24" s="9">
-        <f t="shared" ref="U24" si="49">U3/Q3-1</f>
-        <v>0.14999999999999991</v>
-      </c>
-      <c r="V24" s="9">
-        <f t="shared" ref="V24" si="50">V3/R3-1</f>
-        <v>0.14999999999999991</v>
       </c>
       <c r="Y24" s="9"/>
       <c r="Z24" s="9">
@@ -4080,64 +4044,64 @@
         <v>0.45045312732134901</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" ref="AA24:AO24" si="51">AA3/Z3-1</f>
+        <f t="shared" ref="AA24:AO24" si="45">AA3/Z3-1</f>
         <v>0.68329406944586712</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="45"/>
         <v>0.43610806863818907</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="45"/>
         <v>-3.9023770179229644E-2</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="45"/>
         <v>0.13690476190476186</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="51"/>
-        <v>0.18932906728718235</v>
+        <f t="shared" si="45"/>
+        <v>0.29515222028311028</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="51"/>
-        <v>0.15999999999999992</v>
+        <f t="shared" si="45"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="51"/>
-        <v>0.12000000000000011</v>
+        <f t="shared" si="45"/>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="45"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AI24" s="9">
+        <f t="shared" si="45"/>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="AI24" s="9">
-        <f t="shared" si="51"/>
-        <v>6.0000000000000053E-2</v>
-      </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="51"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="45"/>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="AK24" s="9">
-        <f t="shared" si="51"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="45"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AL24" s="9">
-        <f t="shared" si="51"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="45"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AM24" s="9">
-        <f t="shared" si="51"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="45"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AN24" s="9">
-        <f t="shared" si="51"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="45"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AO24" s="9">
-        <f t="shared" si="51"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="45"/>
+        <v>5.0000000000000044E-2</v>
       </c>
     </row>
     <row r="25" spans="2:142" x14ac:dyDescent="0.3">
@@ -4145,19 +4109,19 @@
         <v>46</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:F25" si="52">C7/C3</f>
+        <f t="shared" ref="C25:F25" si="46">C7/C3</f>
         <v>0.46066763425253993</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="46"/>
         <v>0.47532467532467532</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="46"/>
         <v>0.48365406909343844</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="46"/>
         <v>0.50269374222958974</v>
       </c>
       <c r="G25" s="9">
@@ -4165,132 +4129,132 @@
         <v>0.4786818413453372</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" ref="H25:R25" si="53">H7/H3</f>
+        <f t="shared" ref="H25:R25" si="47">H7/H3</f>
         <v>0.46229007633587788</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>0.42300089847259659</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>0.42918378281836045</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>0.44068746497291239</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>0.4558686322075014</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>0.4736206896551724</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>0.47195201037613488</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>0.46775077653937513</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>0.49083119108826051</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>0.50139316615339491</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="47"/>
         <v>0.50692086706711936</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" ref="S25:V25" si="54">S7/S3</f>
-        <v>0.52</v>
+        <f t="shared" ref="S25:V25" si="48">S7/S3</f>
+        <v>0.50228556063457919</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" si="54"/>
-        <v>0.52</v>
+        <f t="shared" si="48"/>
+        <v>0.39804814573845154</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="54"/>
-        <v>0.52999999999999992</v>
+        <f t="shared" si="48"/>
+        <v>0.53</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="48"/>
         <v>0.54</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" ref="Y25" si="55">Y7/Y3</f>
+        <f t="shared" ref="Y25" si="49">Y7/Y3</f>
         <v>0.42608824840291187</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" ref="Z25:AO25" si="56">Z7/Z3</f>
+        <f t="shared" ref="Z25:AO25" si="50">Z7/Z3</f>
         <v>0.44525248386766364</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>0.48247535596933189</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>0.4492606245498072</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>0.46119929453262787</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>0.49350397517936784</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="56"/>
-        <v>0.52830057537699504</v>
+        <f t="shared" si="50"/>
+        <v>0.49632884670090288</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>0.55000000000000004</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>0.56999999999999995</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>0.59</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>0.6</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>0.61</v>
       </c>
       <c r="AK25" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>0.62</v>
       </c>
       <c r="AL25" s="9">
-        <f t="shared" si="56"/>
-        <v>0.63</v>
+        <f t="shared" si="50"/>
+        <v>0.62</v>
       </c>
       <c r="AM25" s="9">
-        <f t="shared" si="56"/>
-        <v>0.64</v>
+        <f t="shared" si="50"/>
+        <v>0.62</v>
       </c>
       <c r="AN25" s="9">
-        <f t="shared" si="56"/>
-        <v>0.65</v>
+        <f t="shared" si="50"/>
+        <v>0.62</v>
       </c>
       <c r="AO25" s="9">
-        <f t="shared" si="56"/>
-        <v>0.65</v>
+        <f t="shared" si="50"/>
+        <v>0.62</v>
       </c>
       <c r="AQ25" t="s">
         <v>54</v>
@@ -4304,19 +4268,19 @@
         <v>47</v>
       </c>
       <c r="C26" s="9">
-        <f t="shared" ref="C26:F26" si="57">(C3-C4)/C3</f>
+        <f t="shared" ref="C26:F26" si="51">(C3-C4)/C3</f>
         <v>0.46066763425253993</v>
       </c>
       <c r="D26" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="51"/>
         <v>0.47532467532467532</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="51"/>
         <v>0.48365406909343844</v>
       </c>
       <c r="F26" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="51"/>
         <v>0.50269374222958974</v>
       </c>
       <c r="G26" s="9">
@@ -4324,87 +4288,87 @@
         <v>0.51027688126380155</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" ref="H26:R26" si="58">(H3-H4)/H3</f>
+        <f t="shared" ref="H26:R26" si="52">(H3-H4)/H3</f>
         <v>0.52442748091603053</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.49703504043126684</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.5083050544740132</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.49766486082570521</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.49542825153946629</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.5098275862068965</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.50680933852140075</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.5097752603690846</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.53041988003427587</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.53556239917876525</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.53982763123530952</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" ref="S26:V26" si="59">(S3-S4)/S3</f>
+        <f t="shared" ref="S26:V26" si="53">(S3-S4)/S3</f>
+        <v>0.53603119118042486</v>
+      </c>
+      <c r="T26" s="9">
+        <f t="shared" si="53"/>
+        <v>0.43188028627195835</v>
+      </c>
+      <c r="U26" s="9">
+        <f t="shared" si="53"/>
         <v>1</v>
       </c>
-      <c r="T26" s="9">
-        <f t="shared" si="59"/>
+      <c r="V26" s="9">
+        <f t="shared" si="53"/>
         <v>1</v>
       </c>
-      <c r="U26" s="9">
-        <f t="shared" si="59"/>
-        <v>1</v>
-      </c>
-      <c r="V26" s="9">
-        <f t="shared" si="59"/>
-        <v>1</v>
-      </c>
       <c r="Y26" s="9">
-        <f t="shared" ref="Y26" si="60">(Y3-Y4)/Y3</f>
+        <f t="shared" ref="Y26" si="54">(Y3-Y4)/Y3</f>
         <v>0.42608824840291187</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" ref="Z26:AD26" si="61">(Z3-Z4)/Z3</f>
+        <f t="shared" ref="Z26:AD26" si="55">(Z3-Z4)/Z3</f>
         <v>0.44525248386766364</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="55"/>
         <v>0.48247535596933189</v>
       </c>
       <c r="AB26" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="55"/>
         <v>0.51061395703571888</v>
       </c>
       <c r="AC26" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="55"/>
         <v>0.5027336860670194</v>
       </c>
       <c r="AD26" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="55"/>
         <v>0.53019197207678881</v>
       </c>
       <c r="AE26" s="9"/>
@@ -4422,7 +4386,7 @@
         <v>55</v>
       </c>
       <c r="AR26" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="27" spans="2:142" x14ac:dyDescent="0.3">
@@ -4438,64 +4402,64 @@
         <v>0.73770491803278682</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" ref="H27:R27" si="62">H8/D8-1</f>
+        <f t="shared" ref="H27:R27" si="56">H8/D8-1</f>
         <v>0.9726858877086495</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>0.67189542483660136</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>0.68434032059186189</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>0.33113207547169821</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>0.1100000000000001</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>0.17826426896012504</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>0.10614934114202046</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>8.0793763288447895E-2</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>9.7020097020096951E-2</v>
       </c>
       <c r="Q27" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>8.5600530856005275E-2</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>0.13302448709463932</v>
       </c>
       <c r="S27" s="9">
-        <f t="shared" ref="S27:S28" si="63">S8/O8-1</f>
-        <v>0.1399999999999999</v>
+        <f t="shared" ref="S27:S28" si="57">S8/O8-1</f>
+        <v>0.1331147540983606</v>
       </c>
       <c r="T27" s="9">
-        <f t="shared" ref="T27:T28" si="64">T8/P8-1</f>
-        <v>0.12000000000000011</v>
+        <f t="shared" ref="T27:T28" si="58">T8/P8-1</f>
+        <v>0.19646241313960844</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" ref="U27:U28" si="65">U8/Q8-1</f>
-        <v>0.12000000000000011</v>
+        <f t="shared" ref="U27:U28" si="59">U8/Q8-1</f>
+        <v>0.21999999999999997</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" ref="V27:V28" si="66">V8/R8-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="V27:V28" si="60">V8/R8-1</f>
+        <v>0.19999999999999996</v>
       </c>
       <c r="Y27" s="9"/>
       <c r="Z27" s="9">
@@ -4503,71 +4467,71 @@
         <v>0.28183581124757606</v>
       </c>
       <c r="AA27" s="9">
-        <f t="shared" ref="AA27:AO27" si="67">AA8/Z8-1</f>
+        <f t="shared" ref="AA27:AO27" si="61">AA8/Z8-1</f>
         <v>0.43469490670700961</v>
       </c>
       <c r="AB27" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="61"/>
         <v>0.75922671353251325</v>
       </c>
       <c r="AC27" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="61"/>
         <v>0.17322677322677316</v>
       </c>
       <c r="AD27" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="61"/>
         <v>9.9455040871934575E-2</v>
       </c>
       <c r="AE27" s="9">
-        <f t="shared" si="67"/>
-        <v>0.11942069392812904</v>
+        <f t="shared" si="61"/>
+        <v>0.18840148698884751</v>
       </c>
       <c r="AF27" s="9">
-        <f t="shared" si="67"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="61"/>
+        <v>0.12999999999999989</v>
       </c>
       <c r="AG27" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="61"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AH27" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="61"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AI27" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="61"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AJ27" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="61"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AK27" s="9">
-        <f t="shared" si="67"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="61"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AL27" s="9">
-        <f t="shared" si="67"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="61"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AM27" s="9">
-        <f t="shared" si="67"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="61"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AN27" s="9">
-        <f t="shared" si="67"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="61"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AO27" s="9">
-        <f t="shared" si="67"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="61"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AQ27" t="s">
         <v>56</v>
       </c>
       <c r="AR27" s="5">
         <f>NPV(AR26,AE20:EL20)</f>
-        <v>181842.68949999224</v>
+        <v>300334.0880058615</v>
       </c>
     </row>
     <row r="28" spans="2:142" x14ac:dyDescent="0.3">
@@ -4583,64 +4547,64 @@
         <v>0.87147335423197503</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" ref="H28:R28" si="68">H9/D9-1</f>
+        <f t="shared" ref="H28:R28" si="62">H9/D9-1</f>
         <v>0.73607038123167157</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>0.4813829787234043</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>0.43203883495145634</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>-2.010050251256279E-2</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>-7.6013513513513487E-2</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>3.4111310592459532E-2</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>9.1525423728813449E-2</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>5.9829059829059839E-2</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>0.1882998171846435</v>
       </c>
       <c r="Q28" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>0.25173611111111116</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>0.22981366459627339</v>
       </c>
       <c r="S28" s="9">
-        <f t="shared" si="63"/>
-        <v>0.27</v>
+        <f t="shared" si="57"/>
+        <v>0.42903225806451606</v>
       </c>
       <c r="T28" s="9">
-        <f t="shared" si="64"/>
-        <v>0.25</v>
+        <f t="shared" si="58"/>
+        <v>0.52461538461538471</v>
       </c>
       <c r="U28" s="9">
-        <f t="shared" si="65"/>
-        <v>0.19999999999999996</v>
+        <f t="shared" si="59"/>
+        <v>0.44999999999999996</v>
       </c>
       <c r="V28" s="9">
-        <f t="shared" si="66"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="60"/>
+        <v>0.39999999999999991</v>
       </c>
       <c r="Y28" s="9"/>
       <c r="Z28" s="9">
@@ -4648,71 +4612,71 @@
         <v>0.32666666666666666</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" ref="AA28:AO28" si="69">AA9/Z9-1</f>
+        <f t="shared" ref="AA28:AO28" si="63">AA9/Z9-1</f>
         <v>0.45527638190954778</v>
       </c>
       <c r="AB28" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="63"/>
         <v>0.61325966850828739</v>
       </c>
       <c r="AC28" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="63"/>
         <v>6.8493150684931781E-3</v>
       </c>
       <c r="AD28" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="63"/>
         <v>0.18324829931972797</v>
       </c>
       <c r="AE28" s="9">
-        <f t="shared" si="69"/>
-        <v>0.21304347826086945</v>
+        <f t="shared" si="63"/>
+        <v>0.44852676967301464</v>
       </c>
       <c r="AF28" s="9">
-        <f t="shared" si="69"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="63"/>
+        <v>0.17999999999999994</v>
       </c>
       <c r="AG28" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="63"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="AH28" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="63"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="63"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AJ28" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="63"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AK28" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="63"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AL28" s="9">
-        <f t="shared" si="69"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="63"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AM28" s="9">
-        <f t="shared" si="69"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="63"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AN28" s="9">
-        <f t="shared" si="69"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="63"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AO28" s="9">
-        <f t="shared" si="69"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="63"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AQ28" t="s">
         <v>57</v>
       </c>
       <c r="AR28" s="5">
         <f>Main!D8</f>
-        <v>3560</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="29" spans="2:142" x14ac:dyDescent="0.3">
@@ -4720,19 +4684,19 @@
         <v>50</v>
       </c>
       <c r="C29" s="9">
-        <f t="shared" ref="C29:F29" si="70">C9/C3</f>
+        <f t="shared" ref="C29:F29" si="64">C9/C3</f>
         <v>9.2597968069666178E-2</v>
       </c>
       <c r="D29" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="64"/>
         <v>8.8571428571428565E-2</v>
       </c>
       <c r="E29" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="64"/>
         <v>8.7178298168328311E-2</v>
       </c>
       <c r="F29" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="64"/>
         <v>8.5370907583920436E-2</v>
       </c>
       <c r="G29" s="9">
@@ -4740,139 +4704,139 @@
         <v>0.10140988618990997</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" ref="H29:R29" si="71">H9/H3</f>
+        <f t="shared" ref="H29:R29" si="65">H9/H3</f>
         <v>9.0381679389312977E-2</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="65"/>
         <v>0.10008984725965858</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="65"/>
         <v>0.10537595999285587</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="65"/>
         <v>0.10928451335699607</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="65"/>
         <v>0.10207128195558873</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="65"/>
         <v>9.9310344827586203E-2</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="65"/>
         <v>0.10440985732814527</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="65"/>
         <v>0.11328339119312991</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="65"/>
         <v>0.11139674378748929</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="65"/>
         <v>0.10573397858923596</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="65"/>
         <v>0.10342125881431183</v>
       </c>
       <c r="S29" s="9">
-        <f t="shared" ref="S29:V29" si="72">S9/S3</f>
-        <v>0.11509592545221999</v>
+        <f t="shared" ref="S29:V29" si="66">S9/S3</f>
+        <v>0.11911804248453886</v>
       </c>
       <c r="T29" s="9">
-        <f t="shared" si="72"/>
-        <v>0.11320807295476554</v>
+        <f t="shared" si="66"/>
+        <v>0.12895250487963567</v>
       </c>
       <c r="U29" s="9">
-        <f t="shared" si="72"/>
-        <v>0.11033110809311578</v>
+        <f t="shared" si="66"/>
+        <v>0.12016666666666667</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="72"/>
-        <v>0.10342125881431184</v>
+        <f t="shared" si="66"/>
+        <v>0.11583180987202925</v>
       </c>
       <c r="Y29" s="9">
-        <f t="shared" ref="Y29" si="73">Y9/Y3</f>
+        <f t="shared" ref="Y29" si="67">Y9/Y3</f>
         <v>0.1114247511513891</v>
       </c>
       <c r="Z29" s="9">
-        <f t="shared" ref="Z29:AO29" si="74">Z9/Z3</f>
+        <f t="shared" ref="Z29:AO29" si="68">Z9/Z3</f>
         <v>0.10191539485813787</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>8.81100158208592E-2</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>9.8978856828100509E-2</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>0.1037037037037037</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>0.10793096761683149</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" si="74"/>
-        <v>0.11008303754705813</v>
+        <f t="shared" si="68"/>
+        <v>0.12071237142728811</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" si="74"/>
-        <v>0.10913404584406626</v>
+        <f t="shared" si="68"/>
+        <v>0.11870049857016664</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" si="74"/>
-        <v>0.10621081247324304</v>
+        <f t="shared" si="68"/>
+        <v>0.11250742907954928</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" si="74"/>
-        <v>0.10328757910241984</v>
+        <f t="shared" si="68"/>
+        <v>0.10841624984029294</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="74"/>
-        <v>0.10133875685520438</v>
+        <f t="shared" si="68"/>
+        <v>0.10344302737055473</v>
       </c>
       <c r="AJ29" s="9">
-        <f t="shared" si="74"/>
-        <v>0.10133875685520438</v>
+        <f t="shared" si="68"/>
+        <v>0.10054275557511862</v>
       </c>
       <c r="AK29" s="9">
-        <f t="shared" si="74"/>
-        <v>0.10232262828098307</v>
+        <f t="shared" si="68"/>
+        <v>9.9585205522022241E-2</v>
       </c>
       <c r="AL29" s="9">
-        <f t="shared" si="74"/>
-        <v>0.10232262828098307</v>
+        <f t="shared" si="68"/>
+        <v>9.8636774993241083E-2</v>
       </c>
       <c r="AM29" s="9">
-        <f t="shared" si="74"/>
-        <v>0.10232262828098307</v>
+        <f t="shared" si="68"/>
+        <v>9.7697377136162597E-2</v>
       </c>
       <c r="AN29" s="9">
-        <f t="shared" si="74"/>
-        <v>0.10232262828098307</v>
+        <f t="shared" si="68"/>
+        <v>9.6766925925341987E-2</v>
       </c>
       <c r="AO29" s="9">
-        <f t="shared" si="74"/>
-        <v>0.10232262828098307</v>
+        <f t="shared" si="68"/>
+        <v>9.5845336154624455E-2</v>
       </c>
       <c r="AQ29" t="s">
         <v>58</v>
       </c>
       <c r="AR29" s="5">
         <f>AR27+AR28</f>
-        <v>185402.68949999224</v>
+        <v>302983.0880058615</v>
       </c>
     </row>
     <row r="30" spans="2:142" x14ac:dyDescent="0.3">
@@ -4884,155 +4848,125 @@
         <v>0</v>
       </c>
       <c r="D30" s="9">
-        <f t="shared" ref="D30:R30" si="75">D10/D3</f>
+        <f t="shared" ref="D30:R30" si="69">D10/D3</f>
         <v>0</v>
       </c>
       <c r="E30" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="F30" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="G30" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="69"/>
         <v>4.9770681161882116E-2</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="69"/>
         <v>9.4045801526717557E-2</v>
       </c>
       <c r="I30" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="69"/>
         <v>0.10601976639712489</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="69"/>
         <v>0.10734059653509555</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="69"/>
         <v>9.6768167382776007E-2</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="69"/>
         <v>8.9755551408844933E-2</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="69"/>
         <v>7.7586206896551727E-2</v>
       </c>
       <c r="N30" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="69"/>
         <v>6.8093385214007776E-2</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="69"/>
         <v>7.1624337657591811E-2</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="69"/>
         <v>6.3753213367609252E-2</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="69"/>
         <v>5.1620472210001468E-2</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="69"/>
         <v>4.3353355967615567E-2</v>
       </c>
       <c r="S30" s="9">
-        <f t="shared" ref="S30:V30" si="76">S10/S3</f>
-        <v>5.6153480723551981E-2</v>
+        <f t="shared" ref="S30:V30" si="70">S10/S3</f>
+        <v>4.2484538854530789E-2</v>
       </c>
       <c r="T30" s="9">
-        <f t="shared" si="76"/>
-        <v>5.0795243170940703E-2</v>
+        <f t="shared" si="70"/>
+        <v>4.0078074170461941E-2</v>
       </c>
       <c r="U30" s="9">
-        <f t="shared" si="76"/>
-        <v>4.3989619796349078E-2</v>
+        <f t="shared" si="70"/>
+        <v>3.9650574712643674E-2</v>
       </c>
       <c r="V30" s="9">
-        <f t="shared" si="76"/>
-        <v>3.6944598998489793E-2</v>
+        <f t="shared" si="70"/>
+        <v>3.3989031078610607E-2</v>
       </c>
       <c r="Y30" s="9">
-        <f t="shared" ref="Y30" si="77">Y10/Y3</f>
+        <f t="shared" ref="Y30" si="71">Y10/Y3</f>
         <v>0</v>
       </c>
       <c r="Z30" s="9">
-        <f t="shared" ref="Z30:AO30" si="78">Z10/Z3</f>
+        <f t="shared" ref="Z30:AE30" si="72">Z10/Z3</f>
         <v>0</v>
       </c>
       <c r="AA30" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AB30" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="72"/>
         <v>8.8979280538960218E-2</v>
       </c>
       <c r="AC30" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="72"/>
         <v>8.2407407407407401E-2</v>
       </c>
       <c r="AD30" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="72"/>
         <v>5.6156680240449876E-2</v>
       </c>
       <c r="AE30" s="9">
-        <f t="shared" si="78"/>
-        <v>4.6272766847589498E-2</v>
-      </c>
-      <c r="AF30" s="9">
-        <f t="shared" si="78"/>
-        <v>3.7895800435525887E-2</v>
-      </c>
-      <c r="AG30" s="9">
-        <f t="shared" si="78"/>
-        <v>3.2143759297990702E-2</v>
-      </c>
-      <c r="AH30" s="9">
-        <f t="shared" si="78"/>
-        <v>2.8015203057881799E-2</v>
-      </c>
-      <c r="AI30" s="9">
-        <f t="shared" si="78"/>
-        <v>2.5107965004705385E-2</v>
-      </c>
-      <c r="AJ30" s="9">
-        <f t="shared" si="78"/>
-        <v>2.2935160340836647E-2</v>
-      </c>
-      <c r="AK30" s="9">
-        <f t="shared" si="78"/>
-        <v>2.1153788663878459E-2</v>
-      </c>
-      <c r="AL30" s="9">
-        <f t="shared" si="78"/>
-        <v>1.9510775952120907E-2</v>
-      </c>
-      <c r="AM30" s="9">
-        <f t="shared" si="78"/>
-        <v>1.799537587816977E-2</v>
-      </c>
-      <c r="AN30" s="9">
-        <f t="shared" si="78"/>
-        <v>1.6597676780836193E-2</v>
-      </c>
-      <c r="AO30" s="9">
-        <f t="shared" si="78"/>
-        <v>1.5308536836693577E-2</v>
-      </c>
+        <f t="shared" si="72"/>
+        <v>3.8757317602671024E-2</v>
+      </c>
+      <c r="AF30" s="9"/>
+      <c r="AG30" s="9"/>
+      <c r="AH30" s="9"/>
+      <c r="AI30" s="9"/>
+      <c r="AJ30" s="9"/>
+      <c r="AK30" s="9"/>
+      <c r="AL30" s="9"/>
+      <c r="AM30" s="9"/>
+      <c r="AN30" s="9"/>
+      <c r="AO30" s="9"/>
       <c r="AQ30" t="s">
         <v>59</v>
       </c>
       <c r="AR30" s="4">
         <f>AR29/AO21</f>
-        <v>114.41079265658269</v>
+        <v>186.68089217859611</v>
       </c>
     </row>
     <row r="31" spans="2:142" x14ac:dyDescent="0.3">
@@ -5040,19 +4974,19 @@
         <v>51</v>
       </c>
       <c r="C31" s="9">
-        <f t="shared" ref="C31:F31" si="79">C14/C3</f>
+        <f t="shared" ref="C31:F31" si="73">C14/C3</f>
         <v>0.19216255442670538</v>
       </c>
       <c r="D31" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="73"/>
         <v>0.21584415584415584</v>
       </c>
       <c r="E31" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="73"/>
         <v>0.21980060282865754</v>
       </c>
       <c r="F31" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="73"/>
         <v>0.25010360547036886</v>
       </c>
       <c r="G31" s="9">
@@ -5060,139 +4994,139 @@
         <v>0.16154238151860031</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" ref="H31:R31" si="80">H14/H3</f>
+        <f t="shared" ref="H31:R31" si="74">H14/H3</f>
         <v>8.0305343511450383E-2</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="74"/>
         <v>-1.1500449236298293E-2</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="74"/>
         <v>-2.661189498124665E-2</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="74"/>
         <v>-2.7087614421819541E-2</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="74"/>
         <v>-3.7320395596193321E-3</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="74"/>
         <v>3.8620689655172416E-2</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="74"/>
         <v>5.544747081712062E-2</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="74"/>
         <v>6.5777452950849628E-3</v>
       </c>
       <c r="P31" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="74"/>
         <v>4.6101113967437872E-2</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="74"/>
         <v>0.10617392579557119</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="74"/>
         <v>0.11373726821624446</v>
       </c>
       <c r="S31" s="9">
-        <f t="shared" ref="S31:V31" si="81">S14/S3</f>
-        <v>8.2198428649735145E-2</v>
+        <f t="shared" ref="S31:V31" si="75">S14/S3</f>
+        <v>0.10836246302769562</v>
       </c>
       <c r="T31" s="9">
-        <f t="shared" si="81"/>
-        <v>0.10360050438550662</v>
+        <f t="shared" si="75"/>
+        <v>-1.7436564736499675E-2</v>
       </c>
       <c r="U31" s="9">
-        <f t="shared" si="81"/>
-        <v>0.13769716329692605</v>
+        <f t="shared" si="75"/>
+        <v>0.14076666666666668</v>
       </c>
       <c r="V31" s="9">
-        <f t="shared" si="81"/>
-        <v>0.18723335642181516</v>
+        <f t="shared" si="75"/>
+        <v>0.17556437712196402</v>
       </c>
       <c r="Y31" s="9">
-        <f t="shared" ref="Y31" si="82">Y14/Y3</f>
+        <f t="shared" ref="Y31" si="76">Y14/Y3</f>
         <v>9.3745357302035356E-2</v>
       </c>
       <c r="Z31" s="9">
-        <f t="shared" ref="Z31:AO31" si="83">Z14/Z3</f>
+        <f t="shared" ref="Z31:AO31" si="77">Z14/Z3</f>
         <v>0.14022329202089523</v>
       </c>
       <c r="AA31" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="77"/>
         <v>0.22197882438846295</v>
       </c>
       <c r="AB31" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="77"/>
         <v>5.3557052667259859E-2</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="77"/>
         <v>1.7680776014109348E-2</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="77"/>
         <v>7.3686251696722896E-2</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" si="83"/>
-        <v>0.13156207761801422</v>
+        <f t="shared" si="77"/>
+        <v>0.10711802488359216</v>
       </c>
       <c r="AF31" s="9">
-        <f t="shared" si="83"/>
-        <v>0.18149853242069264</v>
+        <f t="shared" si="77"/>
+        <v>0.21695993472174405</v>
       </c>
       <c r="AG31" s="9">
-        <f t="shared" si="83"/>
-        <v>0.21815493626118362</v>
+        <f t="shared" si="77"/>
+        <v>0.25632149957720152</v>
       </c>
       <c r="AH31" s="9">
-        <f t="shared" si="83"/>
-        <v>0.2511376568437006</v>
+        <f t="shared" si="77"/>
+        <v>0.28780071777439414</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="83"/>
-        <v>0.26994767112514906</v>
+        <f t="shared" si="77"/>
+        <v>0.3117548132893303</v>
       </c>
       <c r="AJ31" s="9">
-        <f t="shared" si="83"/>
-        <v>0.28409745277954607</v>
+        <f t="shared" si="77"/>
+        <v>0.33163834337785486</v>
       </c>
       <c r="AK31" s="9">
-        <f t="shared" si="83"/>
-        <v>0.29884890701178207</v>
+        <f t="shared" si="77"/>
+        <v>0.34602101535565644</v>
       </c>
       <c r="AL31" s="9">
-        <f t="shared" si="83"/>
-        <v>0.31436909789913881</v>
+        <f t="shared" si="77"/>
+        <v>0.35032932739152944</v>
       </c>
       <c r="AM31" s="9">
-        <f t="shared" si="83"/>
-        <v>0.32968639113557074</v>
+        <f t="shared" si="77"/>
+        <v>0.35456460901270753</v>
       </c>
       <c r="AN31" s="9">
-        <f t="shared" si="83"/>
-        <v>0.34481216022718153</v>
+        <f t="shared" si="77"/>
+        <v>0.35872816524926399</v>
       </c>
       <c r="AO31" s="9">
-        <f t="shared" si="83"/>
-        <v>0.34975698045697456</v>
+        <f t="shared" si="77"/>
+        <v>0.36282127709284612</v>
       </c>
       <c r="AQ31" t="s">
         <v>60</v>
       </c>
       <c r="AR31" s="4">
         <f>Main!D3</f>
-        <v>93.62</v>
+        <v>150.74</v>
       </c>
     </row>
     <row r="32" spans="2:142" x14ac:dyDescent="0.3">
@@ -5200,19 +5134,19 @@
         <v>27</v>
       </c>
       <c r="C32" s="9">
-        <f t="shared" ref="C32:F32" si="84">C18/C17</f>
+        <f t="shared" ref="C32:F32" si="78">C18/C17</f>
         <v>0.13862928348909656</v>
       </c>
       <c r="D32" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="78"/>
         <v>0.13763702801461633</v>
       </c>
       <c r="E32" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="78"/>
         <v>8.175473579262213E-2</v>
       </c>
       <c r="F32" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="78"/>
         <v>0.19035743973399832</v>
       </c>
       <c r="G32" s="9">
@@ -5220,139 +5154,139 @@
         <v>0.12611607142857142</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" ref="H32:R32" si="85">H18/H17</f>
+        <f t="shared" ref="H32:R32" si="79">H18/H17</f>
         <v>0.10865191146881288</v>
       </c>
       <c r="I32" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>1.8493150684931507</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>1.1323529411764706</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>-0.10236220472440945</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>11.5</v>
       </c>
       <c r="M32" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>-0.1517509727626459</v>
       </c>
       <c r="N32" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>-0.81593406593406592</v>
       </c>
       <c r="O32" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>-0.8125</v>
       </c>
       <c r="P32" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>0.13712374581939799</v>
       </c>
       <c r="Q32" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>-3.6635006784260515E-2</v>
       </c>
       <c r="R32" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>0.47131608548931386</v>
       </c>
       <c r="S32" s="9">
-        <f t="shared" ref="S32:V32" si="86">S18/S17</f>
+        <f t="shared" ref="S32:V32" si="80">S18/S17</f>
+        <v>0.14909090909090908</v>
+      </c>
+      <c r="T32" s="9">
+        <f t="shared" si="80"/>
+        <v>11.27027027027027</v>
+      </c>
+      <c r="U32" s="9">
+        <f t="shared" si="80"/>
         <v>0.18</v>
       </c>
-      <c r="T32" s="9">
-        <f t="shared" si="86"/>
+      <c r="V32" s="9">
+        <f t="shared" si="80"/>
         <v>0.18</v>
       </c>
-      <c r="U32" s="9">
-        <f t="shared" si="86"/>
-        <v>0.18</v>
-      </c>
-      <c r="V32" s="9">
-        <f t="shared" si="86"/>
-        <v>0.18</v>
-      </c>
       <c r="Y32" s="9">
-        <f t="shared" ref="Y32" si="87">Y18/Y17</f>
+        <f t="shared" ref="Y32" si="81">Y18/Y17</f>
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="Z32" s="9">
-        <f t="shared" ref="Z32:AO32" si="88">Z18/Z17</f>
+        <f t="shared" ref="Z32:AO32" si="82">Z18/Z17</f>
         <v>-0.94901960784313721</v>
       </c>
       <c r="AA32" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="82"/>
         <v>0.13982011447260834</v>
       </c>
       <c r="AB32" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="82"/>
         <v>-0.10304054054054054</v>
       </c>
       <c r="AC32" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="82"/>
         <v>-0.7032520325203252</v>
       </c>
       <c r="AD32" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="82"/>
         <v>0.19155354449472098</v>
       </c>
       <c r="AE32" s="9">
-        <f t="shared" si="88"/>
-        <v>0.18000000000000002</v>
+        <f t="shared" si="82"/>
+        <v>-4.8557691788259014E-2</v>
       </c>
       <c r="AF32" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="82"/>
+        <v>0.12</v>
+      </c>
+      <c r="AG32" s="9">
+        <f t="shared" si="82"/>
+        <v>0.12</v>
+      </c>
+      <c r="AH32" s="9">
+        <f t="shared" si="82"/>
         <v>0.11999999999999998</v>
       </c>
-      <c r="AG32" s="9">
-        <f t="shared" si="88"/>
+      <c r="AI32" s="9">
+        <f t="shared" si="82"/>
         <v>0.12</v>
       </c>
-      <c r="AH32" s="9">
-        <f t="shared" si="88"/>
+      <c r="AJ32" s="9">
+        <f t="shared" si="82"/>
         <v>0.12</v>
       </c>
-      <c r="AI32" s="9">
-        <f t="shared" si="88"/>
+      <c r="AK32" s="9">
+        <f t="shared" si="82"/>
+        <v>0.12000000000000001</v>
+      </c>
+      <c r="AL32" s="9">
+        <f t="shared" si="82"/>
         <v>0.12</v>
       </c>
-      <c r="AJ32" s="9">
-        <f t="shared" si="88"/>
+      <c r="AM32" s="9">
+        <f t="shared" si="82"/>
         <v>0.12</v>
       </c>
-      <c r="AK32" s="9">
-        <f t="shared" si="88"/>
+      <c r="AN32" s="9">
+        <f t="shared" si="82"/>
+        <v>0.11999999999999998</v>
+      </c>
+      <c r="AO32" s="9">
+        <f t="shared" si="82"/>
         <v>0.12</v>
-      </c>
-      <c r="AL32" s="9">
-        <f t="shared" si="88"/>
-        <v>0.12</v>
-      </c>
-      <c r="AM32" s="9">
-        <f t="shared" si="88"/>
-        <v>0.12</v>
-      </c>
-      <c r="AN32" s="9">
-        <f t="shared" si="88"/>
-        <v>0.11999999999999998</v>
-      </c>
-      <c r="AO32" s="9">
-        <f t="shared" si="88"/>
-        <v>0.12000000000000001</v>
       </c>
       <c r="AQ32" s="3" t="s">
         <v>61</v>
       </c>
       <c r="AR32" s="10">
         <f>AR30/AR31-1</f>
-        <v>0.22207640094619396</v>
+        <v>0.2384296946968032</v>
       </c>
     </row>
     <row r="33" spans="2:44" x14ac:dyDescent="0.3">
@@ -5360,19 +5294,19 @@
         <v>52</v>
       </c>
       <c r="C33" s="9">
-        <f t="shared" ref="C33:F33" si="89">C20/C3</f>
+        <f t="shared" ref="C33:F33" si="83">C20/C3</f>
         <v>0.16110304789550073</v>
       </c>
       <c r="D33" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="83"/>
         <v>0.18441558441558442</v>
       </c>
       <c r="E33" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="83"/>
         <v>0.21400417342916764</v>
       </c>
       <c r="F33" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="83"/>
         <v>0.20182345627849149</v>
       </c>
       <c r="G33" s="9">
@@ -5380,138 +5314,138 @@
         <v>0.13351452352641413</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" ref="H33:R33" si="90">H20/H3</f>
+        <f t="shared" ref="H33:R33" si="84">H20/H3</f>
         <v>6.8244274809160302E-2</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="84"/>
         <v>1.1859838274932614E-2</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="84"/>
         <v>3.7506697624575818E-3</v>
       </c>
       <c r="K33" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="84"/>
         <v>-2.5966747618158044E-2</v>
       </c>
       <c r="L33" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="84"/>
         <v>5.0382534054860982E-3</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="84"/>
         <v>5.1551724137931035E-2</v>
       </c>
       <c r="N33" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="84"/>
         <v>0.10813878080415046</v>
       </c>
       <c r="O33" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="84"/>
         <v>2.2473963091540289E-2</v>
       </c>
       <c r="P33" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="84"/>
         <v>4.5415595544130251E-2</v>
       </c>
       <c r="Q33" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="84"/>
         <v>0.11306643202815662</v>
       </c>
       <c r="R33" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="84"/>
         <v>6.2940715591538257E-2</v>
       </c>
       <c r="S33" s="9">
-        <f t="shared" ref="S33:V33" si="91">S20/S3</f>
-        <v>7.101512150557289E-2</v>
+        <f t="shared" ref="S33:V33" si="85">S20/S3</f>
+        <v>9.5321322936273198E-2</v>
       </c>
       <c r="T33" s="9">
-        <f t="shared" si="91"/>
-        <v>8.8648285855609243E-2</v>
+        <f t="shared" si="85"/>
+        <v>9.9934938191281714E-2</v>
       </c>
       <c r="U33" s="9">
-        <f t="shared" si="91"/>
-        <v>0.11672302007817027</v>
+        <f t="shared" si="85"/>
+        <v>0.11903058620689655</v>
       </c>
       <c r="V33" s="9">
-        <f t="shared" si="91"/>
-        <v>0.15757135362848737</v>
+        <f t="shared" si="85"/>
+        <v>0.14771268738574045</v>
       </c>
       <c r="Y33" s="9">
-        <f t="shared" ref="Y33" si="92">Y20/Y3</f>
+        <f t="shared" ref="Y33" si="86">Y20/Y3</f>
         <v>5.0661120190164909E-2</v>
       </c>
       <c r="Z33" s="9">
-        <f t="shared" ref="Z33:AO33" si="93">Z20/Z3</f>
+        <f t="shared" ref="Z33:AO33" si="87">Z20/Z3</f>
         <v>0.25504455597664655</v>
       </c>
       <c r="AA33" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="87"/>
         <v>0.19240598758671049</v>
       </c>
       <c r="AB33" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="87"/>
         <v>5.5929833481632135E-2</v>
       </c>
       <c r="AC33" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="87"/>
         <v>3.7654320987654324E-2</v>
       </c>
       <c r="AD33" s="9">
-        <f t="shared" si="93"/>
+        <f t="shared" si="87"/>
         <v>6.3641652123327522E-2</v>
       </c>
       <c r="AE33" s="9">
-        <f t="shared" si="93"/>
-        <v>0.11168650953717123</v>
+        <f t="shared" si="87"/>
+        <v>0.1175770927220734</v>
       </c>
       <c r="AF33" s="9">
-        <f t="shared" si="93"/>
-        <v>0.16383640497576488</v>
+        <f t="shared" si="87"/>
+        <v>0.19587552250053658</v>
       </c>
       <c r="AG33" s="9">
-        <f t="shared" si="93"/>
-        <v>0.19621439465211826</v>
+        <f t="shared" si="87"/>
+        <v>0.23054864470762024</v>
       </c>
       <c r="AH33" s="9">
-        <f t="shared" si="93"/>
-        <v>0.22539931712987848</v>
+        <f t="shared" si="87"/>
+        <v>0.25834831276280001</v>
       </c>
       <c r="AI33" s="9">
-        <f t="shared" si="93"/>
-        <v>0.24203317479721215</v>
+        <f t="shared" si="87"/>
+        <v>0.27948813914659476</v>
       </c>
       <c r="AJ33" s="9">
-        <f t="shared" si="93"/>
-        <v>0.25455743388622659</v>
+        <f t="shared" si="87"/>
+        <v>0.29705423391278701</v>
       </c>
       <c r="AK33" s="9">
-        <f t="shared" si="93"/>
-        <v>0.26763547486569139</v>
+        <f t="shared" si="87"/>
+        <v>0.30976643451015956</v>
       </c>
       <c r="AL33" s="9">
-        <f t="shared" si="93"/>
-        <v>0.28139884721936148</v>
+        <f t="shared" si="87"/>
+        <v>0.31351628279871974</v>
       </c>
       <c r="AM33" s="9">
-        <f t="shared" si="93"/>
-        <v>0.29498277232016978</v>
+        <f t="shared" si="87"/>
+        <v>0.31720480304822868</v>
       </c>
       <c r="AN33" s="9">
-        <f t="shared" si="93"/>
-        <v>0.30839734897776766</v>
+        <f t="shared" si="87"/>
+        <v>0.32083300416003313</v>
       </c>
       <c r="AO33" s="9">
-        <f t="shared" si="93"/>
-        <v>0.31275196605760081</v>
+        <f t="shared" si="87"/>
+        <v>0.32440187981947322</v>
       </c>
       <c r="AQ33" t="s">
         <v>62</v>
       </c>
       <c r="AR33" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/AMD.xlsx
+++ b/Financial Analysis/AMD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90592336-7628-436E-A184-C7AEEF03C703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0662FF93-B5FE-4FBE-A730-15236FEF286B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9151AF15-9D45-44A9-8CA3-26C538A98864}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9151AF15-9D45-44A9-8CA3-26C538A98864}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -232,10 +232,10 @@
     <t>Restructuring</t>
   </si>
   <si>
-    <t>Q225 8K</t>
-  </si>
-  <si>
-    <t>Slightly undervalued</t>
+    <t>Slightly overvalued</t>
+  </si>
+  <si>
+    <t>Q325 8K</t>
   </si>
 </sst>
 </file>
@@ -335,14 +335,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
@@ -359,7 +359,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13106400" y="0"/>
+          <a:off x="13708380" y="0"/>
           <a:ext cx="0" cy="6499860"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -759,17 +759,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>150.74</v>
+        <v>239.23</v>
       </c>
       <c r="E3" s="2">
-        <v>45918</v>
+        <v>45966</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45918</v>
+        <v>45966</v>
       </c>
       <c r="G3" s="2">
-        <v>45967</v>
+        <v>46056</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -777,11 +777,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>1623</f>
-        <v>1623</v>
+        <f>1626</f>
+        <v>1626</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -790,7 +790,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>244651.02000000002</v>
+        <v>388987.98</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -798,11 +798,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>4442+1425</f>
-        <v>5867</v>
+        <f>4808+2435</f>
+        <v>7243</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -810,11 +810,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>3218</f>
-        <v>3218</v>
+        <f>873+2347</f>
+        <v>3220</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -823,7 +823,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>2649</v>
+        <v>4023</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -832,7 +832,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>242002.02000000002</v>
+        <v>384964.98</v>
       </c>
     </row>
   </sheetData>
@@ -1024,11 +1024,11 @@
         <v>7685</v>
       </c>
       <c r="U3" s="8">
-        <v>8700</v>
+        <v>9246</v>
       </c>
       <c r="V3" s="8">
-        <f>R3*1.25</f>
-        <v>9572.5</v>
+        <f>R3*1.27</f>
+        <v>9725.66</v>
       </c>
       <c r="Y3" s="8">
         <v>6731</v>
@@ -1053,47 +1053,47 @@
       </c>
       <c r="AE3" s="8">
         <f>SUM(S3:V3)</f>
-        <v>33395.5</v>
+        <v>34094.660000000003</v>
       </c>
       <c r="AF3" s="8">
-        <f>AE3*1.2</f>
-        <v>40074.6</v>
+        <f>AE3*1.23</f>
+        <v>41936.431800000006</v>
       </c>
       <c r="AG3" s="8">
         <f>AF3*1.15</f>
-        <v>46085.789999999994</v>
+        <v>48226.896570000004</v>
       </c>
       <c r="AH3" s="8">
         <f>AG3*1.1</f>
-        <v>50694.368999999999</v>
+        <v>53049.586227000007</v>
       </c>
       <c r="AI3" s="8">
         <f>AH3*1.09</f>
-        <v>55256.862209999999</v>
+        <v>57824.048987430011</v>
       </c>
       <c r="AJ3" s="8">
         <f>AI3*1.07</f>
-        <v>59124.842564700004</v>
+        <v>61871.732416550112</v>
       </c>
       <c r="AK3" s="8">
         <f>AJ3*1.05</f>
-        <v>62081.084692935008</v>
+        <v>64965.319037377623</v>
       </c>
       <c r="AL3" s="8">
         <f t="shared" ref="AL3:AO3" si="0">AK3*1.05</f>
-        <v>65185.138927581764</v>
+        <v>68213.584989246505</v>
       </c>
       <c r="AM3" s="8">
         <f t="shared" si="0"/>
-        <v>68444.39587396085</v>
+        <v>71624.264238708827</v>
       </c>
       <c r="AN3" s="8">
         <f t="shared" si="0"/>
-        <v>71866.615667658902</v>
+        <v>75205.477450644277</v>
       </c>
       <c r="AO3" s="8">
         <f t="shared" si="0"/>
-        <v>75459.946451041847</v>
+        <v>78965.75132317649</v>
       </c>
     </row>
     <row r="4" spans="2:41" x14ac:dyDescent="0.3">
@@ -1155,8 +1155,13 @@
       <c r="T4" s="5">
         <v>4366</v>
       </c>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
+      <c r="U4" s="5">
+        <v>4206</v>
+      </c>
+      <c r="V4" s="5">
+        <f>V6-V5</f>
+        <v>4155.1752999999999</v>
+      </c>
       <c r="Y4" s="5">
         <v>3863</v>
       </c>
@@ -1178,7 +1183,10 @@
         <f>SUM(O4:R4)</f>
         <v>12114</v>
       </c>
-      <c r="AE4" s="5"/>
+      <c r="AE4" s="5">
+        <f>SUM(S4:V4)</f>
+        <v>16178.175299999999</v>
+      </c>
       <c r="AF4" s="5"/>
       <c r="AG4" s="5"/>
       <c r="AH4" s="5"/>
@@ -1249,8 +1257,12 @@
       <c r="T5" s="5">
         <v>260</v>
       </c>
-      <c r="U5" s="5"/>
-      <c r="V5" s="5"/>
+      <c r="U5" s="5">
+        <v>260</v>
+      </c>
+      <c r="V5" s="5">
+        <v>270</v>
+      </c>
       <c r="Y5" s="5"/>
       <c r="Z5" s="5"/>
       <c r="AA5" s="5"/>
@@ -1266,7 +1278,10 @@
         <f>SUM(O5:R5)</f>
         <v>946</v>
       </c>
-      <c r="AE5" s="5"/>
+      <c r="AE5" s="5">
+        <f>SUM(S5:V5)</f>
+        <v>1041</v>
+      </c>
       <c r="AF5" s="5"/>
       <c r="AG5" s="5"/>
       <c r="AH5" s="5"/>
@@ -1283,7 +1298,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="5">
-        <f t="shared" ref="C6:T6" si="1">SUM(C4:C5)</f>
+        <f t="shared" ref="C6:U6" si="1">SUM(C4:C5)</f>
         <v>1858</v>
       </c>
       <c r="D6" s="5">
@@ -1355,12 +1370,12 @@
         <v>4626</v>
       </c>
       <c r="U6" s="5">
-        <f t="shared" ref="U6:V6" si="2">U3-U7</f>
-        <v>4089</v>
+        <f t="shared" si="1"/>
+        <v>4466</v>
       </c>
       <c r="V6" s="5">
-        <f t="shared" si="2"/>
-        <v>4403.3499999999995</v>
+        <f t="shared" ref="V6" si="2">V3-V7</f>
+        <v>4425.1752999999999</v>
       </c>
       <c r="Y6" s="5">
         <f t="shared" ref="Y6:AD6" si="3">SUM(Y4:Y5)</f>
@@ -1388,47 +1403,47 @@
       </c>
       <c r="AE6" s="5">
         <f>SUM(S6:V6)</f>
-        <v>16820.349999999999</v>
+        <v>17219.175299999999</v>
       </c>
       <c r="AF6" s="5">
         <f>AF3-AF7</f>
-        <v>18033.569999999996</v>
+        <v>18871.39431</v>
       </c>
       <c r="AG6" s="5">
         <f t="shared" ref="AG6:AO6" si="4">AG3-AG7</f>
-        <v>19816.8897</v>
+        <v>20737.565525100003</v>
       </c>
       <c r="AH6" s="5">
         <f t="shared" si="4"/>
-        <v>20784.691290000002</v>
+        <v>22280.826215340006</v>
       </c>
       <c r="AI6" s="5">
         <f t="shared" si="4"/>
-        <v>22102.744884</v>
+        <v>23707.860084846303</v>
       </c>
       <c r="AJ6" s="5">
         <f t="shared" si="4"/>
-        <v>23058.688600232999</v>
+        <v>24748.692966620045</v>
       </c>
       <c r="AK6" s="5">
         <f t="shared" si="4"/>
-        <v>23590.812183315305</v>
+        <v>25986.127614951052</v>
       </c>
       <c r="AL6" s="5">
         <f t="shared" si="4"/>
-        <v>24770.35279248107</v>
+        <v>27285.4339956986</v>
       </c>
       <c r="AM6" s="5">
         <f t="shared" si="4"/>
-        <v>26008.870432105126</v>
+        <v>28649.705695483535</v>
       </c>
       <c r="AN6" s="5">
         <f t="shared" si="4"/>
-        <v>27309.313953710385</v>
+        <v>30082.190980257714</v>
       </c>
       <c r="AO6" s="5">
         <f t="shared" si="4"/>
-        <v>28674.779651395904</v>
+        <v>31586.3005292706</v>
       </c>
     </row>
     <row r="7" spans="2:41" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1436,7 +1451,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="8">
-        <f t="shared" ref="C7:T7" si="5">C3-C6</f>
+        <f t="shared" ref="C7:U7" si="5">C3-C6</f>
         <v>1587</v>
       </c>
       <c r="D7" s="8">
@@ -1508,12 +1523,12 @@
         <v>3059</v>
       </c>
       <c r="U7" s="8">
-        <f>U3*0.53</f>
-        <v>4611</v>
+        <f t="shared" si="5"/>
+        <v>4780</v>
       </c>
       <c r="V7" s="8">
-        <f>V3*0.54</f>
-        <v>5169.1500000000005</v>
+        <f>V3*0.545</f>
+        <v>5300.4847</v>
       </c>
       <c r="Y7" s="8">
         <f t="shared" ref="Y7:AE7" si="6">Y3-Y6</f>
@@ -1541,47 +1556,47 @@
       </c>
       <c r="AE7" s="8">
         <f t="shared" si="6"/>
-        <v>16575.150000000001</v>
+        <v>16875.484700000005</v>
       </c>
       <c r="AF7" s="8">
         <f>AF3*0.55</f>
-        <v>22041.030000000002</v>
+        <v>23065.037490000006</v>
       </c>
       <c r="AG7" s="8">
         <f>AG3*0.57</f>
-        <v>26268.900299999994</v>
+        <v>27489.331044900002</v>
       </c>
       <c r="AH7" s="8">
-        <f>AH3*0.59</f>
-        <v>29909.677709999996</v>
+        <f>AH3*0.58</f>
+        <v>30768.760011660001</v>
       </c>
       <c r="AI7" s="8">
-        <f>AI3*0.6</f>
-        <v>33154.117326</v>
+        <f>AI3*0.59</f>
+        <v>34116.188902583708</v>
       </c>
       <c r="AJ7" s="8">
-        <f>AJ3*0.61</f>
-        <v>36066.153964467005</v>
+        <f>AJ3*0.6</f>
+        <v>37123.039449930067</v>
       </c>
       <c r="AK7" s="8">
-        <f>AK3*0.62</f>
-        <v>38490.272509619703</v>
+        <f t="shared" ref="AK7:AO7" si="7">AK3*0.6</f>
+        <v>38979.191422426571</v>
       </c>
       <c r="AL7" s="8">
-        <f t="shared" ref="AL7:AO7" si="7">AL3*0.62</f>
-        <v>40414.786135100694</v>
+        <f t="shared" si="7"/>
+        <v>40928.150993547904</v>
       </c>
       <c r="AM7" s="8">
         <f t="shared" si="7"/>
-        <v>42435.525441855723</v>
+        <v>42974.558543225292</v>
       </c>
       <c r="AN7" s="8">
         <f t="shared" si="7"/>
-        <v>44557.301713948516</v>
+        <v>45123.286470386563</v>
       </c>
       <c r="AO7" s="8">
         <f t="shared" si="7"/>
-        <v>46785.166799645944</v>
+        <v>47379.450793905889</v>
       </c>
     </row>
     <row r="8" spans="2:41" x14ac:dyDescent="0.3">
@@ -1644,12 +1659,11 @@
         <v>1894</v>
       </c>
       <c r="U8" s="5">
-        <f>Q8*1.22</f>
-        <v>1995.9199999999998</v>
+        <v>2139</v>
       </c>
       <c r="V8" s="5">
-        <f>R8*1.2</f>
-        <v>2054.4</v>
+        <f>R8*1.28</f>
+        <v>2191.36</v>
       </c>
       <c r="Y8" s="5">
         <v>1547</v>
@@ -1674,47 +1688,47 @@
       </c>
       <c r="AE8" s="5">
         <f>SUM(S8:V8)</f>
-        <v>7672.32</v>
+        <v>7952.3600000000006</v>
       </c>
       <c r="AF8" s="5">
-        <f>AE8*1.13</f>
-        <v>8669.7215999999989</v>
+        <f>AE8*1.14</f>
+        <v>9065.6903999999995</v>
       </c>
       <c r="AG8" s="5">
         <f>AF8*1.08</f>
-        <v>9363.2993279999992</v>
+        <v>9790.9456320000008</v>
       </c>
       <c r="AH8" s="5">
         <f>AG8*1.06</f>
-        <v>9925.0972876799988</v>
+        <v>10378.402369920001</v>
       </c>
       <c r="AI8" s="5">
         <f>AH8*1.04</f>
-        <v>10322.101179187199</v>
+        <v>10793.538464716801</v>
       </c>
       <c r="AJ8" s="5">
         <f>AI8*1.03</f>
-        <v>10631.764214562814</v>
+        <v>11117.344618658306</v>
       </c>
       <c r="AK8" s="5">
         <f t="shared" ref="AK8:AO8" si="8">AJ8*1.03</f>
-        <v>10950.717140999699</v>
+        <v>11450.864957218055</v>
       </c>
       <c r="AL8" s="5">
         <f t="shared" si="8"/>
-        <v>11279.23865522969</v>
+        <v>11794.390905934597</v>
       </c>
       <c r="AM8" s="5">
         <f t="shared" si="8"/>
-        <v>11617.615814886582</v>
+        <v>12148.222633112635</v>
       </c>
       <c r="AN8" s="5">
         <f t="shared" si="8"/>
-        <v>11966.144289333179</v>
+        <v>12512.669312106014</v>
       </c>
       <c r="AO8" s="5">
         <f t="shared" si="8"/>
-        <v>12325.128618013174</v>
+        <v>12888.049391469194</v>
       </c>
     </row>
     <row r="9" spans="2:41" x14ac:dyDescent="0.3">
@@ -1777,8 +1791,7 @@
         <v>991</v>
       </c>
       <c r="U9" s="5">
-        <f>Q9*1.45</f>
-        <v>1045.45</v>
+        <v>1069</v>
       </c>
       <c r="V9" s="5">
         <f>R9*1.4</f>
@@ -1807,47 +1820,47 @@
       </c>
       <c r="AE9" s="5">
         <f>SUM(S9:V9)</f>
-        <v>4031.25</v>
+        <v>4054.8</v>
       </c>
       <c r="AF9" s="5">
         <f>AE9*1.18</f>
-        <v>4756.875</v>
+        <v>4784.6639999999998</v>
       </c>
       <c r="AG9" s="5">
         <f>AF9*1.09</f>
-        <v>5184.9937500000005</v>
+        <v>5215.2837600000003</v>
       </c>
       <c r="AH9" s="5">
         <f>AG9*1.06</f>
-        <v>5496.0933750000013</v>
+        <v>5528.2007856000009</v>
       </c>
       <c r="AI9" s="5">
         <f>AH9*1.04</f>
-        <v>5715.9371100000017</v>
+        <v>5749.3288170240012</v>
       </c>
       <c r="AJ9" s="5">
         <f>AI9*1.04</f>
-        <v>5944.5745944000018</v>
+        <v>5979.3019697049613</v>
       </c>
       <c r="AK9" s="5">
         <f t="shared" ref="AK9:AO9" si="9">AJ9*1.04</f>
-        <v>6182.3575781760019</v>
+        <v>6218.4740484931599</v>
       </c>
       <c r="AL9" s="5">
         <f t="shared" si="9"/>
-        <v>6429.6518813030425</v>
+        <v>6467.2130104328862</v>
       </c>
       <c r="AM9" s="5">
         <f t="shared" si="9"/>
-        <v>6686.8379565551641</v>
+        <v>6725.9015308502021</v>
       </c>
       <c r="AN9" s="5">
         <f t="shared" si="9"/>
-        <v>6954.3114748173712</v>
+        <v>6994.9375920842103</v>
       </c>
       <c r="AO9" s="5">
         <f t="shared" si="9"/>
-        <v>7232.4839338100664</v>
+        <v>7274.735095767579</v>
       </c>
     </row>
     <row r="10" spans="2:41" x14ac:dyDescent="0.3">
@@ -1910,11 +1923,10 @@
         <v>308</v>
       </c>
       <c r="U10" s="5">
-        <f t="shared" ref="U10:V10" si="10">Q10*0.98</f>
-        <v>344.96</v>
+        <v>302</v>
       </c>
       <c r="V10" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="V10" si="10">R10*0.98</f>
         <v>325.36</v>
       </c>
       <c r="Y10" s="5"/>
@@ -1934,7 +1946,7 @@
       </c>
       <c r="AE10" s="5">
         <f>SUM(S10:V10)</f>
-        <v>1294.3200000000002</v>
+        <v>1251.3600000000001</v>
       </c>
       <c r="AF10" s="5"/>
       <c r="AG10" s="5"/>
@@ -2039,43 +2051,43 @@
       </c>
       <c r="AF11" s="5">
         <f t="shared" ref="AF11:AO11" si="11">-AF3*0.002</f>
-        <v>-80.149199999999993</v>
+        <v>-83.872863600000017</v>
       </c>
       <c r="AG11" s="5">
         <f t="shared" si="11"/>
-        <v>-92.171579999999992</v>
+        <v>-96.453793140000016</v>
       </c>
       <c r="AH11" s="5">
         <f t="shared" si="11"/>
-        <v>-101.388738</v>
+        <v>-106.09917245400001</v>
       </c>
       <c r="AI11" s="5">
         <f t="shared" si="11"/>
-        <v>-110.51372442</v>
+        <v>-115.64809797486002</v>
       </c>
       <c r="AJ11" s="5">
         <f t="shared" si="11"/>
-        <v>-118.24968512940001</v>
+        <v>-123.74346483310023</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" si="11"/>
-        <v>-124.16216938587002</v>
+        <v>-129.93063807475525</v>
       </c>
       <c r="AL11" s="5">
         <f t="shared" si="11"/>
-        <v>-130.37027785516352</v>
+        <v>-136.42716997849303</v>
       </c>
       <c r="AM11" s="5">
         <f t="shared" si="11"/>
-        <v>-136.88879174792172</v>
+        <v>-143.24852847741766</v>
       </c>
       <c r="AN11" s="5">
         <f t="shared" si="11"/>
-        <v>-143.73323133531781</v>
+        <v>-150.41095490128856</v>
       </c>
       <c r="AO11" s="5">
         <f t="shared" si="11"/>
-        <v>-150.91989290208369</v>
+        <v>-157.93150264635298</v>
       </c>
     </row>
     <row r="12" spans="2:41" x14ac:dyDescent="0.3">
@@ -2214,11 +2226,11 @@
       </c>
       <c r="U13" s="5">
         <f t="shared" si="13"/>
-        <v>3386.33</v>
+        <v>3510</v>
       </c>
       <c r="V13" s="5">
         <f t="shared" si="13"/>
-        <v>3488.56</v>
+        <v>3625.52</v>
       </c>
       <c r="Y13" s="5">
         <f t="shared" ref="Y13:AC13" si="14">SUM(Y8:Y11)</f>
@@ -2246,47 +2258,47 @@
       </c>
       <c r="AE13" s="5">
         <f t="shared" ref="AE13:AO13" si="15">SUM(AE8:AE12)</f>
-        <v>12997.89</v>
+        <v>13258.52</v>
       </c>
       <c r="AF13" s="5">
         <f t="shared" si="15"/>
-        <v>13346.447399999999</v>
+        <v>13766.481536400001</v>
       </c>
       <c r="AG13" s="5">
         <f t="shared" si="15"/>
-        <v>14456.121497999999</v>
+        <v>14909.77559886</v>
       </c>
       <c r="AH13" s="5">
         <f t="shared" si="15"/>
-        <v>15319.801924680001</v>
+        <v>15800.503983066003</v>
       </c>
       <c r="AI13" s="5">
         <f t="shared" si="15"/>
-        <v>15927.5245647672</v>
+        <v>16427.219183765941</v>
       </c>
       <c r="AJ13" s="5">
         <f t="shared" si="15"/>
-        <v>16458.089123833415</v>
+        <v>16972.903123530166</v>
       </c>
       <c r="AK13" s="5">
         <f t="shared" si="15"/>
-        <v>17008.912549789831</v>
+        <v>17539.408367636461</v>
       </c>
       <c r="AL13" s="5">
         <f t="shared" si="15"/>
-        <v>17578.52025867757</v>
+        <v>18125.176746388992</v>
       </c>
       <c r="AM13" s="5">
         <f t="shared" si="15"/>
-        <v>18167.564979693823</v>
+        <v>18730.875635485416</v>
       </c>
       <c r="AN13" s="5">
         <f t="shared" si="15"/>
-        <v>18776.722532815231</v>
+        <v>19357.195949288933</v>
       </c>
       <c r="AO13" s="5">
         <f t="shared" si="15"/>
-        <v>19406.692658921158</v>
+        <v>20004.85298459042</v>
       </c>
     </row>
     <row r="14" spans="2:41" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -2367,11 +2379,11 @@
       </c>
       <c r="U14" s="8">
         <f t="shared" si="17"/>
-        <v>1224.67</v>
+        <v>1270</v>
       </c>
       <c r="V14" s="8">
         <f t="shared" si="17"/>
-        <v>1680.5900000000006</v>
+        <v>1674.9647</v>
       </c>
       <c r="Y14" s="8">
         <f t="shared" ref="Y14:AD14" si="18">Y7-Y13</f>
@@ -2399,47 +2411,47 @@
       </c>
       <c r="AE14" s="8">
         <f t="shared" ref="AE14:AO14" si="19">AE7-AE13</f>
-        <v>3577.260000000002</v>
+        <v>3616.9647000000041</v>
       </c>
       <c r="AF14" s="8">
         <f t="shared" si="19"/>
-        <v>8694.5826000000034</v>
+        <v>9298.5559536000055</v>
       </c>
       <c r="AG14" s="8">
         <f t="shared" si="19"/>
-        <v>11812.778801999995</v>
+        <v>12579.555446040002</v>
       </c>
       <c r="AH14" s="8">
         <f t="shared" si="19"/>
-        <v>14589.875785319995</v>
+        <v>14968.256028593998</v>
       </c>
       <c r="AI14" s="8">
         <f t="shared" si="19"/>
-        <v>17226.592761232801</v>
+        <v>17688.969718817767</v>
       </c>
       <c r="AJ14" s="8">
         <f t="shared" si="19"/>
-        <v>19608.064840633589</v>
+        <v>20150.136326399901</v>
       </c>
       <c r="AK14" s="8">
         <f t="shared" si="19"/>
-        <v>21481.359959829872</v>
+        <v>21439.78305479011</v>
       </c>
       <c r="AL14" s="8">
         <f t="shared" si="19"/>
-        <v>22836.265876423124</v>
+        <v>22802.974247158912</v>
       </c>
       <c r="AM14" s="8">
         <f t="shared" si="19"/>
-        <v>24267.9604621619</v>
+        <v>24243.682907739876</v>
       </c>
       <c r="AN14" s="8">
         <f t="shared" si="19"/>
-        <v>25780.579181133286</v>
+        <v>25766.090521097631</v>
       </c>
       <c r="AO14" s="8">
         <f t="shared" si="19"/>
-        <v>27378.474140724786</v>
+        <v>27374.59780931547</v>
       </c>
     </row>
     <row r="15" spans="2:41" x14ac:dyDescent="0.3">
@@ -2502,7 +2514,7 @@
         <v>38</v>
       </c>
       <c r="U15" s="5">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="V15" s="5">
         <v>22</v>
@@ -2530,47 +2542,47 @@
       </c>
       <c r="AE15" s="5">
         <f>SUM(S15:V15)</f>
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="AF15" s="5">
         <f t="shared" ref="AF15:AO15" si="20">AE15*1.02</f>
-        <v>104.04</v>
+        <v>119.34</v>
       </c>
       <c r="AG15" s="5">
         <f t="shared" si="20"/>
-        <v>106.1208</v>
+        <v>121.72680000000001</v>
       </c>
       <c r="AH15" s="5">
         <f t="shared" si="20"/>
-        <v>108.243216</v>
+        <v>124.16133600000002</v>
       </c>
       <c r="AI15" s="5">
         <f t="shared" si="20"/>
-        <v>110.40808032000001</v>
+        <v>126.64456272000002</v>
       </c>
       <c r="AJ15" s="5">
         <f t="shared" si="20"/>
-        <v>112.61624192640001</v>
+        <v>129.17745397440004</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="20"/>
-        <v>114.868566764928</v>
+        <v>131.76100305388803</v>
       </c>
       <c r="AL15" s="5">
         <f t="shared" si="20"/>
-        <v>117.16593810022657</v>
+        <v>134.39622311496581</v>
       </c>
       <c r="AM15" s="5">
         <f t="shared" si="20"/>
-        <v>119.5092568622311</v>
+        <v>137.08414757726513</v>
       </c>
       <c r="AN15" s="5">
         <f t="shared" si="20"/>
-        <v>121.89944199947573</v>
+        <v>139.82583052881043</v>
       </c>
       <c r="AO15" s="5">
         <f t="shared" si="20"/>
-        <v>124.33743083946524</v>
+        <v>142.62234713938665</v>
       </c>
     </row>
     <row r="16" spans="2:41" x14ac:dyDescent="0.3">
@@ -2633,7 +2645,7 @@
         <v>-98</v>
       </c>
       <c r="U16" s="5">
-        <v>-45</v>
+        <v>-82</v>
       </c>
       <c r="V16" s="5">
         <v>-45</v>
@@ -2661,47 +2673,47 @@
       </c>
       <c r="AE16" s="5">
         <f>SUM(S16:V16)</f>
-        <v>-227</v>
+        <v>-264</v>
       </c>
       <c r="AF16" s="5">
         <f t="shared" ref="AF16:AO16" si="21">AE16*1.01</f>
-        <v>-229.27</v>
+        <v>-266.64</v>
       </c>
       <c r="AG16" s="5">
         <f t="shared" si="21"/>
-        <v>-231.56270000000001</v>
+        <v>-269.3064</v>
       </c>
       <c r="AH16" s="5">
         <f t="shared" si="21"/>
-        <v>-233.87832700000001</v>
+        <v>-271.99946399999999</v>
       </c>
       <c r="AI16" s="5">
         <f t="shared" si="21"/>
-        <v>-236.21711027000001</v>
+        <v>-274.71945863999997</v>
       </c>
       <c r="AJ16" s="5">
         <f t="shared" si="21"/>
-        <v>-238.5792813727</v>
+        <v>-277.46665322639996</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="21"/>
-        <v>-240.96507418642699</v>
+        <v>-280.24131975866396</v>
       </c>
       <c r="AL16" s="5">
         <f t="shared" si="21"/>
-        <v>-243.37472492829127</v>
+        <v>-283.04373295625061</v>
       </c>
       <c r="AM16" s="5">
         <f t="shared" si="21"/>
-        <v>-245.80847217757417</v>
+        <v>-285.87417028581314</v>
       </c>
       <c r="AN16" s="5">
         <f t="shared" si="21"/>
-        <v>-248.26655689934992</v>
+        <v>-288.73291198867128</v>
       </c>
       <c r="AO16" s="5">
         <f t="shared" si="21"/>
-        <v>-250.74922246834342</v>
+        <v>-291.62024110855799</v>
       </c>
     </row>
     <row r="17" spans="2:142" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -2782,11 +2794,11 @@
       </c>
       <c r="U17" s="8">
         <f t="shared" si="22"/>
-        <v>1247.67</v>
+        <v>1315</v>
       </c>
       <c r="V17" s="8">
         <f t="shared" si="22"/>
-        <v>1703.5900000000006</v>
+        <v>1697.9647</v>
       </c>
       <c r="Y17" s="8">
         <f t="shared" ref="Y17:AD17" si="23">Y14-SUM(Y15:Y16)</f>
@@ -2814,47 +2826,47 @@
       </c>
       <c r="AE17" s="8">
         <f t="shared" ref="AE17:AO17" si="24">AE14-SUM(AE15:AE16)</f>
-        <v>3702.260000000002</v>
+        <v>3763.9647000000041</v>
       </c>
       <c r="AF17" s="8">
         <f t="shared" si="24"/>
-        <v>8819.8126000000029</v>
+        <v>9445.8559536000048</v>
       </c>
       <c r="AG17" s="8">
         <f t="shared" si="24"/>
-        <v>11938.220701999995</v>
+        <v>12727.135046040001</v>
       </c>
       <c r="AH17" s="8">
         <f t="shared" si="24"/>
-        <v>14715.510896319995</v>
+        <v>15116.094156593997</v>
       </c>
       <c r="AI17" s="8">
         <f t="shared" si="24"/>
-        <v>17352.401791182801</v>
+        <v>17837.044614737766</v>
       </c>
       <c r="AJ17" s="8">
         <f t="shared" si="24"/>
-        <v>19734.027880079888</v>
+        <v>20298.425525651903</v>
       </c>
       <c r="AK17" s="8">
         <f t="shared" si="24"/>
-        <v>21607.45646725137</v>
+        <v>21588.263371494886</v>
       </c>
       <c r="AL17" s="8">
         <f t="shared" si="24"/>
-        <v>22962.474663251189</v>
+        <v>22951.621757000197</v>
       </c>
       <c r="AM17" s="8">
         <f t="shared" si="24"/>
-        <v>24394.259677477243</v>
+        <v>24392.472930448424</v>
       </c>
       <c r="AN17" s="8">
         <f t="shared" si="24"/>
-        <v>25906.946296033158</v>
+        <v>25914.997602557491</v>
       </c>
       <c r="AO17" s="8">
         <f t="shared" si="24"/>
-        <v>27504.885932353664</v>
+        <v>27523.595703284642</v>
       </c>
     </row>
     <row r="18" spans="2:142" x14ac:dyDescent="0.3">
@@ -2917,12 +2929,11 @@
         <v>-834</v>
       </c>
       <c r="U18" s="5">
-        <f t="shared" ref="U18:V18" si="25">U17*0.18</f>
-        <v>224.5806</v>
+        <v>153</v>
       </c>
       <c r="V18" s="5">
-        <f t="shared" si="25"/>
-        <v>306.64620000000008</v>
+        <f t="shared" ref="V18" si="25">V17*0.18</f>
+        <v>305.633646</v>
       </c>
       <c r="Y18" s="5">
         <v>31</v>
@@ -2947,47 +2958,47 @@
       </c>
       <c r="AE18" s="5">
         <f>SUM(S18:V18)</f>
-        <v>-179.77319999999992</v>
+        <v>-252.366354</v>
       </c>
       <c r="AF18" s="5">
         <f t="shared" ref="AF18:AO18" si="26">AF17*0.12</f>
-        <v>1058.3775120000003</v>
+        <v>1133.5027144320006</v>
       </c>
       <c r="AG18" s="5">
         <f t="shared" si="26"/>
-        <v>1432.5864842399994</v>
+        <v>1527.2562055248</v>
       </c>
       <c r="AH18" s="5">
         <f t="shared" si="26"/>
-        <v>1765.8613075583992</v>
+        <v>1813.9312987912797</v>
       </c>
       <c r="AI18" s="5">
         <f t="shared" si="26"/>
-        <v>2082.2882149419361</v>
+        <v>2140.4453537685317</v>
       </c>
       <c r="AJ18" s="5">
         <f t="shared" si="26"/>
-        <v>2368.0833456095866</v>
+        <v>2435.811063078228</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="26"/>
-        <v>2592.8947760701644</v>
+        <v>2590.5916045793861</v>
       </c>
       <c r="AL18" s="5">
         <f t="shared" si="26"/>
-        <v>2755.4969595901425</v>
+        <v>2754.1946108400234</v>
       </c>
       <c r="AM18" s="5">
         <f t="shared" si="26"/>
-        <v>2927.3111612972689</v>
+        <v>2927.0967516538108</v>
       </c>
       <c r="AN18" s="5">
         <f t="shared" si="26"/>
-        <v>3108.8335555239787</v>
+        <v>3109.799712306899</v>
       </c>
       <c r="AO18" s="5">
         <f t="shared" si="26"/>
-        <v>3300.5863118824395</v>
+        <v>3302.8314843941571</v>
       </c>
     </row>
     <row r="19" spans="2:142" x14ac:dyDescent="0.3">
@@ -3050,12 +3061,11 @@
         <v>-8</v>
       </c>
       <c r="U19" s="5">
-        <f t="shared" ref="U19:V19" si="27">-U17*0.01</f>
-        <v>-12.476700000000001</v>
+        <v>-10</v>
       </c>
       <c r="V19" s="5">
-        <f t="shared" si="27"/>
-        <v>-17.035900000000005</v>
+        <f t="shared" ref="V19" si="27">-V17*0.01</f>
+        <v>-16.979647</v>
       </c>
       <c r="Y19" s="5">
         <v>0</v>
@@ -3080,47 +3090,47 @@
       </c>
       <c r="AE19" s="5">
         <f>SUM(S19:V19)</f>
-        <v>-44.512600000000006</v>
+        <v>-41.979647</v>
       </c>
       <c r="AF19" s="5">
         <f>-AF17*0.01</f>
-        <v>-88.19812600000003</v>
+        <v>-94.458559536000053</v>
       </c>
       <c r="AG19" s="5">
         <f t="shared" ref="AG19:AO19" si="28">-AG17*0.01</f>
-        <v>-119.38220701999995</v>
+        <v>-127.27135046040001</v>
       </c>
       <c r="AH19" s="5">
         <f t="shared" si="28"/>
-        <v>-147.15510896319995</v>
+        <v>-151.16094156593996</v>
       </c>
       <c r="AI19" s="5">
         <f t="shared" si="28"/>
-        <v>-173.52401791182803</v>
+        <v>-178.37044614737766</v>
       </c>
       <c r="AJ19" s="5">
         <f t="shared" si="28"/>
-        <v>-197.34027880079887</v>
+        <v>-202.98425525651902</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="28"/>
-        <v>-216.0745646725137</v>
+        <v>-215.88263371494887</v>
       </c>
       <c r="AL19" s="5">
         <f t="shared" si="28"/>
-        <v>-229.62474663251189</v>
+        <v>-229.51621757000197</v>
       </c>
       <c r="AM19" s="5">
         <f t="shared" si="28"/>
-        <v>-243.94259677477243</v>
+        <v>-243.92472930448426</v>
       </c>
       <c r="AN19" s="5">
         <f t="shared" si="28"/>
-        <v>-259.06946296033158</v>
+        <v>-259.14997602557492</v>
       </c>
       <c r="AO19" s="5">
         <f t="shared" si="28"/>
-        <v>-275.04885932353665</v>
+        <v>-275.23595703284644</v>
       </c>
     </row>
     <row r="20" spans="2:142" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -3201,11 +3211,11 @@
       </c>
       <c r="U20" s="8">
         <f t="shared" si="30"/>
-        <v>1035.5661</v>
+        <v>1172</v>
       </c>
       <c r="V20" s="8">
         <f t="shared" si="30"/>
-        <v>1413.9797000000005</v>
+        <v>1409.3107009999999</v>
       </c>
       <c r="Y20" s="8">
         <f t="shared" ref="Y20:AD20" si="31">Y17-Y18-Y19</f>
@@ -3233,451 +3243,451 @@
       </c>
       <c r="AE20" s="8">
         <f t="shared" ref="AE20:AO20" si="32">AE17-AE18-AE19</f>
-        <v>3926.5458000000021</v>
+        <v>4058.310701000004</v>
       </c>
       <c r="AF20" s="8">
         <f t="shared" si="32"/>
-        <v>7849.6332140000031</v>
+        <v>8406.8117987040041</v>
       </c>
       <c r="AG20" s="8">
         <f t="shared" si="32"/>
-        <v>10625.016424779997</v>
+        <v>11327.150190975601</v>
       </c>
       <c r="AH20" s="8">
         <f t="shared" si="32"/>
-        <v>13096.804697724794</v>
+        <v>13453.323799368658</v>
       </c>
       <c r="AI20" s="8">
         <f t="shared" si="32"/>
-        <v>15443.637594152693</v>
+        <v>15874.969707116612</v>
       </c>
       <c r="AJ20" s="8">
         <f t="shared" si="32"/>
-        <v>17563.284813271101</v>
+        <v>18065.598717830195</v>
       </c>
       <c r="AK20" s="8">
         <f t="shared" si="32"/>
-        <v>19230.636255853722</v>
+        <v>19213.554400630448</v>
       </c>
       <c r="AL20" s="8">
         <f t="shared" si="32"/>
-        <v>20436.602450293558</v>
+        <v>20426.943363730177</v>
       </c>
       <c r="AM20" s="8">
         <f t="shared" si="32"/>
-        <v>21710.891112954749</v>
+        <v>21709.300908099096</v>
       </c>
       <c r="AN20" s="8">
         <f t="shared" si="32"/>
-        <v>23057.182203469511</v>
+        <v>23064.347866276166</v>
       </c>
       <c r="AO20" s="8">
         <f t="shared" si="32"/>
-        <v>24479.34847979476</v>
+        <v>24496.000175923335</v>
       </c>
       <c r="AP20" s="3">
         <f>AO20*(1+$AR$25)</f>
-        <v>24234.554994996812</v>
+        <v>24251.0401741641</v>
       </c>
       <c r="AQ20" s="3">
         <f t="shared" ref="AQ20:DB20" si="33">AP20*(1+$AR$25)</f>
-        <v>23992.209445046843</v>
+        <v>24008.529772422458</v>
       </c>
       <c r="AR20" s="3">
         <f t="shared" si="33"/>
-        <v>23752.287350596376</v>
+        <v>23768.444474698234</v>
       </c>
       <c r="AS20" s="3">
         <f t="shared" si="33"/>
-        <v>23514.764477090412</v>
+        <v>23530.760029951252</v>
       </c>
       <c r="AT20" s="3">
         <f t="shared" si="33"/>
-        <v>23279.616832319509</v>
+        <v>23295.452429651741</v>
       </c>
       <c r="AU20" s="3">
         <f t="shared" si="33"/>
-        <v>23046.820663996314</v>
+        <v>23062.497905355223</v>
       </c>
       <c r="AV20" s="3">
         <f t="shared" si="33"/>
-        <v>22816.352457356352</v>
+        <v>22831.872926301672</v>
       </c>
       <c r="AW20" s="3">
         <f t="shared" si="33"/>
-        <v>22588.188932782788</v>
+        <v>22603.554197038655</v>
       </c>
       <c r="AX20" s="3">
         <f t="shared" si="33"/>
-        <v>22362.307043454959</v>
+        <v>22377.518655068267</v>
       </c>
       <c r="AY20" s="3">
         <f t="shared" si="33"/>
-        <v>22138.683973020408</v>
+        <v>22153.743468517583</v>
       </c>
       <c r="AZ20" s="3">
         <f t="shared" si="33"/>
-        <v>21917.297133290205</v>
+        <v>21932.206033832408</v>
       </c>
       <c r="BA20" s="3">
         <f t="shared" si="33"/>
-        <v>21698.124161957305</v>
+        <v>21712.883973494085</v>
       </c>
       <c r="BB20" s="3">
         <f t="shared" si="33"/>
-        <v>21481.14292033773</v>
+        <v>21495.755133759143</v>
       </c>
       <c r="BC20" s="3">
         <f t="shared" si="33"/>
-        <v>21266.331491134351</v>
+        <v>21280.79758242155</v>
       </c>
       <c r="BD20" s="3">
         <f t="shared" si="33"/>
-        <v>21053.668176223007</v>
+        <v>21067.989606597333</v>
       </c>
       <c r="BE20" s="3">
         <f t="shared" si="33"/>
-        <v>20843.131494460777</v>
+        <v>20857.309710531361</v>
       </c>
       <c r="BF20" s="3">
         <f t="shared" si="33"/>
-        <v>20634.700179516167</v>
+        <v>20648.736613426048</v>
       </c>
       <c r="BG20" s="3">
         <f t="shared" si="33"/>
-        <v>20428.353177721005</v>
+        <v>20442.249247291787</v>
       </c>
       <c r="BH20" s="3">
         <f t="shared" si="33"/>
-        <v>20224.069645943793</v>
+        <v>20237.826754818871</v>
       </c>
       <c r="BI20" s="3">
         <f t="shared" si="33"/>
-        <v>20021.828949484356</v>
+        <v>20035.448487270682</v>
       </c>
       <c r="BJ20" s="3">
         <f t="shared" si="33"/>
-        <v>19821.61065998951</v>
+        <v>19835.094002397975</v>
       </c>
       <c r="BK20" s="3">
         <f t="shared" si="33"/>
-        <v>19623.394553389615</v>
+        <v>19636.743062373997</v>
       </c>
       <c r="BL20" s="3">
         <f t="shared" si="33"/>
-        <v>19427.16060785572</v>
+        <v>19440.375631750256</v>
       </c>
       <c r="BM20" s="3">
         <f t="shared" si="33"/>
-        <v>19232.889001777163</v>
+        <v>19245.971875432751</v>
       </c>
       <c r="BN20" s="3">
         <f t="shared" si="33"/>
-        <v>19040.560111759391</v>
+        <v>19053.512156678426</v>
       </c>
       <c r="BO20" s="3">
         <f t="shared" si="33"/>
-        <v>18850.154510641798</v>
+        <v>18862.977035111642</v>
       </c>
       <c r="BP20" s="3">
         <f t="shared" si="33"/>
-        <v>18661.652965535381</v>
+        <v>18674.347264760527</v>
       </c>
       <c r="BQ20" s="3">
         <f t="shared" si="33"/>
-        <v>18475.036435880025</v>
+        <v>18487.603792112921</v>
       </c>
       <c r="BR20" s="3">
         <f t="shared" si="33"/>
-        <v>18290.286071521226</v>
+        <v>18302.72775419179</v>
       </c>
       <c r="BS20" s="3">
         <f t="shared" si="33"/>
-        <v>18107.383210806012</v>
+        <v>18119.700476649872</v>
       </c>
       <c r="BT20" s="3">
         <f t="shared" si="33"/>
-        <v>17926.309378697952</v>
+        <v>17938.503471883374</v>
       </c>
       <c r="BU20" s="3">
         <f t="shared" si="33"/>
-        <v>17747.046284910972</v>
+        <v>17759.11843716454</v>
       </c>
       <c r="BV20" s="3">
         <f t="shared" si="33"/>
-        <v>17569.575822061863</v>
+        <v>17581.527252792894</v>
       </c>
       <c r="BW20" s="3">
         <f t="shared" si="33"/>
-        <v>17393.880063841243</v>
+        <v>17405.711980264965</v>
       </c>
       <c r="BX20" s="3">
         <f t="shared" si="33"/>
-        <v>17219.941263202829</v>
+        <v>17231.654860462317</v>
       </c>
       <c r="BY20" s="3">
         <f t="shared" si="33"/>
-        <v>17047.741850570801</v>
+        <v>17059.338311857693</v>
       </c>
       <c r="BZ20" s="3">
         <f t="shared" si="33"/>
-        <v>16877.264432065094</v>
+        <v>16888.744928739117</v>
       </c>
       <c r="CA20" s="3">
         <f t="shared" si="33"/>
-        <v>16708.491787744442</v>
+        <v>16719.857479451726</v>
       </c>
       <c r="CB20" s="3">
         <f t="shared" si="33"/>
-        <v>16541.406869866998</v>
+        <v>16552.658904657208</v>
       </c>
       <c r="CC20" s="3">
         <f t="shared" si="33"/>
-        <v>16375.992801168328</v>
+        <v>16387.132315610637</v>
       </c>
       <c r="CD20" s="3">
         <f t="shared" si="33"/>
-        <v>16212.232873156645</v>
+        <v>16223.26099245453</v>
       </c>
       <c r="CE20" s="3">
         <f t="shared" si="33"/>
-        <v>16050.110544425079</v>
+        <v>16061.028382529985</v>
       </c>
       <c r="CF20" s="3">
         <f t="shared" si="33"/>
-        <v>15889.609438980828</v>
+        <v>15900.418098704686</v>
       </c>
       <c r="CG20" s="3">
         <f t="shared" si="33"/>
-        <v>15730.713344591019</v>
+        <v>15741.413917717638</v>
       </c>
       <c r="CH20" s="3">
         <f t="shared" si="33"/>
-        <v>15573.406211145108</v>
+        <v>15583.999778540461</v>
       </c>
       <c r="CI20" s="3">
         <f t="shared" si="33"/>
-        <v>15417.672149033657</v>
+        <v>15428.159780755057</v>
       </c>
       <c r="CJ20" s="3">
         <f t="shared" si="33"/>
-        <v>15263.495427543319</v>
+        <v>15273.878182947507</v>
       </c>
       <c r="CK20" s="3">
         <f t="shared" si="33"/>
-        <v>15110.860473267885</v>
+        <v>15121.139401118031</v>
       </c>
       <c r="CL20" s="3">
         <f t="shared" si="33"/>
-        <v>14959.751868535206</v>
+        <v>14969.92800710685</v>
       </c>
       <c r="CM20" s="3">
         <f t="shared" si="33"/>
-        <v>14810.154349849854</v>
+        <v>14820.228727035781</v>
       </c>
       <c r="CN20" s="3">
         <f t="shared" si="33"/>
-        <v>14662.052806351356</v>
+        <v>14672.026439765423</v>
       </c>
       <c r="CO20" s="3">
         <f t="shared" si="33"/>
-        <v>14515.432278287843</v>
+        <v>14525.306175367768</v>
       </c>
       <c r="CP20" s="3">
         <f t="shared" si="33"/>
-        <v>14370.277955504964</v>
+        <v>14380.053113614091</v>
       </c>
       <c r="CQ20" s="3">
         <f t="shared" si="33"/>
-        <v>14226.575175949914</v>
+        <v>14236.25258247795</v>
       </c>
       <c r="CR20" s="3">
         <f t="shared" si="33"/>
-        <v>14084.309424190415</v>
+        <v>14093.89005665317</v>
       </c>
       <c r="CS20" s="3">
         <f t="shared" si="33"/>
-        <v>13943.466329948511</v>
+        <v>13952.951156086638</v>
       </c>
       <c r="CT20" s="3">
         <f t="shared" si="33"/>
-        <v>13804.031666649025</v>
+        <v>13813.421644525772</v>
       </c>
       <c r="CU20" s="3">
         <f t="shared" si="33"/>
-        <v>13665.991349982534</v>
+        <v>13675.287428080514</v>
       </c>
       <c r="CV20" s="3">
         <f t="shared" si="33"/>
-        <v>13529.331436482709</v>
+        <v>13538.534553799709</v>
       </c>
       <c r="CW20" s="3">
         <f t="shared" si="33"/>
-        <v>13394.038122117881</v>
+        <v>13403.149208261711</v>
       </c>
       <c r="CX20" s="3">
         <f t="shared" si="33"/>
-        <v>13260.097740896703</v>
+        <v>13269.117716179095</v>
       </c>
       <c r="CY20" s="3">
         <f t="shared" si="33"/>
-        <v>13127.496763487736</v>
+        <v>13136.426539017304</v>
       </c>
       <c r="CZ20" s="3">
         <f t="shared" si="33"/>
-        <v>12996.221795852858</v>
+        <v>13005.062273627131</v>
       </c>
       <c r="DA20" s="3">
         <f t="shared" si="33"/>
-        <v>12866.259577894329</v>
+        <v>12875.01165089086</v>
       </c>
       <c r="DB20" s="3">
         <f t="shared" si="33"/>
-        <v>12737.596982115385</v>
+        <v>12746.261534381951</v>
       </c>
       <c r="DC20" s="3">
         <f t="shared" ref="DC20:EL20" si="34">DB20*(1+$AR$25)</f>
-        <v>12610.221012294231</v>
+        <v>12618.79891903813</v>
       </c>
       <c r="DD20" s="3">
         <f t="shared" si="34"/>
-        <v>12484.118802171288</v>
+        <v>12492.61092984775</v>
       </c>
       <c r="DE20" s="3">
         <f t="shared" si="34"/>
-        <v>12359.277614149574</v>
+        <v>12367.684820549272</v>
       </c>
       <c r="DF20" s="3">
         <f t="shared" si="34"/>
-        <v>12235.684838008079</v>
+        <v>12244.007972343779</v>
       </c>
       <c r="DG20" s="3">
         <f t="shared" si="34"/>
-        <v>12113.327989627998</v>
+        <v>12121.567892620342</v>
       </c>
       <c r="DH20" s="3">
         <f t="shared" si="34"/>
-        <v>11992.194709731719</v>
+        <v>12000.352213694137</v>
       </c>
       <c r="DI20" s="3">
         <f t="shared" si="34"/>
-        <v>11872.272762634402</v>
+        <v>11880.348691557196</v>
       </c>
       <c r="DJ20" s="3">
         <f t="shared" si="34"/>
-        <v>11753.550035008058</v>
+        <v>11761.545204641623</v>
       </c>
       <c r="DK20" s="3">
         <f t="shared" si="34"/>
-        <v>11636.014534657977</v>
+        <v>11643.929752595206</v>
       </c>
       <c r="DL20" s="3">
         <f t="shared" si="34"/>
-        <v>11519.654389311398</v>
+        <v>11527.490455069254</v>
       </c>
       <c r="DM20" s="3">
         <f t="shared" si="34"/>
-        <v>11404.457845418283</v>
+        <v>11412.21555051856</v>
       </c>
       <c r="DN20" s="3">
         <f t="shared" si="34"/>
-        <v>11290.4132669641</v>
+        <v>11298.093395013375</v>
       </c>
       <c r="DO20" s="3">
         <f t="shared" si="34"/>
-        <v>11177.50913429446</v>
+        <v>11185.112461063241</v>
       </c>
       <c r="DP20" s="3">
         <f t="shared" si="34"/>
-        <v>11065.734042951515</v>
+        <v>11073.26133645261</v>
       </c>
       <c r="DQ20" s="3">
         <f t="shared" si="34"/>
-        <v>10955.076702521999</v>
+        <v>10962.528723088084</v>
       </c>
       <c r="DR20" s="3">
         <f t="shared" si="34"/>
-        <v>10845.525935496778</v>
+        <v>10852.903435857203</v>
       </c>
       <c r="DS20" s="3">
         <f t="shared" si="34"/>
-        <v>10737.070676141811</v>
+        <v>10744.37440149863</v>
       </c>
       <c r="DT20" s="3">
         <f t="shared" si="34"/>
-        <v>10629.699969380394</v>
+        <v>10636.930657483643</v>
       </c>
       <c r="DU20" s="3">
         <f t="shared" si="34"/>
-        <v>10523.402969686589</v>
+        <v>10530.561350908807</v>
       </c>
       <c r="DV20" s="3">
         <f t="shared" si="34"/>
-        <v>10418.168939989722</v>
+        <v>10425.255737399719</v>
       </c>
       <c r="DW20" s="3">
         <f t="shared" si="34"/>
-        <v>10313.987250589826</v>
+        <v>10321.003180025722</v>
       </c>
       <c r="DX20" s="3">
         <f t="shared" si="34"/>
-        <v>10210.847378083927</v>
+        <v>10217.793148225464</v>
       </c>
       <c r="DY20" s="3">
         <f t="shared" si="34"/>
-        <v>10108.738904303087</v>
+        <v>10115.61521674321</v>
       </c>
       <c r="DZ20" s="3">
         <f t="shared" si="34"/>
-        <v>10007.651515260057</v>
+        <v>10014.459064575778</v>
       </c>
       <c r="EA20" s="3">
         <f t="shared" si="34"/>
-        <v>9907.5750001074557</v>
+        <v>9914.3144739300205</v>
       </c>
       <c r="EB20" s="3">
         <f t="shared" si="34"/>
-        <v>9808.4992501063807</v>
+        <v>9815.1713291907199</v>
       </c>
       <c r="EC20" s="3">
         <f t="shared" si="34"/>
-        <v>9710.4142576053164</v>
+        <v>9717.0196158988128</v>
       </c>
       <c r="ED20" s="3">
         <f t="shared" si="34"/>
-        <v>9613.3101150292623</v>
+        <v>9619.849419739825</v>
       </c>
       <c r="EE20" s="3">
         <f t="shared" si="34"/>
-        <v>9517.1770138789689</v>
+        <v>9523.6509255424262</v>
       </c>
       <c r="EF20" s="3">
         <f t="shared" si="34"/>
-        <v>9422.0052437401791</v>
+        <v>9428.4144162870016</v>
       </c>
       <c r="EG20" s="3">
         <f t="shared" si="34"/>
-        <v>9327.7851913027771</v>
+        <v>9334.1302721241318</v>
       </c>
       <c r="EH20" s="3">
         <f t="shared" si="34"/>
-        <v>9234.5073393897492</v>
+        <v>9240.7889694028909</v>
       </c>
       <c r="EI20" s="3">
         <f t="shared" si="34"/>
-        <v>9142.1622659958521</v>
+        <v>9148.3810797088627</v>
       </c>
       <c r="EJ20" s="3">
         <f t="shared" si="34"/>
-        <v>9050.7406433358938</v>
+        <v>9056.8972689117745</v>
       </c>
       <c r="EK20" s="3">
         <f t="shared" si="34"/>
-        <v>8960.2332369025353</v>
+        <v>8966.3282962226567</v>
       </c>
       <c r="EL20" s="3">
         <f t="shared" si="34"/>
-        <v>8870.6309045335092</v>
+        <v>8876.66501326043</v>
       </c>
     </row>
     <row r="21" spans="2:142" x14ac:dyDescent="0.3">
@@ -3742,12 +3752,12 @@
         <v>1623</v>
       </c>
       <c r="U21" s="5">
-        <f>1623</f>
-        <v>1623</v>
+        <f>1626</f>
+        <v>1626</v>
       </c>
       <c r="V21" s="5">
-        <f>1623</f>
-        <v>1623</v>
+        <f>1626</f>
+        <v>1626</v>
       </c>
       <c r="Y21" s="5">
         <v>1622.8</v>
@@ -3769,48 +3779,48 @@
         <v>1620.5</v>
       </c>
       <c r="AE21" s="5">
-        <f>1623</f>
-        <v>1623</v>
+        <f>1626</f>
+        <v>1626</v>
       </c>
       <c r="AF21" s="5">
-        <f>1623</f>
-        <v>1623</v>
+        <f>1626</f>
+        <v>1626</v>
       </c>
       <c r="AG21" s="5">
-        <f>1623</f>
-        <v>1623</v>
+        <f>1626</f>
+        <v>1626</v>
       </c>
       <c r="AH21" s="5">
-        <f>1623</f>
-        <v>1623</v>
+        <f>1626</f>
+        <v>1626</v>
       </c>
       <c r="AI21" s="5">
-        <f>1623</f>
-        <v>1623</v>
+        <f>1626</f>
+        <v>1626</v>
       </c>
       <c r="AJ21" s="5">
-        <f>1623</f>
-        <v>1623</v>
+        <f>1626</f>
+        <v>1626</v>
       </c>
       <c r="AK21" s="5">
-        <f>1623</f>
-        <v>1623</v>
+        <f>1626</f>
+        <v>1626</v>
       </c>
       <c r="AL21" s="5">
-        <f>1623</f>
-        <v>1623</v>
+        <f>1626</f>
+        <v>1626</v>
       </c>
       <c r="AM21" s="5">
-        <f>1623</f>
-        <v>1623</v>
+        <f>1626</f>
+        <v>1626</v>
       </c>
       <c r="AN21" s="5">
-        <f>1623</f>
-        <v>1623</v>
+        <f>1626</f>
+        <v>1626</v>
       </c>
       <c r="AO21" s="5">
-        <f>1623</f>
-        <v>1623</v>
+        <f>1626</f>
+        <v>1626</v>
       </c>
     </row>
     <row r="22" spans="2:142" x14ac:dyDescent="0.3">
@@ -3891,11 +3901,11 @@
       </c>
       <c r="U22" s="7">
         <f t="shared" si="37"/>
-        <v>0.63805674676524959</v>
+        <v>0.72078720787207873</v>
       </c>
       <c r="V22" s="7">
         <f t="shared" si="37"/>
-        <v>0.87121361675908848</v>
+        <v>0.86673474846248455</v>
       </c>
       <c r="Y22" s="7">
         <f t="shared" ref="Y22:AD22" si="38">Y20/Y21</f>
@@ -3923,47 +3933,47 @@
       </c>
       <c r="AE22" s="7">
         <f t="shared" ref="AE22:AO22" si="39">AE20/AE21</f>
-        <v>2.4193134935305003</v>
+        <v>2.4958860399754021</v>
       </c>
       <c r="AF22" s="7">
         <f t="shared" si="39"/>
-        <v>4.8364961269254483</v>
+        <v>5.1702409586125491</v>
       </c>
       <c r="AG22" s="7">
         <f t="shared" si="39"/>
-        <v>6.546528912372148</v>
+        <v>6.9662670301202958</v>
       </c>
       <c r="AH22" s="7">
         <f t="shared" si="39"/>
-        <v>8.0695038186844084</v>
+        <v>8.2738768753804788</v>
       </c>
       <c r="AI22" s="7">
         <f t="shared" si="39"/>
-        <v>9.5154883512955593</v>
+        <v>9.7632040019167352</v>
       </c>
       <c r="AJ22" s="7">
         <f t="shared" si="39"/>
-        <v>10.821494031590326</v>
+        <v>11.110454316008729</v>
       </c>
       <c r="AK22" s="7">
         <f t="shared" si="39"/>
-        <v>11.848820860045423</v>
+        <v>11.816454120928935</v>
       </c>
       <c r="AL22" s="7">
         <f t="shared" si="39"/>
-        <v>12.591868422854935</v>
+        <v>12.562695795652015</v>
       </c>
       <c r="AM22" s="7">
         <f t="shared" si="39"/>
-        <v>13.377012392455175</v>
+        <v>13.351353572016665</v>
       </c>
       <c r="AN22" s="7">
         <f t="shared" si="39"/>
-        <v>14.206520150012022</v>
+        <v>14.184715784917691</v>
       </c>
       <c r="AO22" s="7">
         <f t="shared" si="39"/>
-        <v>15.082777868018953</v>
+        <v>15.065190760100451</v>
       </c>
     </row>
     <row r="24" spans="2:142" x14ac:dyDescent="0.3">
@@ -4032,11 +4042,11 @@
       </c>
       <c r="U24" s="9">
         <f t="shared" ref="U24" si="43">U3/Q3-1</f>
-        <v>0.27584689837219534</v>
+        <v>0.35591728992520899</v>
       </c>
       <c r="V24" s="9">
         <f t="shared" ref="V24" si="44">V3/R3-1</f>
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="Y24" s="9"/>
       <c r="Z24" s="9">
@@ -4061,11 +4071,11 @@
       </c>
       <c r="AE24" s="9">
         <f t="shared" si="45"/>
-        <v>0.29515222028311028</v>
+        <v>0.32226720961799504</v>
       </c>
       <c r="AF24" s="9">
         <f t="shared" si="45"/>
-        <v>0.19999999999999996</v>
+        <v>0.22999999999999998</v>
       </c>
       <c r="AG24" s="9">
         <f t="shared" si="45"/>
@@ -4182,11 +4192,11 @@
       </c>
       <c r="U25" s="9">
         <f t="shared" si="48"/>
-        <v>0.53</v>
+        <v>0.51698031581224313</v>
       </c>
       <c r="V25" s="9">
         <f t="shared" si="48"/>
-        <v>0.54</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="Y25" s="9">
         <f t="shared" ref="Y25" si="49">Y7/Y3</f>
@@ -4214,7 +4224,7 @@
       </c>
       <c r="AE25" s="9">
         <f t="shared" si="50"/>
-        <v>0.49632884670090288</v>
+        <v>0.49495975909423945</v>
       </c>
       <c r="AF25" s="9">
         <f t="shared" si="50"/>
@@ -4226,35 +4236,35 @@
       </c>
       <c r="AH25" s="9">
         <f t="shared" si="50"/>
-        <v>0.59</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AI25" s="9">
         <f t="shared" si="50"/>
-        <v>0.6</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="AJ25" s="9">
         <f t="shared" si="50"/>
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="AK25" s="9">
         <f t="shared" si="50"/>
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="AL25" s="9">
         <f t="shared" si="50"/>
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="AM25" s="9">
         <f t="shared" si="50"/>
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="AN25" s="9">
         <f t="shared" si="50"/>
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="AO25" s="9">
         <f t="shared" si="50"/>
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="AQ25" t="s">
         <v>54</v>
@@ -4341,18 +4351,18 @@
       </c>
       <c r="U26" s="9">
         <f t="shared" si="53"/>
-        <v>1</v>
+        <v>0.54510058403633999</v>
       </c>
       <c r="V26" s="9">
         <f t="shared" si="53"/>
-        <v>1</v>
+        <v>0.57276161206540221</v>
       </c>
       <c r="Y26" s="9">
         <f t="shared" ref="Y26" si="54">(Y3-Y4)/Y3</f>
         <v>0.42608824840291187</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" ref="Z26:AD26" si="55">(Z3-Z4)/Z3</f>
+        <f t="shared" ref="Z26:AE26" si="55">(Z3-Z4)/Z3</f>
         <v>0.44525248386766364</v>
       </c>
       <c r="AA26" s="9">
@@ -4371,7 +4381,10 @@
         <f t="shared" si="55"/>
         <v>0.53019197207678881</v>
       </c>
-      <c r="AE26" s="9"/>
+      <c r="AE26" s="9">
+        <f t="shared" si="55"/>
+        <v>0.52549239968957029</v>
+      </c>
       <c r="AF26" s="9"/>
       <c r="AG26" s="9"/>
       <c r="AH26" s="9"/>
@@ -4455,11 +4468,11 @@
       </c>
       <c r="U27" s="9">
         <f t="shared" ref="U27:U28" si="59">U8/Q8-1</f>
-        <v>0.21999999999999997</v>
+        <v>0.30745721271393633</v>
       </c>
       <c r="V27" s="9">
         <f t="shared" ref="V27:V28" si="60">V8/R8-1</f>
-        <v>0.19999999999999996</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="Y27" s="9"/>
       <c r="Z27" s="9">
@@ -4484,11 +4497,11 @@
       </c>
       <c r="AE27" s="9">
         <f t="shared" si="61"/>
-        <v>0.18840148698884751</v>
+        <v>0.23177819083023543</v>
       </c>
       <c r="AF27" s="9">
         <f t="shared" si="61"/>
-        <v>0.12999999999999989</v>
+        <v>0.1399999999999999</v>
       </c>
       <c r="AG27" s="9">
         <f t="shared" si="61"/>
@@ -4531,7 +4544,7 @@
       </c>
       <c r="AR27" s="5">
         <f>NPV(AR26,AE20:EL20)</f>
-        <v>300334.0880058615</v>
+        <v>302620.97708222189</v>
       </c>
     </row>
     <row r="28" spans="2:142" x14ac:dyDescent="0.3">
@@ -4600,7 +4613,7 @@
       </c>
       <c r="U28" s="9">
         <f t="shared" si="59"/>
-        <v>0.44999999999999996</v>
+        <v>0.48266296809986131</v>
       </c>
       <c r="V28" s="9">
         <f t="shared" si="60"/>
@@ -4629,7 +4642,7 @@
       </c>
       <c r="AE28" s="9">
         <f t="shared" si="63"/>
-        <v>0.44852676967301464</v>
+        <v>0.4569888609414301</v>
       </c>
       <c r="AF28" s="9">
         <f t="shared" si="63"/>
@@ -4676,7 +4689,7 @@
       </c>
       <c r="AR28" s="5">
         <f>Main!D8</f>
-        <v>2649</v>
+        <v>4023</v>
       </c>
     </row>
     <row r="29" spans="2:142" x14ac:dyDescent="0.3">
@@ -4757,11 +4770,11 @@
       </c>
       <c r="U29" s="9">
         <f t="shared" si="66"/>
-        <v>0.12016666666666667</v>
+        <v>0.11561756435215229</v>
       </c>
       <c r="V29" s="9">
         <f t="shared" si="66"/>
-        <v>0.11583180987202925</v>
+        <v>0.11400768688191855</v>
       </c>
       <c r="Y29" s="9">
         <f t="shared" ref="Y29" si="67">Y9/Y3</f>
@@ -4789,54 +4802,54 @@
       </c>
       <c r="AE29" s="9">
         <f t="shared" si="68"/>
-        <v>0.12071237142728811</v>
+        <v>0.11892771477996847</v>
       </c>
       <c r="AF29" s="9">
         <f t="shared" si="68"/>
-        <v>0.11870049857016664</v>
+        <v>0.11409325482956323</v>
       </c>
       <c r="AG29" s="9">
         <f t="shared" si="68"/>
-        <v>0.11250742907954928</v>
+        <v>0.1081405632732382</v>
       </c>
       <c r="AH29" s="9">
         <f t="shared" si="68"/>
-        <v>0.10841624984029294</v>
+        <v>0.10420817915421138</v>
       </c>
       <c r="AI29" s="9">
         <f t="shared" si="68"/>
-        <v>0.10344302737055473</v>
+        <v>9.9427987449889746E-2</v>
       </c>
       <c r="AJ29" s="9">
         <f t="shared" si="68"/>
-        <v>0.10054275557511862</v>
+        <v>9.6640286867182554E-2</v>
       </c>
       <c r="AK29" s="9">
         <f t="shared" si="68"/>
-        <v>9.9585205522022241E-2</v>
+        <v>9.5719903182733199E-2</v>
       </c>
       <c r="AL29" s="9">
         <f t="shared" si="68"/>
-        <v>9.8636774993241083E-2</v>
+        <v>9.4808285057183361E-2</v>
       </c>
       <c r="AM29" s="9">
         <f t="shared" si="68"/>
-        <v>9.7697377136162597E-2</v>
+        <v>9.3905349009019715E-2</v>
       </c>
       <c r="AN29" s="9">
         <f t="shared" si="68"/>
-        <v>9.6766925925341987E-2</v>
+        <v>9.3011012351790948E-2</v>
       </c>
       <c r="AO29" s="9">
         <f t="shared" si="68"/>
-        <v>9.5845336154624455E-2</v>
+        <v>9.2125193186535795E-2</v>
       </c>
       <c r="AQ29" t="s">
         <v>58</v>
       </c>
       <c r="AR29" s="5">
         <f>AR27+AR28</f>
-        <v>302983.0880058615</v>
+        <v>306643.97708222189</v>
       </c>
     </row>
     <row r="30" spans="2:142" x14ac:dyDescent="0.3">
@@ -4917,11 +4930,11 @@
       </c>
       <c r="U30" s="9">
         <f t="shared" si="70"/>
-        <v>3.9650574712643674E-2</v>
+        <v>3.266277309106641E-2</v>
       </c>
       <c r="V30" s="9">
         <f t="shared" si="70"/>
-        <v>3.3989031078610607E-2</v>
+        <v>3.3453770746663981E-2</v>
       </c>
       <c r="Y30" s="9">
         <f t="shared" ref="Y30" si="71">Y10/Y3</f>
@@ -4949,7 +4962,7 @@
       </c>
       <c r="AE30" s="9">
         <f t="shared" si="72"/>
-        <v>3.8757317602671024E-2</v>
+        <v>3.6702521743874263E-2</v>
       </c>
       <c r="AF30" s="9"/>
       <c r="AG30" s="9"/>
@@ -4966,7 +4979,7 @@
       </c>
       <c r="AR30" s="4">
         <f>AR29/AO21</f>
-        <v>186.68089217859611</v>
+        <v>188.58793178488432</v>
       </c>
     </row>
     <row r="31" spans="2:142" x14ac:dyDescent="0.3">
@@ -5047,11 +5060,11 @@
       </c>
       <c r="U31" s="9">
         <f t="shared" si="75"/>
-        <v>0.14076666666666668</v>
+        <v>0.13735669478693488</v>
       </c>
       <c r="V31" s="9">
         <f t="shared" si="75"/>
-        <v>0.17556437712196402</v>
+        <v>0.17222118601719574</v>
       </c>
       <c r="Y31" s="9">
         <f t="shared" ref="Y31" si="76">Y14/Y3</f>
@@ -5079,54 +5092,54 @@
       </c>
       <c r="AE31" s="9">
         <f t="shared" si="77"/>
-        <v>0.10711802488359216</v>
+        <v>0.1060859589155605</v>
       </c>
       <c r="AF31" s="9">
         <f t="shared" si="77"/>
-        <v>0.21695993472174405</v>
+        <v>0.22172978373424712</v>
       </c>
       <c r="AG31" s="9">
         <f t="shared" si="77"/>
-        <v>0.25632149957720152</v>
+        <v>0.26084107294320974</v>
       </c>
       <c r="AH31" s="9">
         <f t="shared" si="77"/>
-        <v>0.28780071777439414</v>
+        <v>0.28215594301800201</v>
       </c>
       <c r="AI31" s="9">
         <f t="shared" si="77"/>
-        <v>0.3117548132893303</v>
+        <v>0.30591025755846074</v>
       </c>
       <c r="AJ31" s="9">
         <f t="shared" si="77"/>
-        <v>0.33163834337785486</v>
+        <v>0.32567596767356599</v>
       </c>
       <c r="AK31" s="9">
         <f t="shared" si="77"/>
-        <v>0.34602101535565644</v>
+        <v>0.33001889889057251</v>
       </c>
       <c r="AL31" s="9">
         <f t="shared" si="77"/>
-        <v>0.35032932739152944</v>
+        <v>0.33428787316710706</v>
       </c>
       <c r="AM31" s="9">
         <f t="shared" si="77"/>
-        <v>0.35456460901270753</v>
+        <v>0.3384842157252842</v>
       </c>
       <c r="AN31" s="9">
         <f t="shared" si="77"/>
-        <v>0.35872816524926399</v>
+        <v>0.3426092273399548</v>
       </c>
       <c r="AO31" s="9">
         <f t="shared" si="77"/>
-        <v>0.36282127709284612</v>
+        <v>0.34666418479679573</v>
       </c>
       <c r="AQ31" t="s">
         <v>60</v>
       </c>
       <c r="AR31" s="4">
         <f>Main!D3</f>
-        <v>150.74</v>
+        <v>239.23</v>
       </c>
     </row>
     <row r="32" spans="2:142" x14ac:dyDescent="0.3">
@@ -5207,7 +5220,7 @@
       </c>
       <c r="U32" s="9">
         <f t="shared" si="80"/>
-        <v>0.18</v>
+        <v>0.11634980988593156</v>
       </c>
       <c r="V32" s="9">
         <f t="shared" si="80"/>
@@ -5239,19 +5252,19 @@
       </c>
       <c r="AE32" s="9">
         <f t="shared" si="82"/>
-        <v>-4.8557691788259014E-2</v>
+        <v>-6.7048012963564649E-2</v>
       </c>
       <c r="AF32" s="9">
         <f t="shared" si="82"/>
-        <v>0.12</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="AG32" s="9">
         <f t="shared" si="82"/>
-        <v>0.12</v>
+        <v>0.11999999999999998</v>
       </c>
       <c r="AH32" s="9">
         <f t="shared" si="82"/>
-        <v>0.11999999999999998</v>
+        <v>0.12</v>
       </c>
       <c r="AI32" s="9">
         <f t="shared" si="82"/>
@@ -5259,11 +5272,11 @@
       </c>
       <c r="AJ32" s="9">
         <f t="shared" si="82"/>
-        <v>0.12</v>
+        <v>0.11999999999999998</v>
       </c>
       <c r="AK32" s="9">
         <f t="shared" si="82"/>
-        <v>0.12000000000000001</v>
+        <v>0.11999999999999998</v>
       </c>
       <c r="AL32" s="9">
         <f t="shared" si="82"/>
@@ -5275,18 +5288,18 @@
       </c>
       <c r="AN32" s="9">
         <f t="shared" si="82"/>
-        <v>0.11999999999999998</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="AO32" s="9">
         <f t="shared" si="82"/>
-        <v>0.12</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="AQ32" s="3" t="s">
         <v>61</v>
       </c>
       <c r="AR32" s="10">
         <f>AR30/AR31-1</f>
-        <v>0.2384296946968032</v>
+        <v>-0.21168778253193865</v>
       </c>
     </row>
     <row r="33" spans="2:44" x14ac:dyDescent="0.3">
@@ -5367,11 +5380,11 @@
       </c>
       <c r="U33" s="9">
         <f t="shared" si="85"/>
-        <v>0.11903058620689655</v>
+        <v>0.12675751676400607</v>
       </c>
       <c r="V33" s="9">
         <f t="shared" si="85"/>
-        <v>0.14771268738574045</v>
+        <v>0.14490643318808183</v>
       </c>
       <c r="Y33" s="9">
         <f t="shared" ref="Y33" si="86">Y20/Y3</f>
@@ -5399,53 +5412,53 @@
       </c>
       <c r="AE33" s="9">
         <f t="shared" si="87"/>
-        <v>0.1175770927220734</v>
+        <v>0.11903068401327374</v>
       </c>
       <c r="AF33" s="9">
         <f t="shared" si="87"/>
-        <v>0.19587552250053658</v>
+        <v>0.20046559609070039</v>
       </c>
       <c r="AG33" s="9">
         <f t="shared" si="87"/>
-        <v>0.23054864470762024</v>
+        <v>0.23487205266328004</v>
       </c>
       <c r="AH33" s="9">
         <f t="shared" si="87"/>
-        <v>0.25834831276280001</v>
+        <v>0.2535990335872117</v>
       </c>
       <c r="AI33" s="9">
         <f t="shared" si="87"/>
-        <v>0.27948813914659476</v>
+        <v>0.27453922693250982</v>
       </c>
       <c r="AJ33" s="9">
         <f t="shared" si="87"/>
-        <v>0.29705423391278701</v>
+        <v>0.29198469175234887</v>
       </c>
       <c r="AK33" s="9">
         <f t="shared" si="87"/>
-        <v>0.30976643451015956</v>
+        <v>0.29575094350842762</v>
       </c>
       <c r="AL33" s="9">
         <f t="shared" si="87"/>
-        <v>0.31351628279871974</v>
+        <v>0.29945564900232663</v>
       </c>
       <c r="AM33" s="9">
         <f t="shared" si="87"/>
-        <v>0.31720480304822868</v>
+        <v>0.3030998103624003</v>
       </c>
       <c r="AN33" s="9">
         <f t="shared" si="87"/>
-        <v>0.32083300416003313</v>
+        <v>0.30668441512671463</v>
       </c>
       <c r="AO33" s="9">
         <f t="shared" si="87"/>
-        <v>0.32440187981947322</v>
+        <v>0.31021043636589507</v>
       </c>
       <c r="AQ33" t="s">
         <v>62</v>
       </c>
       <c r="AR33" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/AMD.xlsx
+++ b/Financial Analysis/AMD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0662FF93-B5FE-4FBE-A730-15236FEF286B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3B3118-A646-4900-8BB9-6415E4A7E59E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9151AF15-9D45-44A9-8CA3-26C538A98864}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="74">
   <si>
     <t>AMD</t>
   </si>
@@ -232,10 +232,22 @@
     <t>Restructuring</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
-  </si>
-  <si>
     <t>Q325 8K</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Fairly valued</t>
   </si>
 </sst>
 </file>
@@ -335,14 +347,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
@@ -359,7 +371,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13708380" y="0"/>
+          <a:off x="14302740" y="0"/>
           <a:ext cx="0" cy="6499860"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -385,14 +397,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -409,7 +421,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19202400" y="7620"/>
+          <a:off x="22235160" y="7620"/>
           <a:ext cx="0" cy="6499860"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -759,17 +771,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>239.23</v>
+        <v>199.81</v>
       </c>
       <c r="E3" s="2">
-        <v>45966</v>
+        <v>46059</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45966</v>
+        <v>46059</v>
       </c>
       <c r="G3" s="2">
-        <v>46056</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -781,7 +793,7 @@
         <v>1626</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -790,7 +802,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>388987.98</v>
+        <v>324891.06</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -798,11 +810,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>4808+2435</f>
-        <v>7243</v>
+        <f>5539+5013</f>
+        <v>10552</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -810,11 +822,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>873+2347</f>
-        <v>3220</v>
+        <f>874+2348</f>
+        <v>3222</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -823,7 +835,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>4023</v>
+        <v>7330</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -832,7 +844,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>384964.98</v>
+        <v>317561.06</v>
       </c>
     </row>
   </sheetData>
@@ -842,16 +854,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DC7D0B-69F3-453E-80D5-E39B14F299EA}">
-  <dimension ref="B2:EL33"/>
+  <dimension ref="B2:EP33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="8.88671875" customWidth="1"/>
-    <col min="43" max="43" width="13.21875" customWidth="1"/>
-    <col min="44" max="44" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="13.21875" customWidth="1"/>
+    <col min="48" max="48" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:45" x14ac:dyDescent="0.3">
       <c r="C2" s="6" t="s">
         <v>41</v>
       </c>
@@ -912,59 +924,71 @@
       <c r="V2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="Y2">
+      <c r="W2" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC2">
         <v>2019</v>
       </c>
-      <c r="Z2">
+      <c r="AD2">
         <v>2020</v>
       </c>
-      <c r="AA2">
+      <c r="AE2">
         <v>2021</v>
       </c>
-      <c r="AB2">
+      <c r="AF2">
         <v>2022</v>
       </c>
-      <c r="AC2">
+      <c r="AG2">
         <v>2023</v>
       </c>
-      <c r="AD2">
+      <c r="AH2">
         <v>2024</v>
       </c>
-      <c r="AE2">
+      <c r="AI2">
         <v>2025</v>
       </c>
-      <c r="AF2">
+      <c r="AJ2">
         <v>2026</v>
       </c>
-      <c r="AG2">
+      <c r="AK2">
         <v>2027</v>
       </c>
-      <c r="AH2">
+      <c r="AL2">
         <v>2028</v>
       </c>
-      <c r="AI2">
+      <c r="AM2">
         <v>2029</v>
       </c>
-      <c r="AJ2">
+      <c r="AN2">
         <v>2030</v>
       </c>
-      <c r="AK2">
+      <c r="AO2">
         <v>2031</v>
       </c>
-      <c r="AL2">
+      <c r="AP2">
         <v>2032</v>
       </c>
-      <c r="AM2">
+      <c r="AQ2">
         <v>2033</v>
       </c>
-      <c r="AN2">
+      <c r="AR2">
         <v>2034</v>
       </c>
-      <c r="AO2">
+      <c r="AS2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:41" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:45" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
@@ -978,7 +1002,7 @@
         <v>4313</v>
       </c>
       <c r="F3" s="8">
-        <f>AA3-E3-D3-C3</f>
+        <f>AE3-E3-D3-C3</f>
         <v>4826</v>
       </c>
       <c r="G3" s="8">
@@ -1027,76 +1051,79 @@
         <v>9246</v>
       </c>
       <c r="V3" s="8">
-        <f>R3*1.27</f>
-        <v>9725.66</v>
-      </c>
-      <c r="Y3" s="8">
+        <v>10270</v>
+      </c>
+      <c r="W3" s="8"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="8"/>
+      <c r="AC3" s="8">
         <v>6731</v>
       </c>
-      <c r="Z3" s="8">
+      <c r="AD3" s="8">
         <v>9763</v>
       </c>
-      <c r="AA3" s="8">
+      <c r="AE3" s="8">
         <v>16434</v>
       </c>
-      <c r="AB3" s="8">
+      <c r="AF3" s="8">
         <f>SUM(G3:J3)</f>
         <v>23601</v>
       </c>
-      <c r="AC3" s="8">
+      <c r="AG3" s="8">
         <f>SUM(K3:N3)</f>
         <v>22680</v>
       </c>
-      <c r="AD3" s="8">
+      <c r="AH3" s="8">
         <f>SUM(O3:R3)</f>
         <v>25785</v>
       </c>
-      <c r="AE3" s="8">
+      <c r="AI3" s="8">
         <f>SUM(S3:V3)</f>
-        <v>34094.660000000003</v>
-      </c>
-      <c r="AF3" s="8">
-        <f>AE3*1.23</f>
-        <v>41936.431800000006</v>
-      </c>
-      <c r="AG3" s="8">
-        <f>AF3*1.15</f>
-        <v>48226.896570000004</v>
-      </c>
-      <c r="AH3" s="8">
-        <f>AG3*1.1</f>
-        <v>53049.586227000007</v>
-      </c>
-      <c r="AI3" s="8">
-        <f>AH3*1.09</f>
-        <v>57824.048987430011</v>
+        <v>34639</v>
       </c>
       <c r="AJ3" s="8">
-        <f>AI3*1.07</f>
-        <v>61871.732416550112</v>
+        <f>AI3*1.25</f>
+        <v>43298.75</v>
       </c>
       <c r="AK3" s="8">
-        <f>AJ3*1.05</f>
-        <v>64965.319037377623</v>
+        <f>AJ3*1.15</f>
+        <v>49793.562499999993</v>
       </c>
       <c r="AL3" s="8">
-        <f t="shared" ref="AL3:AO3" si="0">AK3*1.05</f>
-        <v>68213.584989246505</v>
+        <f>AK3*1.1</f>
+        <v>54772.918749999997</v>
       </c>
       <c r="AM3" s="8">
+        <f>AL3*1.09</f>
+        <v>59702.481437499999</v>
+      </c>
+      <c r="AN3" s="8">
+        <f>AM3*1.07</f>
+        <v>63881.655138125003</v>
+      </c>
+      <c r="AO3" s="8">
+        <f>AN3*1.05</f>
+        <v>67075.737895031256</v>
+      </c>
+      <c r="AP3" s="8">
+        <f t="shared" ref="AP3:AS3" si="0">AO3*1.05</f>
+        <v>70429.524789782823</v>
+      </c>
+      <c r="AQ3" s="8">
         <f t="shared" si="0"/>
-        <v>71624.264238708827</v>
-      </c>
-      <c r="AN3" s="8">
+        <v>73951.001029271967</v>
+      </c>
+      <c r="AR3" s="8">
         <f t="shared" si="0"/>
-        <v>75205.477450644277</v>
-      </c>
-      <c r="AO3" s="8">
+        <v>77648.551080735575</v>
+      </c>
+      <c r="AS3" s="8">
         <f t="shared" si="0"/>
-        <v>78965.75132317649</v>
+        <v>81530.978634772357</v>
       </c>
     </row>
-    <row r="4" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>14</v>
       </c>
@@ -1110,7 +1137,7 @@
         <v>2227</v>
       </c>
       <c r="F4" s="5">
-        <f>AA4-E4-D4-C4</f>
+        <f>AE4-E4-D4-C4</f>
         <v>2400</v>
       </c>
       <c r="G4" s="5">
@@ -1159,46 +1186,49 @@
         <v>4206</v>
       </c>
       <c r="V4" s="5">
-        <f>V6-V5</f>
-        <v>4155.1752999999999</v>
-      </c>
-      <c r="Y4" s="5">
+        <v>4433</v>
+      </c>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AC4" s="5">
         <v>3863</v>
       </c>
-      <c r="Z4" s="5">
+      <c r="AD4" s="5">
         <v>5416</v>
       </c>
-      <c r="AA4" s="5">
+      <c r="AE4" s="5">
         <v>8505</v>
       </c>
-      <c r="AB4" s="5">
+      <c r="AF4" s="5">
         <f>SUM(G4:J4)</f>
         <v>11550</v>
       </c>
-      <c r="AC4" s="5">
+      <c r="AG4" s="5">
         <f>SUM(K4:N4)</f>
         <v>11278</v>
       </c>
-      <c r="AD4" s="5">
+      <c r="AH4" s="5">
         <f>SUM(O4:R4)</f>
         <v>12114</v>
       </c>
-      <c r="AE4" s="5">
+      <c r="AI4" s="5">
         <f>SUM(S4:V4)</f>
-        <v>16178.175299999999</v>
-      </c>
-      <c r="AF4" s="5"/>
-      <c r="AG4" s="5"/>
-      <c r="AH4" s="5"/>
-      <c r="AI4" s="5"/>
+        <v>16456</v>
+      </c>
       <c r="AJ4" s="5"/>
       <c r="AK4" s="5"/>
       <c r="AL4" s="5"/>
       <c r="AM4" s="5"/>
       <c r="AN4" s="5"/>
       <c r="AO4" s="5"/>
+      <c r="AP4" s="5"/>
+      <c r="AQ4" s="5"/>
+      <c r="AR4" s="5"/>
+      <c r="AS4" s="5"/>
     </row>
-    <row r="5" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>17</v>
       </c>
@@ -1212,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="5">
-        <f>AA5-E5-D5-C5</f>
+        <f>AE5-E5-D5-C5</f>
         <v>0</v>
       </c>
       <c r="G5" s="5">
@@ -1261,44 +1291,48 @@
         <v>260</v>
       </c>
       <c r="V5" s="5">
-        <v>270</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
       <c r="Y5" s="5"/>
       <c r="Z5" s="5"/>
-      <c r="AA5" s="5"/>
-      <c r="AB5" s="5">
+      <c r="AC5" s="5"/>
+      <c r="AD5" s="5"/>
+      <c r="AE5" s="5"/>
+      <c r="AF5" s="5">
         <f>SUM(G5:J5)</f>
         <v>1448</v>
       </c>
-      <c r="AC5" s="5">
+      <c r="AG5" s="5">
         <f>SUM(K5:N5)</f>
         <v>942</v>
       </c>
-      <c r="AD5" s="5">
+      <c r="AH5" s="5">
         <f>SUM(O5:R5)</f>
         <v>946</v>
       </c>
-      <c r="AE5" s="5">
+      <c r="AI5" s="5">
         <f>SUM(S5:V5)</f>
-        <v>1041</v>
-      </c>
-      <c r="AF5" s="5"/>
-      <c r="AG5" s="5"/>
-      <c r="AH5" s="5"/>
-      <c r="AI5" s="5"/>
+        <v>1031</v>
+      </c>
       <c r="AJ5" s="5"/>
       <c r="AK5" s="5"/>
       <c r="AL5" s="5"/>
       <c r="AM5" s="5"/>
       <c r="AN5" s="5"/>
       <c r="AO5" s="5"/>
+      <c r="AP5" s="5"/>
+      <c r="AQ5" s="5"/>
+      <c r="AR5" s="5"/>
+      <c r="AS5" s="5"/>
     </row>
-    <row r="6" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="5">
-        <f t="shared" ref="C6:U6" si="1">SUM(C4:C5)</f>
+        <f t="shared" ref="C6:V6" si="1">SUM(C4:C5)</f>
         <v>1858</v>
       </c>
       <c r="D6" s="5">
@@ -1374,232 +1408,240 @@
         <v>4466</v>
       </c>
       <c r="V6" s="5">
-        <f t="shared" ref="V6" si="2">V3-V7</f>
-        <v>4425.1752999999999</v>
-      </c>
-      <c r="Y6" s="5">
-        <f t="shared" ref="Y6:AD6" si="3">SUM(Y4:Y5)</f>
+        <f t="shared" si="1"/>
+        <v>4693</v>
+      </c>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5"/>
+      <c r="AC6" s="5">
+        <f t="shared" ref="AC6:AH6" si="2">SUM(AC4:AC5)</f>
         <v>3863</v>
       </c>
-      <c r="Z6" s="5">
+      <c r="AD6" s="5">
+        <f t="shared" si="2"/>
+        <v>5416</v>
+      </c>
+      <c r="AE6" s="5">
+        <f t="shared" si="2"/>
+        <v>8505</v>
+      </c>
+      <c r="AF6" s="5">
+        <f t="shared" si="2"/>
+        <v>12998</v>
+      </c>
+      <c r="AG6" s="5">
+        <f t="shared" si="2"/>
+        <v>12220</v>
+      </c>
+      <c r="AH6" s="5">
+        <f t="shared" si="2"/>
+        <v>13060</v>
+      </c>
+      <c r="AI6" s="5">
+        <f>SUM(S6:V6)</f>
+        <v>17487</v>
+      </c>
+      <c r="AJ6" s="5">
+        <f>AJ3-AJ7</f>
+        <v>19484.437499999996</v>
+      </c>
+      <c r="AK6" s="5">
+        <f t="shared" ref="AK6:AS6" si="3">AK3-AK7</f>
+        <v>21411.231874999998</v>
+      </c>
+      <c r="AL6" s="5">
         <f t="shared" si="3"/>
-        <v>5416</v>
-      </c>
-      <c r="AA6" s="5">
+        <v>23004.625875000002</v>
+      </c>
+      <c r="AM6" s="5">
         <f t="shared" si="3"/>
-        <v>8505</v>
-      </c>
-      <c r="AB6" s="5">
+        <v>24478.017389375003</v>
+      </c>
+      <c r="AN6" s="5">
         <f t="shared" si="3"/>
-        <v>12998</v>
-      </c>
-      <c r="AC6" s="5">
+        <v>25552.662055250003</v>
+      </c>
+      <c r="AO6" s="5">
         <f t="shared" si="3"/>
-        <v>12220</v>
-      </c>
-      <c r="AD6" s="5">
+        <v>26830.295158012501</v>
+      </c>
+      <c r="AP6" s="5">
         <f t="shared" si="3"/>
-        <v>13060</v>
-      </c>
-      <c r="AE6" s="5">
-        <f>SUM(S6:V6)</f>
-        <v>17219.175299999999</v>
-      </c>
-      <c r="AF6" s="5">
-        <f>AF3-AF7</f>
-        <v>18871.39431</v>
-      </c>
-      <c r="AG6" s="5">
-        <f t="shared" ref="AG6:AO6" si="4">AG3-AG7</f>
-        <v>20737.565525100003</v>
-      </c>
-      <c r="AH6" s="5">
-        <f t="shared" si="4"/>
-        <v>22280.826215340006</v>
-      </c>
-      <c r="AI6" s="5">
-        <f t="shared" si="4"/>
-        <v>23707.860084846303</v>
-      </c>
-      <c r="AJ6" s="5">
-        <f t="shared" si="4"/>
-        <v>24748.692966620045</v>
-      </c>
-      <c r="AK6" s="5">
-        <f t="shared" si="4"/>
-        <v>25986.127614951052</v>
-      </c>
-      <c r="AL6" s="5">
-        <f t="shared" si="4"/>
-        <v>27285.4339956986</v>
-      </c>
-      <c r="AM6" s="5">
-        <f t="shared" si="4"/>
-        <v>28649.705695483535</v>
-      </c>
-      <c r="AN6" s="5">
-        <f t="shared" si="4"/>
-        <v>30082.190980257714</v>
-      </c>
-      <c r="AO6" s="5">
-        <f t="shared" si="4"/>
-        <v>31586.3005292706</v>
+        <v>28171.809915913131</v>
+      </c>
+      <c r="AQ6" s="5">
+        <f t="shared" si="3"/>
+        <v>29580.40041170879</v>
+      </c>
+      <c r="AR6" s="5">
+        <f t="shared" si="3"/>
+        <v>31059.420432294231</v>
+      </c>
+      <c r="AS6" s="5">
+        <f t="shared" si="3"/>
+        <v>32612.391453908946</v>
       </c>
     </row>
-    <row r="7" spans="2:41" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:45" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="8">
-        <f t="shared" ref="C7:U7" si="5">C3-C6</f>
+        <f t="shared" ref="C7:V7" si="4">C3-C6</f>
         <v>1587</v>
       </c>
       <c r="D7" s="8">
+        <f t="shared" si="4"/>
+        <v>1830</v>
+      </c>
+      <c r="E7" s="8">
+        <f t="shared" si="4"/>
+        <v>2086</v>
+      </c>
+      <c r="F7" s="8">
+        <f t="shared" si="4"/>
+        <v>2426</v>
+      </c>
+      <c r="G7" s="8">
+        <f t="shared" si="4"/>
+        <v>2818</v>
+      </c>
+      <c r="H7" s="8">
+        <f t="shared" si="4"/>
+        <v>3028</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" si="4"/>
+        <v>2354</v>
+      </c>
+      <c r="J7" s="8">
+        <f t="shared" si="4"/>
+        <v>2403</v>
+      </c>
+      <c r="K7" s="8">
+        <f t="shared" si="4"/>
+        <v>2359</v>
+      </c>
+      <c r="L7" s="8">
+        <f t="shared" si="4"/>
+        <v>2443</v>
+      </c>
+      <c r="M7" s="8">
+        <f t="shared" si="4"/>
+        <v>2747</v>
+      </c>
+      <c r="N7" s="8">
+        <f t="shared" si="4"/>
+        <v>2911</v>
+      </c>
+      <c r="O7" s="8">
+        <f t="shared" si="4"/>
+        <v>2560</v>
+      </c>
+      <c r="P7" s="8">
+        <f t="shared" si="4"/>
+        <v>2864</v>
+      </c>
+      <c r="Q7" s="8">
+        <f t="shared" si="4"/>
+        <v>3419</v>
+      </c>
+      <c r="R7" s="8">
+        <f t="shared" si="4"/>
+        <v>3882</v>
+      </c>
+      <c r="S7" s="8">
+        <f t="shared" si="4"/>
+        <v>3736</v>
+      </c>
+      <c r="T7" s="8">
+        <f t="shared" si="4"/>
+        <v>3059</v>
+      </c>
+      <c r="U7" s="8">
+        <f t="shared" si="4"/>
+        <v>4780</v>
+      </c>
+      <c r="V7" s="8">
+        <f t="shared" si="4"/>
+        <v>5577</v>
+      </c>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8"/>
+      <c r="AC7" s="8">
+        <f t="shared" ref="AC7:AI7" si="5">AC3-AC6</f>
+        <v>2868</v>
+      </c>
+      <c r="AD7" s="8">
         <f t="shared" si="5"/>
-        <v>1830</v>
-      </c>
-      <c r="E7" s="8">
+        <v>4347</v>
+      </c>
+      <c r="AE7" s="8">
         <f t="shared" si="5"/>
-        <v>2086</v>
-      </c>
-      <c r="F7" s="8">
+        <v>7929</v>
+      </c>
+      <c r="AF7" s="8">
         <f t="shared" si="5"/>
-        <v>2426</v>
-      </c>
-      <c r="G7" s="8">
+        <v>10603</v>
+      </c>
+      <c r="AG7" s="8">
         <f t="shared" si="5"/>
-        <v>2818</v>
-      </c>
-      <c r="H7" s="8">
+        <v>10460</v>
+      </c>
+      <c r="AH7" s="8">
         <f t="shared" si="5"/>
-        <v>3028</v>
-      </c>
-      <c r="I7" s="8">
+        <v>12725</v>
+      </c>
+      <c r="AI7" s="8">
         <f t="shared" si="5"/>
-        <v>2354</v>
-      </c>
-      <c r="J7" s="8">
-        <f t="shared" si="5"/>
-        <v>2403</v>
-      </c>
-      <c r="K7" s="8">
-        <f t="shared" si="5"/>
-        <v>2359</v>
-      </c>
-      <c r="L7" s="8">
-        <f t="shared" si="5"/>
-        <v>2443</v>
-      </c>
-      <c r="M7" s="8">
-        <f t="shared" si="5"/>
-        <v>2747</v>
-      </c>
-      <c r="N7" s="8">
-        <f t="shared" si="5"/>
-        <v>2911</v>
-      </c>
-      <c r="O7" s="8">
-        <f t="shared" si="5"/>
-        <v>2560</v>
-      </c>
-      <c r="P7" s="8">
-        <f t="shared" si="5"/>
-        <v>2864</v>
-      </c>
-      <c r="Q7" s="8">
-        <f t="shared" si="5"/>
-        <v>3419</v>
-      </c>
-      <c r="R7" s="8">
-        <f t="shared" si="5"/>
-        <v>3882</v>
-      </c>
-      <c r="S7" s="8">
-        <f t="shared" si="5"/>
-        <v>3736</v>
-      </c>
-      <c r="T7" s="8">
-        <f t="shared" si="5"/>
-        <v>3059</v>
-      </c>
-      <c r="U7" s="8">
-        <f t="shared" si="5"/>
-        <v>4780</v>
-      </c>
-      <c r="V7" s="8">
-        <f>V3*0.545</f>
-        <v>5300.4847</v>
-      </c>
-      <c r="Y7" s="8">
-        <f t="shared" ref="Y7:AE7" si="6">Y3-Y6</f>
-        <v>2868</v>
-      </c>
-      <c r="Z7" s="8">
+        <v>17152</v>
+      </c>
+      <c r="AJ7" s="8">
+        <f>AJ3*0.55</f>
+        <v>23814.312500000004</v>
+      </c>
+      <c r="AK7" s="8">
+        <f>AK3*0.57</f>
+        <v>28382.330624999995</v>
+      </c>
+      <c r="AL7" s="8">
+        <f>AL3*0.58</f>
+        <v>31768.292874999996</v>
+      </c>
+      <c r="AM7" s="8">
+        <f>AM3*0.59</f>
+        <v>35224.464048124995</v>
+      </c>
+      <c r="AN7" s="8">
+        <f>AN3*0.6</f>
+        <v>38328.993082875</v>
+      </c>
+      <c r="AO7" s="8">
+        <f t="shared" ref="AO7:AS7" si="6">AO3*0.6</f>
+        <v>40245.442737018755</v>
+      </c>
+      <c r="AP7" s="8">
         <f t="shared" si="6"/>
-        <v>4347</v>
-      </c>
-      <c r="AA7" s="8">
+        <v>42257.714873869692</v>
+      </c>
+      <c r="AQ7" s="8">
         <f t="shared" si="6"/>
-        <v>7929</v>
-      </c>
-      <c r="AB7" s="8">
+        <v>44370.600617563177</v>
+      </c>
+      <c r="AR7" s="8">
         <f t="shared" si="6"/>
-        <v>10603</v>
-      </c>
-      <c r="AC7" s="8">
+        <v>46589.130648441344</v>
+      </c>
+      <c r="AS7" s="8">
         <f t="shared" si="6"/>
-        <v>10460</v>
-      </c>
-      <c r="AD7" s="8">
-        <f t="shared" si="6"/>
-        <v>12725</v>
-      </c>
-      <c r="AE7" s="8">
-        <f t="shared" si="6"/>
-        <v>16875.484700000005</v>
-      </c>
-      <c r="AF7" s="8">
-        <f>AF3*0.55</f>
-        <v>23065.037490000006</v>
-      </c>
-      <c r="AG7" s="8">
-        <f>AG3*0.57</f>
-        <v>27489.331044900002</v>
-      </c>
-      <c r="AH7" s="8">
-        <f>AH3*0.58</f>
-        <v>30768.760011660001</v>
-      </c>
-      <c r="AI7" s="8">
-        <f>AI3*0.59</f>
-        <v>34116.188902583708</v>
-      </c>
-      <c r="AJ7" s="8">
-        <f>AJ3*0.6</f>
-        <v>37123.039449930067</v>
-      </c>
-      <c r="AK7" s="8">
-        <f t="shared" ref="AK7:AO7" si="7">AK3*0.6</f>
-        <v>38979.191422426571</v>
-      </c>
-      <c r="AL7" s="8">
-        <f t="shared" si="7"/>
-        <v>40928.150993547904</v>
-      </c>
-      <c r="AM7" s="8">
-        <f t="shared" si="7"/>
-        <v>42974.558543225292</v>
-      </c>
-      <c r="AN7" s="8">
-        <f t="shared" si="7"/>
-        <v>45123.286470386563</v>
-      </c>
-      <c r="AO7" s="8">
-        <f t="shared" si="7"/>
-        <v>47379.450793905889</v>
+        <v>48918.587180863411</v>
       </c>
     </row>
-    <row r="8" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>19</v>
       </c>
@@ -1613,7 +1655,7 @@
         <v>765</v>
       </c>
       <c r="F8" s="5">
-        <f>AA8-E8-D8-C8</f>
+        <f>AE8-E8-D8-C8</f>
         <v>811</v>
       </c>
       <c r="G8" s="5">
@@ -1662,76 +1704,79 @@
         <v>2139</v>
       </c>
       <c r="V8" s="5">
-        <f>R8*1.28</f>
-        <v>2191.36</v>
-      </c>
-      <c r="Y8" s="5">
+        <v>2330</v>
+      </c>
+      <c r="W8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="5"/>
+      <c r="AC8" s="5">
         <v>1547</v>
       </c>
-      <c r="Z8" s="5">
+      <c r="AD8" s="5">
         <v>1983</v>
       </c>
-      <c r="AA8" s="5">
+      <c r="AE8" s="5">
         <v>2845</v>
       </c>
-      <c r="AB8" s="5">
+      <c r="AF8" s="5">
         <f>SUM(G8:J8)</f>
         <v>5005</v>
       </c>
-      <c r="AC8" s="5">
+      <c r="AG8" s="5">
         <f>SUM(K8:N8)</f>
         <v>5872</v>
       </c>
-      <c r="AD8" s="5">
+      <c r="AH8" s="5">
         <f>SUM(O8:R8)</f>
         <v>6456</v>
       </c>
-      <c r="AE8" s="5">
+      <c r="AI8" s="5">
         <f>SUM(S8:V8)</f>
-        <v>7952.3600000000006</v>
-      </c>
-      <c r="AF8" s="5">
-        <f>AE8*1.14</f>
-        <v>9065.6903999999995</v>
-      </c>
-      <c r="AG8" s="5">
-        <f>AF8*1.08</f>
-        <v>9790.9456320000008</v>
-      </c>
-      <c r="AH8" s="5">
-        <f>AG8*1.06</f>
-        <v>10378.402369920001</v>
-      </c>
-      <c r="AI8" s="5">
-        <f>AH8*1.04</f>
-        <v>10793.538464716801</v>
+        <v>8091</v>
       </c>
       <c r="AJ8" s="5">
-        <f>AI8*1.03</f>
-        <v>11117.344618658306</v>
+        <f>AI8*1.18</f>
+        <v>9547.3799999999992</v>
       </c>
       <c r="AK8" s="5">
-        <f t="shared" ref="AK8:AO8" si="8">AJ8*1.03</f>
-        <v>11450.864957218055</v>
+        <f>AJ8*1.08</f>
+        <v>10311.170399999999</v>
       </c>
       <c r="AL8" s="5">
-        <f t="shared" si="8"/>
-        <v>11794.390905934597</v>
+        <f>AK8*1.06</f>
+        <v>10929.840624</v>
       </c>
       <c r="AM8" s="5">
-        <f t="shared" si="8"/>
-        <v>12148.222633112635</v>
+        <f>AL8*1.04</f>
+        <v>11367.034248960001</v>
       </c>
       <c r="AN8" s="5">
-        <f t="shared" si="8"/>
-        <v>12512.669312106014</v>
+        <f>AM8*1.03</f>
+        <v>11708.0452764288</v>
       </c>
       <c r="AO8" s="5">
-        <f t="shared" si="8"/>
-        <v>12888.049391469194</v>
+        <f t="shared" ref="AO8:AS8" si="7">AN8*1.03</f>
+        <v>12059.286634721664</v>
+      </c>
+      <c r="AP8" s="5">
+        <f t="shared" si="7"/>
+        <v>12421.065233763315</v>
+      </c>
+      <c r="AQ8" s="5">
+        <f t="shared" si="7"/>
+        <v>12793.697190776214</v>
+      </c>
+      <c r="AR8" s="5">
+        <f t="shared" si="7"/>
+        <v>13177.508106499501</v>
+      </c>
+      <c r="AS8" s="5">
+        <f t="shared" si="7"/>
+        <v>13572.833349694487</v>
       </c>
     </row>
-    <row r="9" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>20</v>
       </c>
@@ -1745,7 +1790,7 @@
         <v>376</v>
       </c>
       <c r="F9" s="5">
-        <f>AA9-E9-D9-C9</f>
+        <f>AE9-E9-D9-C9</f>
         <v>412</v>
       </c>
       <c r="G9" s="5">
@@ -1794,76 +1839,79 @@
         <v>1069</v>
       </c>
       <c r="V9" s="5">
-        <f>R9*1.4</f>
-        <v>1108.8</v>
-      </c>
-      <c r="Y9" s="5">
+        <v>1198</v>
+      </c>
+      <c r="W9" s="5"/>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
+      <c r="Z9" s="5"/>
+      <c r="AC9" s="5">
         <v>750</v>
       </c>
-      <c r="Z9" s="5">
+      <c r="AD9" s="5">
         <v>995</v>
       </c>
-      <c r="AA9" s="5">
+      <c r="AE9" s="5">
         <v>1448</v>
       </c>
-      <c r="AB9" s="5">
+      <c r="AF9" s="5">
         <f>SUM(G9:J9)</f>
         <v>2336</v>
       </c>
-      <c r="AC9" s="5">
+      <c r="AG9" s="5">
         <f>SUM(K9:N9)</f>
         <v>2352</v>
       </c>
-      <c r="AD9" s="5">
+      <c r="AH9" s="5">
         <f>SUM(O9:R9)</f>
         <v>2783</v>
       </c>
-      <c r="AE9" s="5">
+      <c r="AI9" s="5">
         <f>SUM(S9:V9)</f>
-        <v>4054.8</v>
-      </c>
-      <c r="AF9" s="5">
-        <f>AE9*1.18</f>
-        <v>4784.6639999999998</v>
-      </c>
-      <c r="AG9" s="5">
-        <f>AF9*1.09</f>
-        <v>5215.2837600000003</v>
-      </c>
-      <c r="AH9" s="5">
-        <f>AG9*1.06</f>
-        <v>5528.2007856000009</v>
-      </c>
-      <c r="AI9" s="5">
-        <f>AH9*1.04</f>
-        <v>5749.3288170240012</v>
+        <v>4144</v>
       </c>
       <c r="AJ9" s="5">
-        <f>AI9*1.04</f>
-        <v>5979.3019697049613</v>
+        <f>AI9*1.25</f>
+        <v>5180</v>
       </c>
       <c r="AK9" s="5">
-        <f t="shared" ref="AK9:AO9" si="9">AJ9*1.04</f>
-        <v>6218.4740484931599</v>
+        <f>AJ9*1.14</f>
+        <v>5905.2</v>
       </c>
       <c r="AL9" s="5">
-        <f t="shared" si="9"/>
-        <v>6467.2130104328862</v>
+        <f>AK9*1.08</f>
+        <v>6377.616</v>
       </c>
       <c r="AM9" s="5">
-        <f t="shared" si="9"/>
-        <v>6725.9015308502021</v>
+        <f>AL9*1.04</f>
+        <v>6632.7206400000005</v>
       </c>
       <c r="AN9" s="5">
-        <f t="shared" si="9"/>
-        <v>6994.9375920842103</v>
+        <f>AM9*1.04</f>
+        <v>6898.0294656000005</v>
       </c>
       <c r="AO9" s="5">
-        <f t="shared" si="9"/>
-        <v>7274.735095767579</v>
+        <f t="shared" ref="AO9:AS9" si="8">AN9*1.04</f>
+        <v>7173.9506442240008</v>
+      </c>
+      <c r="AP9" s="5">
+        <f t="shared" si="8"/>
+        <v>7460.9086699929612</v>
+      </c>
+      <c r="AQ9" s="5">
+        <f t="shared" si="8"/>
+        <v>7759.3450167926803</v>
+      </c>
+      <c r="AR9" s="5">
+        <f t="shared" si="8"/>
+        <v>8069.7188174643879</v>
+      </c>
+      <c r="AS9" s="5">
+        <f t="shared" si="8"/>
+        <v>8392.507570162963</v>
       </c>
     </row>
-    <row r="10" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>15</v>
       </c>
@@ -1877,7 +1925,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="5">
-        <f>AA10-E10-D10-C10</f>
+        <f>AE10-E10-D10-C10</f>
         <v>0</v>
       </c>
       <c r="G10" s="5">
@@ -1926,40 +1974,43 @@
         <v>302</v>
       </c>
       <c r="V10" s="5">
-        <f t="shared" ref="V10" si="10">R10*0.98</f>
-        <v>325.36</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="W10" s="5"/>
+      <c r="X10" s="5"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5"/>
-      <c r="AA10" s="5"/>
-      <c r="AB10" s="5">
+      <c r="AC10" s="5"/>
+      <c r="AD10" s="5"/>
+      <c r="AE10" s="5"/>
+      <c r="AF10" s="5">
         <f>SUM(G10:J10)</f>
         <v>2100</v>
       </c>
-      <c r="AC10" s="5">
+      <c r="AG10" s="5">
         <f>SUM(K10:N10)</f>
         <v>1869</v>
       </c>
-      <c r="AD10" s="5">
+      <c r="AH10" s="5">
         <f>SUM(O10:R10)</f>
         <v>1448</v>
       </c>
-      <c r="AE10" s="5">
+      <c r="AI10" s="5">
         <f>SUM(S10:V10)</f>
-        <v>1251.3600000000001</v>
-      </c>
-      <c r="AF10" s="5"/>
-      <c r="AG10" s="5"/>
-      <c r="AH10" s="5"/>
-      <c r="AI10" s="5"/>
+        <v>1223</v>
+      </c>
       <c r="AJ10" s="5"/>
       <c r="AK10" s="5"/>
       <c r="AL10" s="5"/>
       <c r="AM10" s="5"/>
       <c r="AN10" s="5"/>
       <c r="AO10" s="5"/>
+      <c r="AP10" s="5"/>
+      <c r="AQ10" s="5"/>
+      <c r="AR10" s="5"/>
+      <c r="AS10" s="5"/>
     </row>
-    <row r="11" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>21</v>
       </c>
@@ -1973,7 +2024,7 @@
         <v>-3</v>
       </c>
       <c r="F11" s="5">
-        <f>AA11-E11-D11-C11</f>
+        <f>AE11-E11-D11-C11</f>
         <v>-4</v>
       </c>
       <c r="G11" s="5">
@@ -2024,73 +2075,77 @@
       <c r="V11" s="5">
         <v>0</v>
       </c>
-      <c r="Y11" s="5">
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="5"/>
+      <c r="AC11" s="5">
         <v>-60</v>
       </c>
-      <c r="Z11" s="5">
+      <c r="AD11" s="5">
         <v>0</v>
       </c>
-      <c r="AA11" s="5">
+      <c r="AE11" s="5">
         <v>-12</v>
       </c>
-      <c r="AB11" s="5">
+      <c r="AF11" s="5">
         <f>SUM(G11:J11)</f>
         <v>-102</v>
       </c>
-      <c r="AC11" s="5">
+      <c r="AG11" s="5">
         <f>SUM(K11:N11)</f>
         <v>-34</v>
       </c>
-      <c r="AD11" s="5">
+      <c r="AH11" s="5">
         <f>SUM(O11:R11)</f>
         <v>-48</v>
       </c>
-      <c r="AE11" s="5">
+      <c r="AI11" s="5">
         <f>SUM(S11:V11)</f>
         <v>0</v>
       </c>
-      <c r="AF11" s="5">
-        <f t="shared" ref="AF11:AO11" si="11">-AF3*0.002</f>
-        <v>-83.872863600000017</v>
-      </c>
-      <c r="AG11" s="5">
-        <f t="shared" si="11"/>
-        <v>-96.453793140000016</v>
-      </c>
-      <c r="AH11" s="5">
-        <f t="shared" si="11"/>
-        <v>-106.09917245400001</v>
-      </c>
-      <c r="AI11" s="5">
-        <f t="shared" si="11"/>
-        <v>-115.64809797486002</v>
-      </c>
       <c r="AJ11" s="5">
-        <f t="shared" si="11"/>
-        <v>-123.74346483310023</v>
+        <f t="shared" ref="AJ11:AS11" si="9">-AJ3*0.002</f>
+        <v>-86.597499999999997</v>
       </c>
       <c r="AK11" s="5">
-        <f t="shared" si="11"/>
-        <v>-129.93063807475525</v>
+        <f t="shared" si="9"/>
+        <v>-99.587124999999986</v>
       </c>
       <c r="AL11" s="5">
-        <f t="shared" si="11"/>
-        <v>-136.42716997849303</v>
+        <f t="shared" si="9"/>
+        <v>-109.54583749999999</v>
       </c>
       <c r="AM11" s="5">
-        <f t="shared" si="11"/>
-        <v>-143.24852847741766</v>
+        <f t="shared" si="9"/>
+        <v>-119.404962875</v>
       </c>
       <c r="AN11" s="5">
-        <f t="shared" si="11"/>
-        <v>-150.41095490128856</v>
+        <f t="shared" si="9"/>
+        <v>-127.76331027625001</v>
       </c>
       <c r="AO11" s="5">
-        <f t="shared" si="11"/>
-        <v>-157.93150264635298</v>
+        <f t="shared" si="9"/>
+        <v>-134.15147579006251</v>
+      </c>
+      <c r="AP11" s="5">
+        <f t="shared" si="9"/>
+        <v>-140.85904957956564</v>
+      </c>
+      <c r="AQ11" s="5">
+        <f t="shared" si="9"/>
+        <v>-147.90200205854393</v>
+      </c>
+      <c r="AR11" s="5">
+        <f t="shared" si="9"/>
+        <v>-155.29710216147114</v>
+      </c>
+      <c r="AS11" s="5">
+        <f t="shared" si="9"/>
+        <v>-163.06195726954471</v>
       </c>
     </row>
-    <row r="12" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>67</v>
       </c>
@@ -2124,92 +2179,96 @@
       <c r="V12" s="5">
         <v>0</v>
       </c>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5"/>
-      <c r="AA12" s="5"/>
-      <c r="AB12" s="5"/>
       <c r="AC12" s="5"/>
-      <c r="AD12" s="5">
+      <c r="AD12" s="5"/>
+      <c r="AE12" s="5"/>
+      <c r="AF12" s="5"/>
+      <c r="AG12" s="5"/>
+      <c r="AH12" s="5">
         <f>SUM(O12:R12)</f>
         <v>186</v>
       </c>
-      <c r="AE12" s="5">
+      <c r="AI12" s="5">
         <f>SUM(S12:V12)</f>
         <v>0</v>
       </c>
-      <c r="AF12" s="5"/>
-      <c r="AG12" s="5"/>
-      <c r="AH12" s="5"/>
-      <c r="AI12" s="5"/>
       <c r="AJ12" s="5"/>
       <c r="AK12" s="5"/>
       <c r="AL12" s="5"/>
       <c r="AM12" s="5"/>
       <c r="AN12" s="5"/>
       <c r="AO12" s="5"/>
+      <c r="AP12" s="5"/>
+      <c r="AQ12" s="5"/>
+      <c r="AR12" s="5"/>
+      <c r="AS12" s="5"/>
     </row>
-    <row r="13" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>22</v>
       </c>
       <c r="C13" s="5">
-        <f t="shared" ref="C13:Q13" si="12">SUM(C8:C11)</f>
+        <f t="shared" ref="C13:Q13" si="10">SUM(C8:C11)</f>
         <v>925</v>
       </c>
       <c r="D13" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>999</v>
       </c>
       <c r="E13" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1138</v>
       </c>
       <c r="F13" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1219</v>
       </c>
       <c r="G13" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1867</v>
       </c>
       <c r="H13" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>2502</v>
       </c>
       <c r="I13" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>2418</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>2552</v>
       </c>
       <c r="K13" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>2504</v>
       </c>
       <c r="L13" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>2463</v>
       </c>
       <c r="M13" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>2523</v>
       </c>
       <c r="N13" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>2569</v>
       </c>
       <c r="O13" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>2524</v>
       </c>
       <c r="P13" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>2595</v>
       </c>
       <c r="Q13" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>2695</v>
       </c>
       <c r="R13" s="5">
@@ -2217,244 +2276,252 @@
         <v>3011</v>
       </c>
       <c r="S13" s="5">
-        <f t="shared" ref="S13:V13" si="13">SUM(S8:S12)</f>
+        <f t="shared" ref="S13:V13" si="11">SUM(S8:S12)</f>
         <v>2930</v>
       </c>
       <c r="T13" s="5">
+        <f t="shared" si="11"/>
+        <v>3193</v>
+      </c>
+      <c r="U13" s="5">
+        <f t="shared" si="11"/>
+        <v>3510</v>
+      </c>
+      <c r="V13" s="5">
+        <f t="shared" si="11"/>
+        <v>3825</v>
+      </c>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+      <c r="Z13" s="5"/>
+      <c r="AC13" s="5">
+        <f t="shared" ref="AC13:AG13" si="12">SUM(AC8:AC11)</f>
+        <v>2237</v>
+      </c>
+      <c r="AD13" s="5">
+        <f t="shared" si="12"/>
+        <v>2978</v>
+      </c>
+      <c r="AE13" s="5">
+        <f t="shared" si="12"/>
+        <v>4281</v>
+      </c>
+      <c r="AF13" s="5">
+        <f t="shared" si="12"/>
+        <v>9339</v>
+      </c>
+      <c r="AG13" s="5">
+        <f t="shared" si="12"/>
+        <v>10059</v>
+      </c>
+      <c r="AH13" s="5">
+        <f>SUM(AH8:AH12)</f>
+        <v>10825</v>
+      </c>
+      <c r="AI13" s="5">
+        <f t="shared" ref="AI13:AS13" si="13">SUM(AI8:AI12)</f>
+        <v>13458</v>
+      </c>
+      <c r="AJ13" s="5">
         <f t="shared" si="13"/>
-        <v>3193</v>
-      </c>
-      <c r="U13" s="5">
+        <v>14640.782499999999</v>
+      </c>
+      <c r="AK13" s="5">
         <f t="shared" si="13"/>
-        <v>3510</v>
-      </c>
-      <c r="V13" s="5">
+        <v>16116.783275</v>
+      </c>
+      <c r="AL13" s="5">
         <f t="shared" si="13"/>
-        <v>3625.52</v>
-      </c>
-      <c r="Y13" s="5">
-        <f t="shared" ref="Y13:AC13" si="14">SUM(Y8:Y11)</f>
-        <v>2237</v>
-      </c>
-      <c r="Z13" s="5">
-        <f t="shared" si="14"/>
-        <v>2978</v>
-      </c>
-      <c r="AA13" s="5">
-        <f t="shared" si="14"/>
-        <v>4281</v>
-      </c>
-      <c r="AB13" s="5">
-        <f t="shared" si="14"/>
-        <v>9339</v>
-      </c>
-      <c r="AC13" s="5">
-        <f t="shared" si="14"/>
-        <v>10059</v>
-      </c>
-      <c r="AD13" s="5">
-        <f>SUM(AD8:AD12)</f>
-        <v>10825</v>
-      </c>
-      <c r="AE13" s="5">
-        <f t="shared" ref="AE13:AO13" si="15">SUM(AE8:AE12)</f>
-        <v>13258.52</v>
-      </c>
-      <c r="AF13" s="5">
-        <f t="shared" si="15"/>
-        <v>13766.481536400001</v>
-      </c>
-      <c r="AG13" s="5">
-        <f t="shared" si="15"/>
-        <v>14909.77559886</v>
-      </c>
-      <c r="AH13" s="5">
-        <f t="shared" si="15"/>
-        <v>15800.503983066003</v>
-      </c>
-      <c r="AI13" s="5">
-        <f t="shared" si="15"/>
-        <v>16427.219183765941</v>
-      </c>
-      <c r="AJ13" s="5">
-        <f t="shared" si="15"/>
-        <v>16972.903123530166</v>
-      </c>
-      <c r="AK13" s="5">
-        <f t="shared" si="15"/>
-        <v>17539.408367636461</v>
-      </c>
-      <c r="AL13" s="5">
-        <f t="shared" si="15"/>
-        <v>18125.176746388992</v>
+        <v>17197.910786499997</v>
       </c>
       <c r="AM13" s="5">
-        <f t="shared" si="15"/>
-        <v>18730.875635485416</v>
+        <f t="shared" si="13"/>
+        <v>17880.349926085</v>
       </c>
       <c r="AN13" s="5">
-        <f t="shared" si="15"/>
-        <v>19357.195949288933</v>
+        <f t="shared" si="13"/>
+        <v>18478.311431752554</v>
       </c>
       <c r="AO13" s="5">
-        <f t="shared" si="15"/>
-        <v>20004.85298459042</v>
+        <f t="shared" si="13"/>
+        <v>19099.085803155602</v>
+      </c>
+      <c r="AP13" s="5">
+        <f t="shared" si="13"/>
+        <v>19741.114854176711</v>
+      </c>
+      <c r="AQ13" s="5">
+        <f t="shared" si="13"/>
+        <v>20405.14020551035</v>
+      </c>
+      <c r="AR13" s="5">
+        <f t="shared" si="13"/>
+        <v>21091.929821802416</v>
+      </c>
+      <c r="AS13" s="5">
+        <f t="shared" si="13"/>
+        <v>21802.278962587909</v>
       </c>
     </row>
-    <row r="14" spans="2:41" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:45" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C14" s="8">
-        <f t="shared" ref="C14:R14" si="16">C7-C13</f>
+        <f t="shared" ref="C14:R14" si="14">C7-C13</f>
         <v>662</v>
       </c>
       <c r="D14" s="8">
+        <f t="shared" si="14"/>
+        <v>831</v>
+      </c>
+      <c r="E14" s="8">
+        <f t="shared" si="14"/>
+        <v>948</v>
+      </c>
+      <c r="F14" s="8">
+        <f t="shared" si="14"/>
+        <v>1207</v>
+      </c>
+      <c r="G14" s="8">
+        <f t="shared" si="14"/>
+        <v>951</v>
+      </c>
+      <c r="H14" s="8">
+        <f t="shared" si="14"/>
+        <v>526</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="14"/>
+        <v>-64</v>
+      </c>
+      <c r="J14" s="8">
+        <f t="shared" si="14"/>
+        <v>-149</v>
+      </c>
+      <c r="K14" s="8">
+        <f t="shared" si="14"/>
+        <v>-145</v>
+      </c>
+      <c r="L14" s="8">
+        <f t="shared" si="14"/>
+        <v>-20</v>
+      </c>
+      <c r="M14" s="8">
+        <f t="shared" si="14"/>
+        <v>224</v>
+      </c>
+      <c r="N14" s="8">
+        <f t="shared" si="14"/>
+        <v>342</v>
+      </c>
+      <c r="O14" s="8">
+        <f t="shared" si="14"/>
+        <v>36</v>
+      </c>
+      <c r="P14" s="8">
+        <f t="shared" si="14"/>
+        <v>269</v>
+      </c>
+      <c r="Q14" s="8">
+        <f t="shared" si="14"/>
+        <v>724</v>
+      </c>
+      <c r="R14" s="8">
+        <f t="shared" si="14"/>
+        <v>871</v>
+      </c>
+      <c r="S14" s="8">
+        <f t="shared" ref="S14:V14" si="15">S7-S13</f>
+        <v>806</v>
+      </c>
+      <c r="T14" s="8">
+        <f t="shared" si="15"/>
+        <v>-134</v>
+      </c>
+      <c r="U14" s="8">
+        <f t="shared" si="15"/>
+        <v>1270</v>
+      </c>
+      <c r="V14" s="8">
+        <f t="shared" si="15"/>
+        <v>1752</v>
+      </c>
+      <c r="W14" s="8"/>
+      <c r="X14" s="8"/>
+      <c r="Y14" s="8"/>
+      <c r="Z14" s="8"/>
+      <c r="AC14" s="8">
+        <f t="shared" ref="AC14:AH14" si="16">AC7-AC13</f>
+        <v>631</v>
+      </c>
+      <c r="AD14" s="8">
         <f t="shared" si="16"/>
-        <v>831</v>
-      </c>
-      <c r="E14" s="8">
+        <v>1369</v>
+      </c>
+      <c r="AE14" s="8">
         <f t="shared" si="16"/>
-        <v>948</v>
-      </c>
-      <c r="F14" s="8">
+        <v>3648</v>
+      </c>
+      <c r="AF14" s="8">
         <f t="shared" si="16"/>
-        <v>1207</v>
-      </c>
-      <c r="G14" s="8">
+        <v>1264</v>
+      </c>
+      <c r="AG14" s="8">
         <f t="shared" si="16"/>
-        <v>951</v>
-      </c>
-      <c r="H14" s="8">
+        <v>401</v>
+      </c>
+      <c r="AH14" s="8">
         <f t="shared" si="16"/>
-        <v>526</v>
-      </c>
-      <c r="I14" s="8">
-        <f t="shared" si="16"/>
-        <v>-64</v>
-      </c>
-      <c r="J14" s="8">
-        <f t="shared" si="16"/>
-        <v>-149</v>
-      </c>
-      <c r="K14" s="8">
-        <f t="shared" si="16"/>
-        <v>-145</v>
-      </c>
-      <c r="L14" s="8">
-        <f t="shared" si="16"/>
-        <v>-20</v>
-      </c>
-      <c r="M14" s="8">
-        <f t="shared" si="16"/>
-        <v>224</v>
-      </c>
-      <c r="N14" s="8">
-        <f t="shared" si="16"/>
-        <v>342</v>
-      </c>
-      <c r="O14" s="8">
-        <f t="shared" si="16"/>
-        <v>36</v>
-      </c>
-      <c r="P14" s="8">
-        <f t="shared" si="16"/>
-        <v>269</v>
-      </c>
-      <c r="Q14" s="8">
-        <f t="shared" si="16"/>
-        <v>724</v>
-      </c>
-      <c r="R14" s="8">
-        <f t="shared" si="16"/>
-        <v>871</v>
-      </c>
-      <c r="S14" s="8">
-        <f t="shared" ref="S14:V14" si="17">S7-S13</f>
-        <v>806</v>
-      </c>
-      <c r="T14" s="8">
+        <v>1900</v>
+      </c>
+      <c r="AI14" s="8">
+        <f t="shared" ref="AI14:AS14" si="17">AI7-AI13</f>
+        <v>3694</v>
+      </c>
+      <c r="AJ14" s="8">
         <f t="shared" si="17"/>
-        <v>-134</v>
-      </c>
-      <c r="U14" s="8">
+        <v>9173.5300000000043</v>
+      </c>
+      <c r="AK14" s="8">
         <f t="shared" si="17"/>
-        <v>1270</v>
-      </c>
-      <c r="V14" s="8">
+        <v>12265.547349999995</v>
+      </c>
+      <c r="AL14" s="8">
         <f t="shared" si="17"/>
-        <v>1674.9647</v>
-      </c>
-      <c r="Y14" s="8">
-        <f t="shared" ref="Y14:AD14" si="18">Y7-Y13</f>
-        <v>631</v>
-      </c>
-      <c r="Z14" s="8">
-        <f t="shared" si="18"/>
-        <v>1369</v>
-      </c>
-      <c r="AA14" s="8">
-        <f t="shared" si="18"/>
-        <v>3648</v>
-      </c>
-      <c r="AB14" s="8">
-        <f t="shared" si="18"/>
-        <v>1264</v>
-      </c>
-      <c r="AC14" s="8">
-        <f t="shared" si="18"/>
-        <v>401</v>
-      </c>
-      <c r="AD14" s="8">
-        <f t="shared" si="18"/>
-        <v>1900</v>
-      </c>
-      <c r="AE14" s="8">
-        <f t="shared" ref="AE14:AO14" si="19">AE7-AE13</f>
-        <v>3616.9647000000041</v>
-      </c>
-      <c r="AF14" s="8">
-        <f t="shared" si="19"/>
-        <v>9298.5559536000055</v>
-      </c>
-      <c r="AG14" s="8">
-        <f t="shared" si="19"/>
-        <v>12579.555446040002</v>
-      </c>
-      <c r="AH14" s="8">
-        <f t="shared" si="19"/>
-        <v>14968.256028593998</v>
-      </c>
-      <c r="AI14" s="8">
-        <f t="shared" si="19"/>
-        <v>17688.969718817767</v>
-      </c>
-      <c r="AJ14" s="8">
-        <f t="shared" si="19"/>
-        <v>20150.136326399901</v>
-      </c>
-      <c r="AK14" s="8">
-        <f t="shared" si="19"/>
-        <v>21439.78305479011</v>
-      </c>
-      <c r="AL14" s="8">
-        <f t="shared" si="19"/>
-        <v>22802.974247158912</v>
+        <v>14570.382088499999</v>
       </c>
       <c r="AM14" s="8">
-        <f t="shared" si="19"/>
-        <v>24243.682907739876</v>
+        <f t="shared" si="17"/>
+        <v>17344.114122039995</v>
       </c>
       <c r="AN14" s="8">
-        <f t="shared" si="19"/>
-        <v>25766.090521097631</v>
+        <f t="shared" si="17"/>
+        <v>19850.681651122446</v>
       </c>
       <c r="AO14" s="8">
-        <f t="shared" si="19"/>
-        <v>27374.59780931547</v>
+        <f t="shared" si="17"/>
+        <v>21146.356933863153</v>
+      </c>
+      <c r="AP14" s="8">
+        <f t="shared" si="17"/>
+        <v>22516.600019692982</v>
+      </c>
+      <c r="AQ14" s="8">
+        <f t="shared" si="17"/>
+        <v>23965.460412052827</v>
+      </c>
+      <c r="AR14" s="8">
+        <f t="shared" si="17"/>
+        <v>25497.200826638928</v>
+      </c>
+      <c r="AS14" s="8">
+        <f t="shared" si="17"/>
+        <v>27116.308218275502</v>
       </c>
     </row>
-    <row r="15" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>24</v>
       </c>
@@ -2468,7 +2535,7 @@
         <v>7</v>
       </c>
       <c r="F15" s="5">
-        <f>AA15-E15-D15-C15</f>
+        <f>AE15-E15-D15-C15</f>
         <v>8</v>
       </c>
       <c r="G15" s="5">
@@ -2517,75 +2584,79 @@
         <v>37</v>
       </c>
       <c r="V15" s="5">
-        <v>22</v>
-      </c>
-      <c r="Y15" s="5">
+        <v>36</v>
+      </c>
+      <c r="W15" s="5"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="5"/>
+      <c r="AC15" s="5">
         <v>94</v>
       </c>
-      <c r="Z15" s="5">
+      <c r="AD15" s="5">
         <v>47</v>
       </c>
-      <c r="AA15" s="5">
+      <c r="AE15" s="5">
         <v>34</v>
       </c>
-      <c r="AB15" s="5">
+      <c r="AF15" s="5">
         <f>SUM(G15:J15)</f>
         <v>88</v>
       </c>
-      <c r="AC15" s="5">
+      <c r="AG15" s="5">
         <f>SUM(K15:N15)</f>
         <v>106</v>
       </c>
-      <c r="AD15" s="5">
+      <c r="AH15" s="5">
         <f>SUM(O15:R15)</f>
         <v>92</v>
       </c>
-      <c r="AE15" s="5">
+      <c r="AI15" s="5">
         <f>SUM(S15:V15)</f>
-        <v>117</v>
-      </c>
-      <c r="AF15" s="5">
-        <f t="shared" ref="AF15:AO15" si="20">AE15*1.02</f>
-        <v>119.34</v>
-      </c>
-      <c r="AG15" s="5">
-        <f t="shared" si="20"/>
-        <v>121.72680000000001</v>
-      </c>
-      <c r="AH15" s="5">
-        <f t="shared" si="20"/>
-        <v>124.16133600000002</v>
-      </c>
-      <c r="AI15" s="5">
-        <f t="shared" si="20"/>
-        <v>126.64456272000002</v>
+        <v>131</v>
       </c>
       <c r="AJ15" s="5">
-        <f t="shared" si="20"/>
-        <v>129.17745397440004</v>
+        <f t="shared" ref="AJ15:AS15" si="18">AI15*1.02</f>
+        <v>133.62</v>
       </c>
       <c r="AK15" s="5">
-        <f t="shared" si="20"/>
-        <v>131.76100305388803</v>
+        <f t="shared" si="18"/>
+        <v>136.29240000000001</v>
       </c>
       <c r="AL15" s="5">
-        <f t="shared" si="20"/>
-        <v>134.39622311496581</v>
+        <f t="shared" si="18"/>
+        <v>139.01824800000003</v>
       </c>
       <c r="AM15" s="5">
-        <f t="shared" si="20"/>
-        <v>137.08414757726513</v>
+        <f t="shared" si="18"/>
+        <v>141.79861296000004</v>
       </c>
       <c r="AN15" s="5">
-        <f t="shared" si="20"/>
-        <v>139.82583052881043</v>
+        <f t="shared" si="18"/>
+        <v>144.63458521920003</v>
       </c>
       <c r="AO15" s="5">
-        <f t="shared" si="20"/>
-        <v>142.62234713938665</v>
+        <f t="shared" si="18"/>
+        <v>147.52727692358403</v>
+      </c>
+      <c r="AP15" s="5">
+        <f t="shared" si="18"/>
+        <v>150.47782246205571</v>
+      </c>
+      <c r="AQ15" s="5">
+        <f t="shared" si="18"/>
+        <v>153.48737891129682</v>
+      </c>
+      <c r="AR15" s="5">
+        <f t="shared" si="18"/>
+        <v>156.55712648952274</v>
+      </c>
+      <c r="AS15" s="5">
+        <f t="shared" si="18"/>
+        <v>159.6882690193132</v>
       </c>
     </row>
-    <row r="16" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>25</v>
       </c>
@@ -2599,7 +2670,7 @@
         <v>-62</v>
       </c>
       <c r="F16" s="5">
-        <f>AA16-E16-D16-C16</f>
+        <f>AE16-E16-D16-C16</f>
         <v>-4</v>
       </c>
       <c r="G16" s="5">
@@ -2648,228 +2719,236 @@
         <v>-82</v>
       </c>
       <c r="V16" s="5">
-        <v>-45</v>
-      </c>
-      <c r="Y16" s="5">
+        <v>-358</v>
+      </c>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5"/>
+      <c r="Z16" s="5"/>
+      <c r="AC16" s="5">
         <v>165</v>
       </c>
-      <c r="Z16" s="5">
+      <c r="AD16" s="5">
         <v>47</v>
       </c>
-      <c r="AA16" s="5">
+      <c r="AE16" s="5">
         <v>-55</v>
       </c>
-      <c r="AB16" s="5">
+      <c r="AF16" s="5">
         <f>SUM(G16:J16)</f>
         <v>-8</v>
       </c>
-      <c r="AC16" s="5">
+      <c r="AG16" s="5">
         <f>SUM(K16:N16)</f>
         <v>-197</v>
       </c>
-      <c r="AD16" s="5">
+      <c r="AH16" s="5">
         <f>SUM(O16:R16)</f>
         <v>-181</v>
       </c>
-      <c r="AE16" s="5">
+      <c r="AI16" s="5">
         <f>SUM(S16:V16)</f>
-        <v>-264</v>
-      </c>
-      <c r="AF16" s="5">
-        <f t="shared" ref="AF16:AO16" si="21">AE16*1.01</f>
-        <v>-266.64</v>
-      </c>
-      <c r="AG16" s="5">
-        <f t="shared" si="21"/>
-        <v>-269.3064</v>
-      </c>
-      <c r="AH16" s="5">
-        <f t="shared" si="21"/>
-        <v>-271.99946399999999</v>
-      </c>
-      <c r="AI16" s="5">
-        <f t="shared" si="21"/>
-        <v>-274.71945863999997</v>
+        <v>-577</v>
       </c>
       <c r="AJ16" s="5">
-        <f t="shared" si="21"/>
-        <v>-277.46665322639996</v>
+        <f t="shared" ref="AJ16:AS16" si="19">AI16*1.01</f>
+        <v>-582.77</v>
       </c>
       <c r="AK16" s="5">
-        <f t="shared" si="21"/>
-        <v>-280.24131975866396</v>
+        <f t="shared" si="19"/>
+        <v>-588.59770000000003</v>
       </c>
       <c r="AL16" s="5">
-        <f t="shared" si="21"/>
-        <v>-283.04373295625061</v>
+        <f t="shared" si="19"/>
+        <v>-594.48367700000006</v>
       </c>
       <c r="AM16" s="5">
-        <f t="shared" si="21"/>
-        <v>-285.87417028581314</v>
+        <f t="shared" si="19"/>
+        <v>-600.42851377000011</v>
       </c>
       <c r="AN16" s="5">
-        <f t="shared" si="21"/>
-        <v>-288.73291198867128</v>
+        <f t="shared" si="19"/>
+        <v>-606.43279890770009</v>
       </c>
       <c r="AO16" s="5">
-        <f t="shared" si="21"/>
-        <v>-291.62024110855799</v>
+        <f t="shared" si="19"/>
+        <v>-612.4971268967771</v>
+      </c>
+      <c r="AP16" s="5">
+        <f t="shared" si="19"/>
+        <v>-618.62209816574489</v>
+      </c>
+      <c r="AQ16" s="5">
+        <f t="shared" si="19"/>
+        <v>-624.80831914740236</v>
+      </c>
+      <c r="AR16" s="5">
+        <f t="shared" si="19"/>
+        <v>-631.05640233887641</v>
+      </c>
+      <c r="AS16" s="5">
+        <f t="shared" si="19"/>
+        <v>-637.3669663622652</v>
       </c>
     </row>
-    <row r="17" spans="2:142" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:146" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C17" s="8">
-        <f t="shared" ref="C17:V17" si="22">C14-SUM(C15:C16)</f>
+        <f t="shared" ref="C17:V17" si="20">C14-SUM(C15:C16)</f>
         <v>642</v>
       </c>
       <c r="D17" s="8">
+        <f t="shared" si="20"/>
+        <v>821</v>
+      </c>
+      <c r="E17" s="8">
+        <f t="shared" si="20"/>
+        <v>1003</v>
+      </c>
+      <c r="F17" s="8">
+        <f t="shared" si="20"/>
+        <v>1203</v>
+      </c>
+      <c r="G17" s="8">
+        <f t="shared" si="20"/>
+        <v>896</v>
+      </c>
+      <c r="H17" s="8">
+        <f t="shared" si="20"/>
+        <v>497</v>
+      </c>
+      <c r="I17" s="8">
+        <f t="shared" si="20"/>
+        <v>-73</v>
+      </c>
+      <c r="J17" s="8">
+        <f t="shared" si="20"/>
+        <v>-136</v>
+      </c>
+      <c r="K17" s="8">
+        <f t="shared" si="20"/>
+        <v>-127</v>
+      </c>
+      <c r="L17" s="8">
+        <f t="shared" si="20"/>
+        <v>-2</v>
+      </c>
+      <c r="M17" s="8">
+        <f t="shared" si="20"/>
+        <v>257</v>
+      </c>
+      <c r="N17" s="8">
+        <f t="shared" si="20"/>
+        <v>364</v>
+      </c>
+      <c r="O17" s="8">
+        <f t="shared" si="20"/>
+        <v>64</v>
+      </c>
+      <c r="P17" s="8">
+        <f t="shared" si="20"/>
+        <v>299</v>
+      </c>
+      <c r="Q17" s="8">
+        <f t="shared" si="20"/>
+        <v>737</v>
+      </c>
+      <c r="R17" s="8">
+        <f t="shared" si="20"/>
+        <v>889</v>
+      </c>
+      <c r="S17" s="8">
+        <f t="shared" si="20"/>
+        <v>825</v>
+      </c>
+      <c r="T17" s="8">
+        <f t="shared" si="20"/>
+        <v>-74</v>
+      </c>
+      <c r="U17" s="8">
+        <f t="shared" si="20"/>
+        <v>1315</v>
+      </c>
+      <c r="V17" s="8">
+        <f t="shared" si="20"/>
+        <v>2074</v>
+      </c>
+      <c r="W17" s="8"/>
+      <c r="X17" s="8"/>
+      <c r="Y17" s="8"/>
+      <c r="Z17" s="8"/>
+      <c r="AC17" s="8">
+        <f t="shared" ref="AC17:AH17" si="21">AC14-SUM(AC15:AC16)</f>
+        <v>372</v>
+      </c>
+      <c r="AD17" s="8">
+        <f t="shared" si="21"/>
+        <v>1275</v>
+      </c>
+      <c r="AE17" s="8">
+        <f t="shared" si="21"/>
+        <v>3669</v>
+      </c>
+      <c r="AF17" s="8">
+        <f t="shared" si="21"/>
+        <v>1184</v>
+      </c>
+      <c r="AG17" s="8">
+        <f t="shared" si="21"/>
+        <v>492</v>
+      </c>
+      <c r="AH17" s="8">
+        <f t="shared" si="21"/>
+        <v>1989</v>
+      </c>
+      <c r="AI17" s="8">
+        <f t="shared" ref="AI17:AS17" si="22">AI14-SUM(AI15:AI16)</f>
+        <v>4140</v>
+      </c>
+      <c r="AJ17" s="8">
         <f t="shared" si="22"/>
-        <v>821</v>
-      </c>
-      <c r="E17" s="8">
+        <v>9622.6800000000039</v>
+      </c>
+      <c r="AK17" s="8">
         <f t="shared" si="22"/>
-        <v>1003</v>
-      </c>
-      <c r="F17" s="8">
+        <v>12717.852649999995</v>
+      </c>
+      <c r="AL17" s="8">
         <f t="shared" si="22"/>
-        <v>1203</v>
-      </c>
-      <c r="G17" s="8">
+        <v>15025.847517499999</v>
+      </c>
+      <c r="AM17" s="8">
         <f t="shared" si="22"/>
-        <v>896</v>
-      </c>
-      <c r="H17" s="8">
+        <v>17802.744022849995</v>
+      </c>
+      <c r="AN17" s="8">
         <f t="shared" si="22"/>
-        <v>497</v>
-      </c>
-      <c r="I17" s="8">
+        <v>20312.479864810946</v>
+      </c>
+      <c r="AO17" s="8">
         <f t="shared" si="22"/>
-        <v>-73</v>
-      </c>
-      <c r="J17" s="8">
+        <v>21611.326783836346</v>
+      </c>
+      <c r="AP17" s="8">
         <f t="shared" si="22"/>
-        <v>-136</v>
-      </c>
-      <c r="K17" s="8">
+        <v>22984.744295396671</v>
+      </c>
+      <c r="AQ17" s="8">
         <f t="shared" si="22"/>
-        <v>-127</v>
-      </c>
-      <c r="L17" s="8">
+        <v>24436.781352288934</v>
+      </c>
+      <c r="AR17" s="8">
         <f t="shared" si="22"/>
-        <v>-2</v>
-      </c>
-      <c r="M17" s="8">
+        <v>25971.700102488281</v>
+      </c>
+      <c r="AS17" s="8">
         <f t="shared" si="22"/>
-        <v>257</v>
-      </c>
-      <c r="N17" s="8">
-        <f t="shared" si="22"/>
-        <v>364</v>
-      </c>
-      <c r="O17" s="8">
-        <f t="shared" si="22"/>
-        <v>64</v>
-      </c>
-      <c r="P17" s="8">
-        <f t="shared" si="22"/>
-        <v>299</v>
-      </c>
-      <c r="Q17" s="8">
-        <f t="shared" si="22"/>
-        <v>737</v>
-      </c>
-      <c r="R17" s="8">
-        <f t="shared" si="22"/>
-        <v>889</v>
-      </c>
-      <c r="S17" s="8">
-        <f t="shared" si="22"/>
-        <v>825</v>
-      </c>
-      <c r="T17" s="8">
-        <f t="shared" si="22"/>
-        <v>-74</v>
-      </c>
-      <c r="U17" s="8">
-        <f t="shared" si="22"/>
-        <v>1315</v>
-      </c>
-      <c r="V17" s="8">
-        <f t="shared" si="22"/>
-        <v>1697.9647</v>
-      </c>
-      <c r="Y17" s="8">
-        <f t="shared" ref="Y17:AD17" si="23">Y14-SUM(Y15:Y16)</f>
-        <v>372</v>
-      </c>
-      <c r="Z17" s="8">
-        <f t="shared" si="23"/>
-        <v>1275</v>
-      </c>
-      <c r="AA17" s="8">
-        <f t="shared" si="23"/>
-        <v>3669</v>
-      </c>
-      <c r="AB17" s="8">
-        <f t="shared" si="23"/>
-        <v>1184</v>
-      </c>
-      <c r="AC17" s="8">
-        <f t="shared" si="23"/>
-        <v>492</v>
-      </c>
-      <c r="AD17" s="8">
-        <f t="shared" si="23"/>
-        <v>1989</v>
-      </c>
-      <c r="AE17" s="8">
-        <f t="shared" ref="AE17:AO17" si="24">AE14-SUM(AE15:AE16)</f>
-        <v>3763.9647000000041</v>
-      </c>
-      <c r="AF17" s="8">
-        <f t="shared" si="24"/>
-        <v>9445.8559536000048</v>
-      </c>
-      <c r="AG17" s="8">
-        <f t="shared" si="24"/>
-        <v>12727.135046040001</v>
-      </c>
-      <c r="AH17" s="8">
-        <f t="shared" si="24"/>
-        <v>15116.094156593997</v>
-      </c>
-      <c r="AI17" s="8">
-        <f t="shared" si="24"/>
-        <v>17837.044614737766</v>
-      </c>
-      <c r="AJ17" s="8">
-        <f t="shared" si="24"/>
-        <v>20298.425525651903</v>
-      </c>
-      <c r="AK17" s="8">
-        <f t="shared" si="24"/>
-        <v>21588.263371494886</v>
-      </c>
-      <c r="AL17" s="8">
-        <f t="shared" si="24"/>
-        <v>22951.621757000197</v>
-      </c>
-      <c r="AM17" s="8">
-        <f t="shared" si="24"/>
-        <v>24392.472930448424</v>
-      </c>
-      <c r="AN17" s="8">
-        <f t="shared" si="24"/>
-        <v>25914.997602557491</v>
-      </c>
-      <c r="AO17" s="8">
-        <f t="shared" si="24"/>
-        <v>27523.595703284642</v>
+        <v>27593.986915618454</v>
       </c>
     </row>
-    <row r="18" spans="2:142" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>27</v>
       </c>
@@ -2883,7 +2962,7 @@
         <v>82</v>
       </c>
       <c r="F18" s="5">
-        <f>AA18-E18-D18-C18</f>
+        <f>AE18-E18-D18-C18</f>
         <v>229</v>
       </c>
       <c r="G18" s="5">
@@ -2932,76 +3011,79 @@
         <v>153</v>
       </c>
       <c r="V18" s="5">
-        <f t="shared" ref="V18" si="25">V17*0.18</f>
-        <v>305.633646</v>
-      </c>
-      <c r="Y18" s="5">
+        <v>455</v>
+      </c>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="5"/>
+      <c r="AC18" s="5">
         <v>31</v>
       </c>
-      <c r="Z18" s="5">
+      <c r="AD18" s="5">
         <v>-1210</v>
       </c>
-      <c r="AA18" s="5">
+      <c r="AE18" s="5">
         <v>513</v>
       </c>
-      <c r="AB18" s="5">
+      <c r="AF18" s="5">
         <f>SUM(G18:J18)</f>
         <v>-122</v>
       </c>
-      <c r="AC18" s="5">
+      <c r="AG18" s="5">
         <f>SUM(K18:N18)</f>
         <v>-346</v>
       </c>
-      <c r="AD18" s="5">
+      <c r="AH18" s="5">
         <f>SUM(O18:R18)</f>
         <v>381</v>
       </c>
-      <c r="AE18" s="5">
+      <c r="AI18" s="5">
         <f>SUM(S18:V18)</f>
-        <v>-252.366354</v>
-      </c>
-      <c r="AF18" s="5">
-        <f t="shared" ref="AF18:AO18" si="26">AF17*0.12</f>
-        <v>1133.5027144320006</v>
-      </c>
-      <c r="AG18" s="5">
-        <f t="shared" si="26"/>
-        <v>1527.2562055248</v>
-      </c>
-      <c r="AH18" s="5">
-        <f t="shared" si="26"/>
-        <v>1813.9312987912797</v>
-      </c>
-      <c r="AI18" s="5">
-        <f t="shared" si="26"/>
-        <v>2140.4453537685317</v>
+        <v>-103</v>
       </c>
       <c r="AJ18" s="5">
-        <f t="shared" si="26"/>
-        <v>2435.811063078228</v>
+        <f t="shared" ref="AJ18:AS18" si="23">AJ17*0.12</f>
+        <v>1154.7216000000005</v>
       </c>
       <c r="AK18" s="5">
-        <f t="shared" si="26"/>
-        <v>2590.5916045793861</v>
+        <f t="shared" si="23"/>
+        <v>1526.1423179999995</v>
       </c>
       <c r="AL18" s="5">
-        <f t="shared" si="26"/>
-        <v>2754.1946108400234</v>
+        <f t="shared" si="23"/>
+        <v>1803.1017020999998</v>
       </c>
       <c r="AM18" s="5">
-        <f t="shared" si="26"/>
-        <v>2927.0967516538108</v>
+        <f t="shared" si="23"/>
+        <v>2136.3292827419991</v>
       </c>
       <c r="AN18" s="5">
-        <f t="shared" si="26"/>
-        <v>3109.799712306899</v>
+        <f t="shared" si="23"/>
+        <v>2437.4975837773136</v>
       </c>
       <c r="AO18" s="5">
-        <f t="shared" si="26"/>
-        <v>3302.8314843941571</v>
+        <f t="shared" si="23"/>
+        <v>2593.3592140603614</v>
+      </c>
+      <c r="AP18" s="5">
+        <f t="shared" si="23"/>
+        <v>2758.1693154476006</v>
+      </c>
+      <c r="AQ18" s="5">
+        <f t="shared" si="23"/>
+        <v>2932.4137622746721</v>
+      </c>
+      <c r="AR18" s="5">
+        <f t="shared" si="23"/>
+        <v>3116.6040122985937</v>
+      </c>
+      <c r="AS18" s="5">
+        <f t="shared" si="23"/>
+        <v>3311.2784298742145</v>
       </c>
     </row>
-    <row r="19" spans="2:142" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>28</v>
       </c>
@@ -3015,7 +3097,7 @@
         <v>-2</v>
       </c>
       <c r="F19" s="5">
-        <f>AA19-E19-D19-C19</f>
+        <f>AE19-E19-D19-C19</f>
         <v>0</v>
       </c>
       <c r="G19" s="5">
@@ -3064,633 +3146,640 @@
         <v>-10</v>
       </c>
       <c r="V19" s="5">
-        <f t="shared" ref="V19" si="27">-V17*0.01</f>
-        <v>-16.979647</v>
-      </c>
-      <c r="Y19" s="5">
+        <v>-1</v>
+      </c>
+      <c r="W19" s="5"/>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="5"/>
+      <c r="Z19" s="5"/>
+      <c r="AC19" s="5">
         <v>0</v>
       </c>
-      <c r="Z19" s="5">
+      <c r="AD19" s="5">
         <v>-5</v>
       </c>
-      <c r="AA19" s="5">
+      <c r="AE19" s="5">
         <v>-6</v>
       </c>
-      <c r="AB19" s="5">
+      <c r="AF19" s="5">
         <f>SUM(G19:J19)</f>
         <v>-14</v>
       </c>
-      <c r="AC19" s="5">
+      <c r="AG19" s="5">
         <f>SUM(K19:N19)</f>
         <v>-16</v>
       </c>
-      <c r="AD19" s="5">
+      <c r="AH19" s="5">
         <f>SUM(O19:R19)</f>
         <v>-33</v>
       </c>
-      <c r="AE19" s="5">
+      <c r="AI19" s="5">
         <f>SUM(S19:V19)</f>
-        <v>-41.979647</v>
-      </c>
-      <c r="AF19" s="5">
-        <f>-AF17*0.01</f>
-        <v>-94.458559536000053</v>
-      </c>
-      <c r="AG19" s="5">
-        <f t="shared" ref="AG19:AO19" si="28">-AG17*0.01</f>
-        <v>-127.27135046040001</v>
-      </c>
-      <c r="AH19" s="5">
-        <f t="shared" si="28"/>
-        <v>-151.16094156593996</v>
-      </c>
-      <c r="AI19" s="5">
-        <f t="shared" si="28"/>
-        <v>-178.37044614737766</v>
+        <v>-26</v>
       </c>
       <c r="AJ19" s="5">
-        <f t="shared" si="28"/>
-        <v>-202.98425525651902</v>
+        <f>-AJ17*0.01</f>
+        <v>-96.22680000000004</v>
       </c>
       <c r="AK19" s="5">
-        <f t="shared" si="28"/>
-        <v>-215.88263371494887</v>
+        <f t="shared" ref="AK19:AS19" si="24">-AK17*0.01</f>
+        <v>-127.17852649999996</v>
       </c>
       <c r="AL19" s="5">
-        <f t="shared" si="28"/>
-        <v>-229.51621757000197</v>
+        <f t="shared" si="24"/>
+        <v>-150.258475175</v>
       </c>
       <c r="AM19" s="5">
-        <f t="shared" si="28"/>
-        <v>-243.92472930448426</v>
+        <f t="shared" si="24"/>
+        <v>-178.02744022849996</v>
       </c>
       <c r="AN19" s="5">
-        <f t="shared" si="28"/>
-        <v>-259.14997602557492</v>
+        <f t="shared" si="24"/>
+        <v>-203.12479864810948</v>
       </c>
       <c r="AO19" s="5">
-        <f t="shared" si="28"/>
-        <v>-275.23595703284644</v>
+        <f t="shared" si="24"/>
+        <v>-216.11326783836347</v>
+      </c>
+      <c r="AP19" s="5">
+        <f t="shared" si="24"/>
+        <v>-229.84744295396672</v>
+      </c>
+      <c r="AQ19" s="5">
+        <f t="shared" si="24"/>
+        <v>-244.36781352288935</v>
+      </c>
+      <c r="AR19" s="5">
+        <f t="shared" si="24"/>
+        <v>-259.71700102488279</v>
+      </c>
+      <c r="AS19" s="5">
+        <f t="shared" si="24"/>
+        <v>-275.93986915618456</v>
       </c>
     </row>
-    <row r="20" spans="2:142" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:146" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="8">
-        <f t="shared" ref="C20:Q20" si="29">C17-C18-C19</f>
+        <f t="shared" ref="C20:Q20" si="25">C17-C18-C19</f>
         <v>555</v>
       </c>
       <c r="D20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>710</v>
       </c>
       <c r="E20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>923</v>
       </c>
       <c r="F20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>974</v>
       </c>
       <c r="G20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>786</v>
       </c>
       <c r="H20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>447</v>
       </c>
       <c r="I20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>66</v>
       </c>
       <c r="J20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>21</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>-139</v>
       </c>
       <c r="L20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>27</v>
       </c>
       <c r="M20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>299</v>
       </c>
       <c r="N20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>667</v>
       </c>
       <c r="O20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>123</v>
       </c>
       <c r="P20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>265</v>
       </c>
       <c r="Q20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>771</v>
       </c>
       <c r="R20" s="8">
-        <f t="shared" ref="R20:V20" si="30">R17-R18-R19</f>
+        <f t="shared" ref="R20:V20" si="26">R17-R18-R19</f>
         <v>482</v>
       </c>
       <c r="S20" s="8">
+        <f t="shared" si="26"/>
+        <v>709</v>
+      </c>
+      <c r="T20" s="8">
+        <f t="shared" si="26"/>
+        <v>768</v>
+      </c>
+      <c r="U20" s="8">
+        <f t="shared" si="26"/>
+        <v>1172</v>
+      </c>
+      <c r="V20" s="8">
+        <f t="shared" si="26"/>
+        <v>1620</v>
+      </c>
+      <c r="W20" s="8"/>
+      <c r="X20" s="8"/>
+      <c r="Y20" s="8"/>
+      <c r="Z20" s="8"/>
+      <c r="AC20" s="8">
+        <f t="shared" ref="AC20:AH20" si="27">AC17-AC18-AC19</f>
+        <v>341</v>
+      </c>
+      <c r="AD20" s="8">
+        <f t="shared" si="27"/>
+        <v>2490</v>
+      </c>
+      <c r="AE20" s="8">
+        <f t="shared" si="27"/>
+        <v>3162</v>
+      </c>
+      <c r="AF20" s="8">
+        <f t="shared" si="27"/>
+        <v>1320</v>
+      </c>
+      <c r="AG20" s="8">
+        <f t="shared" si="27"/>
+        <v>854</v>
+      </c>
+      <c r="AH20" s="8">
+        <f t="shared" si="27"/>
+        <v>1641</v>
+      </c>
+      <c r="AI20" s="8">
+        <f t="shared" ref="AI20:AS20" si="28">AI17-AI18-AI19</f>
+        <v>4269</v>
+      </c>
+      <c r="AJ20" s="8">
+        <f t="shared" si="28"/>
+        <v>8564.1852000000035</v>
+      </c>
+      <c r="AK20" s="8">
+        <f t="shared" si="28"/>
+        <v>11318.888858499995</v>
+      </c>
+      <c r="AL20" s="8">
+        <f t="shared" si="28"/>
+        <v>13373.004290574998</v>
+      </c>
+      <c r="AM20" s="8">
+        <f t="shared" si="28"/>
+        <v>15844.442180336495</v>
+      </c>
+      <c r="AN20" s="8">
+        <f t="shared" si="28"/>
+        <v>18078.107079681744</v>
+      </c>
+      <c r="AO20" s="8">
+        <f t="shared" si="28"/>
+        <v>19234.080837614347</v>
+      </c>
+      <c r="AP20" s="8">
+        <f t="shared" si="28"/>
+        <v>20456.422422903037</v>
+      </c>
+      <c r="AQ20" s="8">
+        <f t="shared" si="28"/>
+        <v>21748.735403537154</v>
+      </c>
+      <c r="AR20" s="8">
+        <f t="shared" si="28"/>
+        <v>23114.813091214568</v>
+      </c>
+      <c r="AS20" s="8">
+        <f t="shared" si="28"/>
+        <v>24558.648354900422</v>
+      </c>
+      <c r="AT20" s="3">
+        <f>AS20*(1+$AV$25)</f>
+        <v>24313.06187135142</v>
+      </c>
+      <c r="AU20" s="3">
+        <f t="shared" ref="AU20:DF20" si="29">AT20*(1+$AV$25)</f>
+        <v>24069.931252637904</v>
+      </c>
+      <c r="AV20" s="3">
+        <f t="shared" si="29"/>
+        <v>23829.231940111524</v>
+      </c>
+      <c r="AW20" s="3">
+        <f t="shared" si="29"/>
+        <v>23590.939620710407</v>
+      </c>
+      <c r="AX20" s="3">
+        <f t="shared" si="29"/>
+        <v>23355.030224503302</v>
+      </c>
+      <c r="AY20" s="3">
+        <f t="shared" si="29"/>
+        <v>23121.47992225827</v>
+      </c>
+      <c r="AZ20" s="3">
+        <f t="shared" si="29"/>
+        <v>22890.265123035686</v>
+      </c>
+      <c r="BA20" s="3">
+        <f t="shared" si="29"/>
+        <v>22661.362471805329</v>
+      </c>
+      <c r="BB20" s="3">
+        <f t="shared" si="29"/>
+        <v>22434.748847087274</v>
+      </c>
+      <c r="BC20" s="3">
+        <f t="shared" si="29"/>
+        <v>22210.4013586164</v>
+      </c>
+      <c r="BD20" s="3">
+        <f t="shared" si="29"/>
+        <v>21988.297345030234</v>
+      </c>
+      <c r="BE20" s="3">
+        <f t="shared" si="29"/>
+        <v>21768.414371579933</v>
+      </c>
+      <c r="BF20" s="3">
+        <f t="shared" si="29"/>
+        <v>21550.730227864133</v>
+      </c>
+      <c r="BG20" s="3">
+        <f t="shared" si="29"/>
+        <v>21335.222925585491</v>
+      </c>
+      <c r="BH20" s="3">
+        <f t="shared" si="29"/>
+        <v>21121.870696329635</v>
+      </c>
+      <c r="BI20" s="3">
+        <f t="shared" si="29"/>
+        <v>20910.651989366339</v>
+      </c>
+      <c r="BJ20" s="3">
+        <f t="shared" si="29"/>
+        <v>20701.545469472676</v>
+      </c>
+      <c r="BK20" s="3">
+        <f t="shared" si="29"/>
+        <v>20494.530014777949</v>
+      </c>
+      <c r="BL20" s="3">
+        <f t="shared" si="29"/>
+        <v>20289.584714630168</v>
+      </c>
+      <c r="BM20" s="3">
+        <f t="shared" si="29"/>
+        <v>20086.688867483866</v>
+      </c>
+      <c r="BN20" s="3">
+        <f t="shared" si="29"/>
+        <v>19885.821978809028</v>
+      </c>
+      <c r="BO20" s="3">
+        <f t="shared" si="29"/>
+        <v>19686.963759020939</v>
+      </c>
+      <c r="BP20" s="3">
+        <f t="shared" si="29"/>
+        <v>19490.094121430728</v>
+      </c>
+      <c r="BQ20" s="3">
+        <f t="shared" si="29"/>
+        <v>19295.193180216422</v>
+      </c>
+      <c r="BR20" s="3">
+        <f t="shared" si="29"/>
+        <v>19102.241248414259</v>
+      </c>
+      <c r="BS20" s="3">
+        <f t="shared" si="29"/>
+        <v>18911.218835930114</v>
+      </c>
+      <c r="BT20" s="3">
+        <f t="shared" si="29"/>
+        <v>18722.106647570814</v>
+      </c>
+      <c r="BU20" s="3">
+        <f t="shared" si="29"/>
+        <v>18534.885581095106</v>
+      </c>
+      <c r="BV20" s="3">
+        <f t="shared" si="29"/>
+        <v>18349.536725284153</v>
+      </c>
+      <c r="BW20" s="3">
+        <f t="shared" si="29"/>
+        <v>18166.041358031311</v>
+      </c>
+      <c r="BX20" s="3">
+        <f t="shared" si="29"/>
+        <v>17984.380944450997</v>
+      </c>
+      <c r="BY20" s="3">
+        <f t="shared" si="29"/>
+        <v>17804.537135006485</v>
+      </c>
+      <c r="BZ20" s="3">
+        <f t="shared" si="29"/>
+        <v>17626.491763656421</v>
+      </c>
+      <c r="CA20" s="3">
+        <f t="shared" si="29"/>
+        <v>17450.226846019857</v>
+      </c>
+      <c r="CB20" s="3">
+        <f t="shared" si="29"/>
+        <v>17275.72457755966</v>
+      </c>
+      <c r="CC20" s="3">
+        <f t="shared" si="29"/>
+        <v>17102.967331784064</v>
+      </c>
+      <c r="CD20" s="3">
+        <f t="shared" si="29"/>
+        <v>16931.937658466224</v>
+      </c>
+      <c r="CE20" s="3">
+        <f t="shared" si="29"/>
+        <v>16762.618281881561</v>
+      </c>
+      <c r="CF20" s="3">
+        <f t="shared" si="29"/>
+        <v>16594.992099062747</v>
+      </c>
+      <c r="CG20" s="3">
+        <f t="shared" si="29"/>
+        <v>16429.042178072119</v>
+      </c>
+      <c r="CH20" s="3">
+        <f t="shared" si="29"/>
+        <v>16264.751756291398</v>
+      </c>
+      <c r="CI20" s="3">
+        <f t="shared" si="29"/>
+        <v>16102.104238728483</v>
+      </c>
+      <c r="CJ20" s="3">
+        <f t="shared" si="29"/>
+        <v>15941.083196341198</v>
+      </c>
+      <c r="CK20" s="3">
+        <f t="shared" si="29"/>
+        <v>15781.672364377786</v>
+      </c>
+      <c r="CL20" s="3">
+        <f t="shared" si="29"/>
+        <v>15623.855640734007</v>
+      </c>
+      <c r="CM20" s="3">
+        <f t="shared" si="29"/>
+        <v>15467.617084326666</v>
+      </c>
+      <c r="CN20" s="3">
+        <f t="shared" si="29"/>
+        <v>15312.9409134834</v>
+      </c>
+      <c r="CO20" s="3">
+        <f t="shared" si="29"/>
+        <v>15159.811504348567</v>
+      </c>
+      <c r="CP20" s="3">
+        <f t="shared" si="29"/>
+        <v>15008.213389305081</v>
+      </c>
+      <c r="CQ20" s="3">
+        <f t="shared" si="29"/>
+        <v>14858.13125541203</v>
+      </c>
+      <c r="CR20" s="3">
+        <f t="shared" si="29"/>
+        <v>14709.54994285791</v>
+      </c>
+      <c r="CS20" s="3">
+        <f t="shared" si="29"/>
+        <v>14562.454443429331</v>
+      </c>
+      <c r="CT20" s="3">
+        <f t="shared" si="29"/>
+        <v>14416.829898995038</v>
+      </c>
+      <c r="CU20" s="3">
+        <f t="shared" si="29"/>
+        <v>14272.661600005087</v>
+      </c>
+      <c r="CV20" s="3">
+        <f t="shared" si="29"/>
+        <v>14129.934984005036</v>
+      </c>
+      <c r="CW20" s="3">
+        <f t="shared" si="29"/>
+        <v>13988.635634164986</v>
+      </c>
+      <c r="CX20" s="3">
+        <f t="shared" si="29"/>
+        <v>13848.749277823335</v>
+      </c>
+      <c r="CY20" s="3">
+        <f t="shared" si="29"/>
+        <v>13710.261785045102</v>
+      </c>
+      <c r="CZ20" s="3">
+        <f t="shared" si="29"/>
+        <v>13573.159167194652</v>
+      </c>
+      <c r="DA20" s="3">
+        <f t="shared" si="29"/>
+        <v>13437.427575522705</v>
+      </c>
+      <c r="DB20" s="3">
+        <f t="shared" si="29"/>
+        <v>13303.053299767478</v>
+      </c>
+      <c r="DC20" s="3">
+        <f t="shared" si="29"/>
+        <v>13170.022766769804</v>
+      </c>
+      <c r="DD20" s="3">
+        <f t="shared" si="29"/>
+        <v>13038.322539102106</v>
+      </c>
+      <c r="DE20" s="3">
+        <f t="shared" si="29"/>
+        <v>12907.939313711086</v>
+      </c>
+      <c r="DF20" s="3">
+        <f t="shared" si="29"/>
+        <v>12778.859920573974</v>
+      </c>
+      <c r="DG20" s="3">
+        <f t="shared" ref="DG20:EP20" si="30">DF20*(1+$AV$25)</f>
+        <v>12651.071321368234</v>
+      </c>
+      <c r="DH20" s="3">
         <f t="shared" si="30"/>
-        <v>709</v>
-      </c>
-      <c r="T20" s="8">
+        <v>12524.560608154552</v>
+      </c>
+      <c r="DI20" s="3">
         <f t="shared" si="30"/>
-        <v>768</v>
-      </c>
-      <c r="U20" s="8">
+        <v>12399.315002073006</v>
+      </c>
+      <c r="DJ20" s="3">
         <f t="shared" si="30"/>
-        <v>1172</v>
-      </c>
-      <c r="V20" s="8">
+        <v>12275.321852052277</v>
+      </c>
+      <c r="DK20" s="3">
         <f t="shared" si="30"/>
-        <v>1409.3107009999999</v>
-      </c>
-      <c r="Y20" s="8">
-        <f t="shared" ref="Y20:AD20" si="31">Y17-Y18-Y19</f>
-        <v>341</v>
-      </c>
-      <c r="Z20" s="8">
-        <f t="shared" si="31"/>
-        <v>2490</v>
-      </c>
-      <c r="AA20" s="8">
-        <f t="shared" si="31"/>
-        <v>3162</v>
-      </c>
-      <c r="AB20" s="8">
-        <f t="shared" si="31"/>
-        <v>1320</v>
-      </c>
-      <c r="AC20" s="8">
-        <f t="shared" si="31"/>
-        <v>854</v>
-      </c>
-      <c r="AD20" s="8">
-        <f t="shared" si="31"/>
-        <v>1641</v>
-      </c>
-      <c r="AE20" s="8">
-        <f t="shared" ref="AE20:AO20" si="32">AE17-AE18-AE19</f>
-        <v>4058.310701000004</v>
-      </c>
-      <c r="AF20" s="8">
-        <f t="shared" si="32"/>
-        <v>8406.8117987040041</v>
-      </c>
-      <c r="AG20" s="8">
-        <f t="shared" si="32"/>
-        <v>11327.150190975601</v>
-      </c>
-      <c r="AH20" s="8">
-        <f t="shared" si="32"/>
-        <v>13453.323799368658</v>
-      </c>
-      <c r="AI20" s="8">
-        <f t="shared" si="32"/>
-        <v>15874.969707116612</v>
-      </c>
-      <c r="AJ20" s="8">
-        <f t="shared" si="32"/>
-        <v>18065.598717830195</v>
-      </c>
-      <c r="AK20" s="8">
-        <f t="shared" si="32"/>
-        <v>19213.554400630448</v>
-      </c>
-      <c r="AL20" s="8">
-        <f t="shared" si="32"/>
-        <v>20426.943363730177</v>
-      </c>
-      <c r="AM20" s="8">
-        <f t="shared" si="32"/>
-        <v>21709.300908099096</v>
-      </c>
-      <c r="AN20" s="8">
-        <f t="shared" si="32"/>
-        <v>23064.347866276166</v>
-      </c>
-      <c r="AO20" s="8">
-        <f t="shared" si="32"/>
-        <v>24496.000175923335</v>
-      </c>
-      <c r="AP20" s="3">
-        <f>AO20*(1+$AR$25)</f>
-        <v>24251.0401741641</v>
-      </c>
-      <c r="AQ20" s="3">
-        <f t="shared" ref="AQ20:DB20" si="33">AP20*(1+$AR$25)</f>
-        <v>24008.529772422458</v>
-      </c>
-      <c r="AR20" s="3">
-        <f t="shared" si="33"/>
-        <v>23768.444474698234</v>
-      </c>
-      <c r="AS20" s="3">
-        <f t="shared" si="33"/>
-        <v>23530.760029951252</v>
-      </c>
-      <c r="AT20" s="3">
-        <f t="shared" si="33"/>
-        <v>23295.452429651741</v>
-      </c>
-      <c r="AU20" s="3">
-        <f t="shared" si="33"/>
-        <v>23062.497905355223</v>
-      </c>
-      <c r="AV20" s="3">
-        <f t="shared" si="33"/>
-        <v>22831.872926301672</v>
-      </c>
-      <c r="AW20" s="3">
-        <f t="shared" si="33"/>
-        <v>22603.554197038655</v>
-      </c>
-      <c r="AX20" s="3">
-        <f t="shared" si="33"/>
-        <v>22377.518655068267</v>
-      </c>
-      <c r="AY20" s="3">
-        <f t="shared" si="33"/>
-        <v>22153.743468517583</v>
-      </c>
-      <c r="AZ20" s="3">
-        <f t="shared" si="33"/>
-        <v>21932.206033832408</v>
-      </c>
-      <c r="BA20" s="3">
-        <f t="shared" si="33"/>
-        <v>21712.883973494085</v>
-      </c>
-      <c r="BB20" s="3">
-        <f t="shared" si="33"/>
-        <v>21495.755133759143</v>
-      </c>
-      <c r="BC20" s="3">
-        <f t="shared" si="33"/>
-        <v>21280.79758242155</v>
-      </c>
-      <c r="BD20" s="3">
-        <f t="shared" si="33"/>
-        <v>21067.989606597333</v>
-      </c>
-      <c r="BE20" s="3">
-        <f t="shared" si="33"/>
-        <v>20857.309710531361</v>
-      </c>
-      <c r="BF20" s="3">
-        <f t="shared" si="33"/>
-        <v>20648.736613426048</v>
-      </c>
-      <c r="BG20" s="3">
-        <f t="shared" si="33"/>
-        <v>20442.249247291787</v>
-      </c>
-      <c r="BH20" s="3">
-        <f t="shared" si="33"/>
-        <v>20237.826754818871</v>
-      </c>
-      <c r="BI20" s="3">
-        <f t="shared" si="33"/>
-        <v>20035.448487270682</v>
-      </c>
-      <c r="BJ20" s="3">
-        <f t="shared" si="33"/>
-        <v>19835.094002397975</v>
-      </c>
-      <c r="BK20" s="3">
-        <f t="shared" si="33"/>
-        <v>19636.743062373997</v>
-      </c>
-      <c r="BL20" s="3">
-        <f t="shared" si="33"/>
-        <v>19440.375631750256</v>
-      </c>
-      <c r="BM20" s="3">
-        <f t="shared" si="33"/>
-        <v>19245.971875432751</v>
-      </c>
-      <c r="BN20" s="3">
-        <f t="shared" si="33"/>
-        <v>19053.512156678426</v>
-      </c>
-      <c r="BO20" s="3">
-        <f t="shared" si="33"/>
-        <v>18862.977035111642</v>
-      </c>
-      <c r="BP20" s="3">
-        <f t="shared" si="33"/>
-        <v>18674.347264760527</v>
-      </c>
-      <c r="BQ20" s="3">
-        <f t="shared" si="33"/>
-        <v>18487.603792112921</v>
-      </c>
-      <c r="BR20" s="3">
-        <f t="shared" si="33"/>
-        <v>18302.72775419179</v>
-      </c>
-      <c r="BS20" s="3">
-        <f t="shared" si="33"/>
-        <v>18119.700476649872</v>
-      </c>
-      <c r="BT20" s="3">
-        <f t="shared" si="33"/>
-        <v>17938.503471883374</v>
-      </c>
-      <c r="BU20" s="3">
-        <f t="shared" si="33"/>
-        <v>17759.11843716454</v>
-      </c>
-      <c r="BV20" s="3">
-        <f t="shared" si="33"/>
-        <v>17581.527252792894</v>
-      </c>
-      <c r="BW20" s="3">
-        <f t="shared" si="33"/>
-        <v>17405.711980264965</v>
-      </c>
-      <c r="BX20" s="3">
-        <f t="shared" si="33"/>
-        <v>17231.654860462317</v>
-      </c>
-      <c r="BY20" s="3">
-        <f t="shared" si="33"/>
-        <v>17059.338311857693</v>
-      </c>
-      <c r="BZ20" s="3">
-        <f t="shared" si="33"/>
-        <v>16888.744928739117</v>
-      </c>
-      <c r="CA20" s="3">
-        <f t="shared" si="33"/>
-        <v>16719.857479451726</v>
-      </c>
-      <c r="CB20" s="3">
-        <f t="shared" si="33"/>
-        <v>16552.658904657208</v>
-      </c>
-      <c r="CC20" s="3">
-        <f t="shared" si="33"/>
-        <v>16387.132315610637</v>
-      </c>
-      <c r="CD20" s="3">
-        <f t="shared" si="33"/>
-        <v>16223.26099245453</v>
-      </c>
-      <c r="CE20" s="3">
-        <f t="shared" si="33"/>
-        <v>16061.028382529985</v>
-      </c>
-      <c r="CF20" s="3">
-        <f t="shared" si="33"/>
-        <v>15900.418098704686</v>
-      </c>
-      <c r="CG20" s="3">
-        <f t="shared" si="33"/>
-        <v>15741.413917717638</v>
-      </c>
-      <c r="CH20" s="3">
-        <f t="shared" si="33"/>
-        <v>15583.999778540461</v>
-      </c>
-      <c r="CI20" s="3">
-        <f t="shared" si="33"/>
-        <v>15428.159780755057</v>
-      </c>
-      <c r="CJ20" s="3">
-        <f t="shared" si="33"/>
-        <v>15273.878182947507</v>
-      </c>
-      <c r="CK20" s="3">
-        <f t="shared" si="33"/>
-        <v>15121.139401118031</v>
-      </c>
-      <c r="CL20" s="3">
-        <f t="shared" si="33"/>
-        <v>14969.92800710685</v>
-      </c>
-      <c r="CM20" s="3">
-        <f t="shared" si="33"/>
-        <v>14820.228727035781</v>
-      </c>
-      <c r="CN20" s="3">
-        <f t="shared" si="33"/>
-        <v>14672.026439765423</v>
-      </c>
-      <c r="CO20" s="3">
-        <f t="shared" si="33"/>
-        <v>14525.306175367768</v>
-      </c>
-      <c r="CP20" s="3">
-        <f t="shared" si="33"/>
-        <v>14380.053113614091</v>
-      </c>
-      <c r="CQ20" s="3">
-        <f t="shared" si="33"/>
-        <v>14236.25258247795</v>
-      </c>
-      <c r="CR20" s="3">
-        <f t="shared" si="33"/>
-        <v>14093.89005665317</v>
-      </c>
-      <c r="CS20" s="3">
-        <f t="shared" si="33"/>
-        <v>13952.951156086638</v>
-      </c>
-      <c r="CT20" s="3">
-        <f t="shared" si="33"/>
-        <v>13813.421644525772</v>
-      </c>
-      <c r="CU20" s="3">
-        <f t="shared" si="33"/>
-        <v>13675.287428080514</v>
-      </c>
-      <c r="CV20" s="3">
-        <f t="shared" si="33"/>
-        <v>13538.534553799709</v>
-      </c>
-      <c r="CW20" s="3">
-        <f t="shared" si="33"/>
-        <v>13403.149208261711</v>
-      </c>
-      <c r="CX20" s="3">
-        <f t="shared" si="33"/>
-        <v>13269.117716179095</v>
-      </c>
-      <c r="CY20" s="3">
-        <f t="shared" si="33"/>
-        <v>13136.426539017304</v>
-      </c>
-      <c r="CZ20" s="3">
-        <f t="shared" si="33"/>
-        <v>13005.062273627131</v>
-      </c>
-      <c r="DA20" s="3">
-        <f t="shared" si="33"/>
-        <v>12875.01165089086</v>
-      </c>
-      <c r="DB20" s="3">
-        <f t="shared" si="33"/>
-        <v>12746.261534381951</v>
-      </c>
-      <c r="DC20" s="3">
-        <f t="shared" ref="DC20:EL20" si="34">DB20*(1+$AR$25)</f>
-        <v>12618.79891903813</v>
-      </c>
-      <c r="DD20" s="3">
-        <f t="shared" si="34"/>
-        <v>12492.61092984775</v>
-      </c>
-      <c r="DE20" s="3">
-        <f t="shared" si="34"/>
-        <v>12367.684820549272</v>
-      </c>
-      <c r="DF20" s="3">
-        <f t="shared" si="34"/>
-        <v>12244.007972343779</v>
-      </c>
-      <c r="DG20" s="3">
-        <f t="shared" si="34"/>
-        <v>12121.567892620342</v>
-      </c>
-      <c r="DH20" s="3">
-        <f t="shared" si="34"/>
-        <v>12000.352213694137</v>
-      </c>
-      <c r="DI20" s="3">
-        <f t="shared" si="34"/>
-        <v>11880.348691557196</v>
-      </c>
-      <c r="DJ20" s="3">
-        <f t="shared" si="34"/>
-        <v>11761.545204641623</v>
-      </c>
-      <c r="DK20" s="3">
-        <f t="shared" si="34"/>
-        <v>11643.929752595206</v>
+        <v>12152.568633531753</v>
       </c>
       <c r="DL20" s="3">
-        <f t="shared" si="34"/>
-        <v>11527.490455069254</v>
+        <f t="shared" si="30"/>
+        <v>12031.042947196436</v>
       </c>
       <c r="DM20" s="3">
-        <f t="shared" si="34"/>
-        <v>11412.21555051856</v>
+        <f t="shared" si="30"/>
+        <v>11910.732517724471</v>
       </c>
       <c r="DN20" s="3">
-        <f t="shared" si="34"/>
-        <v>11298.093395013375</v>
+        <f t="shared" si="30"/>
+        <v>11791.625192547226</v>
       </c>
       <c r="DO20" s="3">
-        <f t="shared" si="34"/>
-        <v>11185.112461063241</v>
+        <f t="shared" si="30"/>
+        <v>11673.708940621753</v>
       </c>
       <c r="DP20" s="3">
-        <f t="shared" si="34"/>
-        <v>11073.26133645261</v>
+        <f t="shared" si="30"/>
+        <v>11556.971851215536</v>
       </c>
       <c r="DQ20" s="3">
-        <f t="shared" si="34"/>
-        <v>10962.528723088084</v>
+        <f t="shared" si="30"/>
+        <v>11441.402132703381</v>
       </c>
       <c r="DR20" s="3">
-        <f t="shared" si="34"/>
-        <v>10852.903435857203</v>
+        <f t="shared" si="30"/>
+        <v>11326.988111376346</v>
       </c>
       <c r="DS20" s="3">
-        <f t="shared" si="34"/>
-        <v>10744.37440149863</v>
+        <f t="shared" si="30"/>
+        <v>11213.718230262582</v>
       </c>
       <c r="DT20" s="3">
-        <f t="shared" si="34"/>
-        <v>10636.930657483643</v>
+        <f t="shared" si="30"/>
+        <v>11101.581047959957</v>
       </c>
       <c r="DU20" s="3">
-        <f t="shared" si="34"/>
-        <v>10530.561350908807</v>
+        <f t="shared" si="30"/>
+        <v>10990.565237480358</v>
       </c>
       <c r="DV20" s="3">
-        <f t="shared" si="34"/>
-        <v>10425.255737399719</v>
+        <f t="shared" si="30"/>
+        <v>10880.659585105554</v>
       </c>
       <c r="DW20" s="3">
-        <f t="shared" si="34"/>
-        <v>10321.003180025722</v>
+        <f t="shared" si="30"/>
+        <v>10771.852989254498</v>
       </c>
       <c r="DX20" s="3">
-        <f t="shared" si="34"/>
-        <v>10217.793148225464</v>
+        <f t="shared" si="30"/>
+        <v>10664.134459361952</v>
       </c>
       <c r="DY20" s="3">
-        <f t="shared" si="34"/>
-        <v>10115.61521674321</v>
+        <f t="shared" si="30"/>
+        <v>10557.493114768333</v>
       </c>
       <c r="DZ20" s="3">
-        <f t="shared" si="34"/>
-        <v>10014.459064575778</v>
+        <f t="shared" si="30"/>
+        <v>10451.91818362065</v>
       </c>
       <c r="EA20" s="3">
-        <f t="shared" si="34"/>
-        <v>9914.3144739300205</v>
+        <f t="shared" si="30"/>
+        <v>10347.399001784443</v>
       </c>
       <c r="EB20" s="3">
-        <f t="shared" si="34"/>
-        <v>9815.1713291907199</v>
+        <f t="shared" si="30"/>
+        <v>10243.925011766598</v>
       </c>
       <c r="EC20" s="3">
-        <f t="shared" si="34"/>
-        <v>9717.0196158988128</v>
+        <f t="shared" si="30"/>
+        <v>10141.485761648932</v>
       </c>
       <c r="ED20" s="3">
-        <f t="shared" si="34"/>
-        <v>9619.849419739825</v>
+        <f t="shared" si="30"/>
+        <v>10040.070904032442</v>
       </c>
       <c r="EE20" s="3">
-        <f t="shared" si="34"/>
-        <v>9523.6509255424262</v>
+        <f t="shared" si="30"/>
+        <v>9939.6701949921171</v>
       </c>
       <c r="EF20" s="3">
-        <f t="shared" si="34"/>
-        <v>9428.4144162870016</v>
+        <f t="shared" si="30"/>
+        <v>9840.2734930421957</v>
       </c>
       <c r="EG20" s="3">
-        <f t="shared" si="34"/>
-        <v>9334.1302721241318</v>
+        <f t="shared" si="30"/>
+        <v>9741.8707581117742</v>
       </c>
       <c r="EH20" s="3">
-        <f t="shared" si="34"/>
-        <v>9240.7889694028909</v>
+        <f t="shared" si="30"/>
+        <v>9644.4520505306555</v>
       </c>
       <c r="EI20" s="3">
-        <f t="shared" si="34"/>
-        <v>9148.3810797088627</v>
+        <f t="shared" si="30"/>
+        <v>9548.0075300253484</v>
       </c>
       <c r="EJ20" s="3">
-        <f t="shared" si="34"/>
-        <v>9056.8972689117745</v>
+        <f t="shared" si="30"/>
+        <v>9452.5274547250956</v>
       </c>
       <c r="EK20" s="3">
-        <f t="shared" si="34"/>
-        <v>8966.3282962226567</v>
+        <f t="shared" si="30"/>
+        <v>9358.0021801778439</v>
       </c>
       <c r="EL20" s="3">
-        <f t="shared" si="34"/>
-        <v>8876.66501326043</v>
+        <f t="shared" si="30"/>
+        <v>9264.4221583760645</v>
+      </c>
+      <c r="EM20" s="3">
+        <f t="shared" si="30"/>
+        <v>9171.7779367923031</v>
+      </c>
+      <c r="EN20" s="3">
+        <f t="shared" si="30"/>
+        <v>9080.0601574243792</v>
+      </c>
+      <c r="EO20" s="3">
+        <f t="shared" si="30"/>
+        <v>8989.2595558501362</v>
+      </c>
+      <c r="EP20" s="3">
+        <f t="shared" si="30"/>
+        <v>8899.3669602916343</v>
       </c>
     </row>
-    <row r="21" spans="2:142" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>2</v>
       </c>
@@ -3759,40 +3848,28 @@
         <f>1626</f>
         <v>1626</v>
       </c>
-      <c r="Y21" s="5">
-        <v>1622.8</v>
-      </c>
-      <c r="Z21" s="5">
-        <v>1622.8</v>
-      </c>
-      <c r="AA21" s="5">
-        <v>1622.8</v>
-      </c>
-      <c r="AB21" s="5">
-        <v>1622.8</v>
-      </c>
+      <c r="W21" s="5"/>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="5"/>
       <c r="AC21" s="5">
         <v>1622.8</v>
       </c>
       <c r="AD21" s="5">
-        <f t="shared" ref="AD21" si="35">1620.5</f>
+        <v>1622.8</v>
+      </c>
+      <c r="AE21" s="5">
+        <v>1622.8</v>
+      </c>
+      <c r="AF21" s="5">
+        <v>1622.8</v>
+      </c>
+      <c r="AG21" s="5">
+        <v>1622.8</v>
+      </c>
+      <c r="AH21" s="5">
+        <f t="shared" ref="AH21" si="31">1620.5</f>
         <v>1620.5</v>
-      </c>
-      <c r="AE21" s="5">
-        <f>1626</f>
-        <v>1626</v>
-      </c>
-      <c r="AF21" s="5">
-        <f>1626</f>
-        <v>1626</v>
-      </c>
-      <c r="AG21" s="5">
-        <f>1626</f>
-        <v>1626</v>
-      </c>
-      <c r="AH21" s="5">
-        <f>1626</f>
-        <v>1626</v>
       </c>
       <c r="AI21" s="5">
         <f>1626</f>
@@ -3822,161 +3899,181 @@
         <f>1626</f>
         <v>1626</v>
       </c>
+      <c r="AP21" s="5">
+        <f>1626</f>
+        <v>1626</v>
+      </c>
+      <c r="AQ21" s="5">
+        <f>1626</f>
+        <v>1626</v>
+      </c>
+      <c r="AR21" s="5">
+        <f>1626</f>
+        <v>1626</v>
+      </c>
+      <c r="AS21" s="5">
+        <f>1626</f>
+        <v>1626</v>
+      </c>
     </row>
-    <row r="22" spans="2:142" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>30</v>
       </c>
       <c r="C22" s="7">
-        <f t="shared" ref="C22:Q22" si="36">C20/C21</f>
+        <f t="shared" ref="C22:Q22" si="32">C20/C21</f>
         <v>0.3420014789253143</v>
       </c>
       <c r="D22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>0.43751540547202367</v>
       </c>
       <c r="E22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>0.56877002711363078</v>
       </c>
       <c r="F22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>0.60019719004190286</v>
       </c>
       <c r="G22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>0.48434804042395863</v>
       </c>
       <c r="H22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>0.27544983978309096</v>
       </c>
       <c r="I22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>4.0670446142469806E-2</v>
       </c>
       <c r="J22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>1.2940596499876757E-2</v>
       </c>
       <c r="K22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>-8.5654424451565195E-2</v>
       </c>
       <c r="L22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>1.6637909785555832E-2</v>
       </c>
       <c r="M22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>0.18424944540300717</v>
       </c>
       <c r="N22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>0.41101799359132363</v>
       </c>
       <c r="O22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>7.5794922356421005E-2</v>
       </c>
       <c r="P22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>0.16329800345082573</v>
       </c>
       <c r="Q22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="32"/>
         <v>0.47510475720976092</v>
       </c>
       <c r="R22" s="7">
-        <f t="shared" ref="R22:V22" si="37">R20/R21</f>
+        <f t="shared" ref="R22:V22" si="33">R20/R21</f>
         <v>0.29743906201789572</v>
       </c>
       <c r="S22" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>0.437519284171552</v>
       </c>
       <c r="T22" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>0.47319778188539741</v>
       </c>
       <c r="U22" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="33"/>
         <v>0.72078720787207873</v>
       </c>
       <c r="V22" s="7">
-        <f t="shared" si="37"/>
-        <v>0.86673474846248455</v>
-      </c>
-      <c r="Y22" s="7">
-        <f t="shared" ref="Y22:AD22" si="38">Y20/Y21</f>
+        <f t="shared" si="33"/>
+        <v>0.99630996309963105</v>
+      </c>
+      <c r="W22" s="7"/>
+      <c r="X22" s="7"/>
+      <c r="Y22" s="7"/>
+      <c r="Z22" s="7"/>
+      <c r="AC22" s="7">
+        <f t="shared" ref="AC22:AH22" si="34">AC20/AC21</f>
         <v>0.21013063840276067</v>
       </c>
-      <c r="Z22" s="7">
-        <f t="shared" si="38"/>
+      <c r="AD22" s="7">
+        <f t="shared" si="34"/>
         <v>1.5343850135568153</v>
       </c>
-      <c r="AA22" s="7">
-        <f t="shared" si="38"/>
+      <c r="AE22" s="7">
+        <f t="shared" si="34"/>
         <v>1.9484841015528716</v>
       </c>
-      <c r="AB22" s="7">
-        <f t="shared" si="38"/>
+      <c r="AF22" s="7">
+        <f t="shared" si="34"/>
         <v>0.81340892284939614</v>
       </c>
-      <c r="AC22" s="7">
-        <f t="shared" si="38"/>
+      <c r="AG22" s="7">
+        <f t="shared" si="34"/>
         <v>0.52625092432832143</v>
       </c>
-      <c r="AD22" s="7">
-        <f t="shared" si="38"/>
+      <c r="AH22" s="7">
+        <f t="shared" si="34"/>
         <v>1.0126504165381056</v>
       </c>
-      <c r="AE22" s="7">
-        <f t="shared" ref="AE22:AO22" si="39">AE20/AE21</f>
-        <v>2.4958860399754021</v>
-      </c>
-      <c r="AF22" s="7">
-        <f t="shared" si="39"/>
-        <v>5.1702409586125491</v>
-      </c>
-      <c r="AG22" s="7">
-        <f t="shared" si="39"/>
-        <v>6.9662670301202958</v>
-      </c>
-      <c r="AH22" s="7">
-        <f t="shared" si="39"/>
-        <v>8.2738768753804788</v>
-      </c>
       <c r="AI22" s="7">
-        <f t="shared" si="39"/>
-        <v>9.7632040019167352</v>
+        <f t="shared" ref="AI22:AS22" si="35">AI20/AI21</f>
+        <v>2.6254612546125462</v>
       </c>
       <c r="AJ22" s="7">
-        <f t="shared" si="39"/>
-        <v>11.110454316008729</v>
+        <f t="shared" si="35"/>
+        <v>5.2670265682656847</v>
       </c>
       <c r="AK22" s="7">
-        <f t="shared" si="39"/>
-        <v>11.816454120928935</v>
+        <f t="shared" si="35"/>
+        <v>6.9611862598400949</v>
       </c>
       <c r="AL22" s="7">
-        <f t="shared" si="39"/>
-        <v>12.562695795652015</v>
+        <f t="shared" si="35"/>
+        <v>8.2244798835024593</v>
       </c>
       <c r="AM22" s="7">
-        <f t="shared" si="39"/>
-        <v>13.351353572016665</v>
+        <f t="shared" si="35"/>
+        <v>9.7444293852007959</v>
       </c>
       <c r="AN22" s="7">
-        <f t="shared" si="39"/>
-        <v>14.184715784917691</v>
+        <f t="shared" si="35"/>
+        <v>11.118147035474628</v>
       </c>
       <c r="AO22" s="7">
-        <f t="shared" si="39"/>
-        <v>15.065190760100451</v>
+        <f t="shared" si="35"/>
+        <v>11.829078005912882</v>
+      </c>
+      <c r="AP22" s="7">
+        <f t="shared" si="35"/>
+        <v>12.580825598341351</v>
+      </c>
+      <c r="AQ22" s="7">
+        <f t="shared" si="35"/>
+        <v>13.375606029235643</v>
+      </c>
+      <c r="AR22" s="7">
+        <f t="shared" si="35"/>
+        <v>14.215752208619046</v>
+      </c>
+      <c r="AS22" s="7">
+        <f t="shared" si="35"/>
+        <v>15.103719775461514</v>
       </c>
     </row>
-    <row r="24" spans="2:142" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>45</v>
       </c>
@@ -3989,149 +4086,153 @@
         <v>0.70885341074020314</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" ref="H24:R24" si="40">H3/D3-1</f>
+        <f t="shared" ref="H24:R24" si="36">H3/D3-1</f>
         <v>0.70129870129870131</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>0.29028518432645489</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>0.16017405719021971</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>-9.0708340411075228E-2</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>-0.18183206106870231</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>4.2228212039532753E-2</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>0.10162529023039824</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>2.2417336073230043E-2</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>8.882254151894009E-2</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>0.17568965517241386</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>0.24156939040207526</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" ref="S24" si="41">S3/O3-1</f>
+        <f t="shared" ref="S24" si="37">S3/O3-1</f>
         <v>0.35903526402338759</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" ref="T24" si="42">T3/P3-1</f>
+        <f t="shared" ref="T24" si="38">T3/P3-1</f>
         <v>0.31705227077977716</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" ref="U24" si="43">U3/Q3-1</f>
+        <f t="shared" ref="U24" si="39">U3/Q3-1</f>
         <v>0.35591728992520899</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" ref="V24" si="44">V3/R3-1</f>
-        <v>0.27</v>
-      </c>
+        <f t="shared" ref="V24" si="40">V3/R3-1</f>
+        <v>0.34108122225124049</v>
+      </c>
+      <c r="W24" s="9"/>
+      <c r="X24" s="9"/>
       <c r="Y24" s="9"/>
-      <c r="Z24" s="9">
-        <f>Z3/Y3-1</f>
+      <c r="Z24" s="9"/>
+      <c r="AC24" s="9"/>
+      <c r="AD24" s="9">
+        <f>AD3/AC3-1</f>
         <v>0.45045312732134901</v>
       </c>
-      <c r="AA24" s="9">
-        <f t="shared" ref="AA24:AO24" si="45">AA3/Z3-1</f>
+      <c r="AE24" s="9">
+        <f t="shared" ref="AE24:AS24" si="41">AE3/AD3-1</f>
         <v>0.68329406944586712</v>
       </c>
-      <c r="AB24" s="9">
-        <f t="shared" si="45"/>
+      <c r="AF24" s="9">
+        <f t="shared" si="41"/>
         <v>0.43610806863818907</v>
       </c>
-      <c r="AC24" s="9">
-        <f t="shared" si="45"/>
+      <c r="AG24" s="9">
+        <f t="shared" si="41"/>
         <v>-3.9023770179229644E-2</v>
       </c>
-      <c r="AD24" s="9">
-        <f t="shared" si="45"/>
+      <c r="AH24" s="9">
+        <f t="shared" si="41"/>
         <v>0.13690476190476186</v>
       </c>
-      <c r="AE24" s="9">
-        <f t="shared" si="45"/>
-        <v>0.32226720961799504</v>
-      </c>
-      <c r="AF24" s="9">
-        <f t="shared" si="45"/>
-        <v>0.22999999999999998</v>
-      </c>
-      <c r="AG24" s="9">
-        <f t="shared" si="45"/>
+      <c r="AI24" s="9">
+        <f t="shared" si="41"/>
+        <v>0.3433779329067288</v>
+      </c>
+      <c r="AJ24" s="9">
+        <f t="shared" si="41"/>
+        <v>0.25</v>
+      </c>
+      <c r="AK24" s="9">
+        <f t="shared" si="41"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AH24" s="9">
-        <f t="shared" si="45"/>
+      <c r="AL24" s="9">
+        <f t="shared" si="41"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AI24" s="9">
-        <f t="shared" si="45"/>
+      <c r="AM24" s="9">
+        <f t="shared" si="41"/>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="AJ24" s="9">
-        <f t="shared" si="45"/>
+      <c r="AN24" s="9">
+        <f t="shared" si="41"/>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="AK24" s="9">
-        <f t="shared" si="45"/>
+      <c r="AO24" s="9">
+        <f t="shared" si="41"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AL24" s="9">
-        <f t="shared" si="45"/>
+      <c r="AP24" s="9">
+        <f t="shared" si="41"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AM24" s="9">
-        <f t="shared" si="45"/>
+      <c r="AQ24" s="9">
+        <f t="shared" si="41"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AN24" s="9">
-        <f t="shared" si="45"/>
+      <c r="AR24" s="9">
+        <f t="shared" si="41"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AO24" s="9">
-        <f t="shared" si="45"/>
+      <c r="AS24" s="9">
+        <f t="shared" si="41"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
-    <row r="25" spans="2:142" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>46</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:F25" si="46">C7/C3</f>
+        <f t="shared" ref="C25:F25" si="42">C7/C3</f>
         <v>0.46066763425253993</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>0.47532467532467532</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>0.48365406909343844</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>0.50269374222958974</v>
       </c>
       <c r="G25" s="9">
@@ -4139,158 +4240,162 @@
         <v>0.4786818413453372</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" ref="H25:R25" si="47">H7/H3</f>
+        <f t="shared" ref="H25:R25" si="43">H7/H3</f>
         <v>0.46229007633587788</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>0.42300089847259659</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>0.42918378281836045</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>0.44068746497291239</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>0.4558686322075014</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>0.4736206896551724</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>0.47195201037613488</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>0.46775077653937513</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>0.49083119108826051</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>0.50139316615339491</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>0.50692086706711936</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" ref="S25:V25" si="48">S7/S3</f>
+        <f t="shared" ref="S25:V25" si="44">S7/S3</f>
         <v>0.50228556063457919</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="44"/>
         <v>0.39804814573845154</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="44"/>
         <v>0.51698031581224313</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="48"/>
-        <v>0.54500000000000004</v>
-      </c>
-      <c r="Y25" s="9">
-        <f t="shared" ref="Y25" si="49">Y7/Y3</f>
+        <f t="shared" si="44"/>
+        <v>0.54303797468354431</v>
+      </c>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="9"/>
+      <c r="Z25" s="9"/>
+      <c r="AC25" s="9">
+        <f t="shared" ref="AC25" si="45">AC7/AC3</f>
         <v>0.42608824840291187</v>
       </c>
-      <c r="Z25" s="9">
-        <f t="shared" ref="Z25:AO25" si="50">Z7/Z3</f>
+      <c r="AD25" s="9">
+        <f t="shared" ref="AD25:AS25" si="46">AD7/AD3</f>
         <v>0.44525248386766364</v>
       </c>
-      <c r="AA25" s="9">
-        <f t="shared" si="50"/>
+      <c r="AE25" s="9">
+        <f t="shared" si="46"/>
         <v>0.48247535596933189</v>
       </c>
-      <c r="AB25" s="9">
-        <f t="shared" si="50"/>
+      <c r="AF25" s="9">
+        <f t="shared" si="46"/>
         <v>0.4492606245498072</v>
       </c>
-      <c r="AC25" s="9">
-        <f t="shared" si="50"/>
+      <c r="AG25" s="9">
+        <f t="shared" si="46"/>
         <v>0.46119929453262787</v>
       </c>
-      <c r="AD25" s="9">
-        <f t="shared" si="50"/>
+      <c r="AH25" s="9">
+        <f t="shared" si="46"/>
         <v>0.49350397517936784</v>
       </c>
-      <c r="AE25" s="9">
-        <f t="shared" si="50"/>
-        <v>0.49495975909423945</v>
-      </c>
-      <c r="AF25" s="9">
-        <f t="shared" si="50"/>
+      <c r="AI25" s="9">
+        <f t="shared" si="46"/>
+        <v>0.49516441005802708</v>
+      </c>
+      <c r="AJ25" s="9">
+        <f t="shared" si="46"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="AG25" s="9">
-        <f t="shared" si="50"/>
+      <c r="AK25" s="9">
+        <f t="shared" si="46"/>
         <v>0.56999999999999995</v>
       </c>
-      <c r="AH25" s="9">
-        <f t="shared" si="50"/>
+      <c r="AL25" s="9">
+        <f t="shared" si="46"/>
         <v>0.57999999999999996</v>
       </c>
-      <c r="AI25" s="9">
-        <f t="shared" si="50"/>
-        <v>0.59000000000000008</v>
-      </c>
-      <c r="AJ25" s="9">
-        <f t="shared" si="50"/>
+      <c r="AM25" s="9">
+        <f t="shared" si="46"/>
+        <v>0.59</v>
+      </c>
+      <c r="AN25" s="9">
+        <f t="shared" si="46"/>
         <v>0.6</v>
       </c>
-      <c r="AK25" s="9">
-        <f t="shared" si="50"/>
+      <c r="AO25" s="9">
+        <f t="shared" si="46"/>
         <v>0.6</v>
       </c>
-      <c r="AL25" s="9">
-        <f t="shared" si="50"/>
+      <c r="AP25" s="9">
+        <f t="shared" si="46"/>
         <v>0.6</v>
       </c>
-      <c r="AM25" s="9">
-        <f t="shared" si="50"/>
+      <c r="AQ25" s="9">
+        <f t="shared" si="46"/>
         <v>0.6</v>
       </c>
-      <c r="AN25" s="9">
-        <f t="shared" si="50"/>
+      <c r="AR25" s="9">
+        <f t="shared" si="46"/>
         <v>0.6</v>
       </c>
-      <c r="AO25" s="9">
-        <f t="shared" si="50"/>
+      <c r="AS25" s="9">
+        <f t="shared" si="46"/>
         <v>0.6</v>
       </c>
-      <c r="AQ25" t="s">
+      <c r="AU25" t="s">
         <v>54</v>
       </c>
-      <c r="AR25" s="9">
+      <c r="AV25" s="9">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="26" spans="2:142" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>47</v>
       </c>
       <c r="C26" s="9">
-        <f t="shared" ref="C26:F26" si="51">(C3-C4)/C3</f>
+        <f t="shared" ref="C26:F26" si="47">(C3-C4)/C3</f>
         <v>0.46066763425253993</v>
       </c>
       <c r="D26" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="47"/>
         <v>0.47532467532467532</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="47"/>
         <v>0.48365406909343844</v>
       </c>
       <c r="F26" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="47"/>
         <v>0.50269374222958974</v>
       </c>
       <c r="G26" s="9">
@@ -4298,111 +4403,115 @@
         <v>0.51027688126380155</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" ref="H26:R26" si="52">(H3-H4)/H3</f>
+        <f t="shared" ref="H26:R26" si="48">(H3-H4)/H3</f>
         <v>0.52442748091603053</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>0.49703504043126684</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>0.5083050544740132</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>0.49766486082570521</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>0.49542825153946629</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>0.5098275862068965</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>0.50680933852140075</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>0.5097752603690846</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>0.53041988003427587</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>0.53556239917876525</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>0.53982763123530952</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" ref="S26:V26" si="53">(S3-S4)/S3</f>
+        <f t="shared" ref="S26:V26" si="49">(S3-S4)/S3</f>
         <v>0.53603119118042486</v>
       </c>
       <c r="T26" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>0.43188028627195835</v>
       </c>
       <c r="U26" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>0.54510058403633999</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" si="53"/>
-        <v>0.57276161206540221</v>
-      </c>
-      <c r="Y26" s="9">
-        <f t="shared" ref="Y26" si="54">(Y3-Y4)/Y3</f>
+        <f t="shared" si="49"/>
+        <v>0.56835443037974687</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AC26" s="9">
+        <f t="shared" ref="AC26" si="50">(AC3-AC4)/AC3</f>
         <v>0.42608824840291187</v>
       </c>
-      <c r="Z26" s="9">
-        <f t="shared" ref="Z26:AE26" si="55">(Z3-Z4)/Z3</f>
+      <c r="AD26" s="9">
+        <f t="shared" ref="AD26:AI26" si="51">(AD3-AD4)/AD3</f>
         <v>0.44525248386766364</v>
       </c>
-      <c r="AA26" s="9">
-        <f t="shared" si="55"/>
+      <c r="AE26" s="9">
+        <f t="shared" si="51"/>
         <v>0.48247535596933189</v>
       </c>
-      <c r="AB26" s="9">
-        <f t="shared" si="55"/>
+      <c r="AF26" s="9">
+        <f t="shared" si="51"/>
         <v>0.51061395703571888</v>
       </c>
-      <c r="AC26" s="9">
-        <f t="shared" si="55"/>
+      <c r="AG26" s="9">
+        <f t="shared" si="51"/>
         <v>0.5027336860670194</v>
       </c>
-      <c r="AD26" s="9">
-        <f t="shared" si="55"/>
+      <c r="AH26" s="9">
+        <f t="shared" si="51"/>
         <v>0.53019197207678881</v>
       </c>
-      <c r="AE26" s="9">
-        <f t="shared" si="55"/>
-        <v>0.52549239968957029</v>
-      </c>
-      <c r="AF26" s="9"/>
-      <c r="AG26" s="9"/>
-      <c r="AH26" s="9"/>
-      <c r="AI26" s="9"/>
+      <c r="AI26" s="9">
+        <f t="shared" si="51"/>
+        <v>0.52492854874563355</v>
+      </c>
       <c r="AJ26" s="9"/>
       <c r="AK26" s="9"/>
       <c r="AL26" s="9"/>
       <c r="AM26" s="9"/>
       <c r="AN26" s="9"/>
       <c r="AO26" s="9"/>
-      <c r="AQ26" t="s">
+      <c r="AP26" s="9"/>
+      <c r="AQ26" s="9"/>
+      <c r="AR26" s="9"/>
+      <c r="AS26" s="9"/>
+      <c r="AU26" t="s">
         <v>55</v>
       </c>
-      <c r="AR26" s="9">
+      <c r="AV26" s="9">
         <v>0.06</v>
       </c>
     </row>
-    <row r="27" spans="2:142" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>48</v>
       </c>
@@ -4415,139 +4524,143 @@
         <v>0.73770491803278682</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" ref="H27:R27" si="56">H8/D8-1</f>
+        <f t="shared" ref="H27:R27" si="52">H8/D8-1</f>
         <v>0.9726858877086495</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>0.67189542483660136</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>0.68434032059186189</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>0.33113207547169821</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>0.1100000000000001</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>0.17826426896012504</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>0.10614934114202046</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>8.0793763288447895E-2</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>9.7020097020096951E-2</v>
       </c>
       <c r="Q27" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>8.5600530856005275E-2</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="52"/>
         <v>0.13302448709463932</v>
       </c>
       <c r="S27" s="9">
-        <f t="shared" ref="S27:S28" si="57">S8/O8-1</f>
+        <f t="shared" ref="S27:S28" si="53">S8/O8-1</f>
         <v>0.1331147540983606</v>
       </c>
       <c r="T27" s="9">
-        <f t="shared" ref="T27:T28" si="58">T8/P8-1</f>
+        <f t="shared" ref="T27:T28" si="54">T8/P8-1</f>
         <v>0.19646241313960844</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" ref="U27:U28" si="59">U8/Q8-1</f>
+        <f t="shared" ref="U27:U28" si="55">U8/Q8-1</f>
         <v>0.30745721271393633</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" ref="V27:V28" si="60">V8/R8-1</f>
-        <v>0.28000000000000003</v>
-      </c>
+        <f t="shared" ref="V27:V28" si="56">V8/R8-1</f>
+        <v>0.36098130841121501</v>
+      </c>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
       <c r="Y27" s="9"/>
-      <c r="Z27" s="9">
-        <f>Z8/Y8-1</f>
+      <c r="Z27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9">
+        <f>AD8/AC8-1</f>
         <v>0.28183581124757606</v>
       </c>
-      <c r="AA27" s="9">
-        <f t="shared" ref="AA27:AO27" si="61">AA8/Z8-1</f>
+      <c r="AE27" s="9">
+        <f t="shared" ref="AE27:AS27" si="57">AE8/AD8-1</f>
         <v>0.43469490670700961</v>
       </c>
-      <c r="AB27" s="9">
-        <f t="shared" si="61"/>
+      <c r="AF27" s="9">
+        <f t="shared" si="57"/>
         <v>0.75922671353251325</v>
       </c>
-      <c r="AC27" s="9">
-        <f t="shared" si="61"/>
+      <c r="AG27" s="9">
+        <f t="shared" si="57"/>
         <v>0.17322677322677316</v>
       </c>
-      <c r="AD27" s="9">
-        <f t="shared" si="61"/>
+      <c r="AH27" s="9">
+        <f t="shared" si="57"/>
         <v>9.9455040871934575E-2</v>
       </c>
-      <c r="AE27" s="9">
-        <f t="shared" si="61"/>
-        <v>0.23177819083023543</v>
-      </c>
-      <c r="AF27" s="9">
-        <f t="shared" si="61"/>
-        <v>0.1399999999999999</v>
-      </c>
-      <c r="AG27" s="9">
-        <f t="shared" si="61"/>
+      <c r="AI27" s="9">
+        <f t="shared" si="57"/>
+        <v>0.25325278810408913</v>
+      </c>
+      <c r="AJ27" s="9">
+        <f t="shared" si="57"/>
+        <v>0.17999999999999994</v>
+      </c>
+      <c r="AK27" s="9">
+        <f t="shared" si="57"/>
         <v>8.0000000000000071E-2</v>
       </c>
-      <c r="AH27" s="9">
-        <f t="shared" si="61"/>
+      <c r="AL27" s="9">
+        <f t="shared" si="57"/>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="AI27" s="9">
-        <f t="shared" si="61"/>
+      <c r="AM27" s="9">
+        <f t="shared" si="57"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AJ27" s="9">
-        <f t="shared" si="61"/>
+      <c r="AN27" s="9">
+        <f t="shared" si="57"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AK27" s="9">
-        <f t="shared" si="61"/>
+      <c r="AO27" s="9">
+        <f t="shared" si="57"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AL27" s="9">
-        <f t="shared" si="61"/>
+      <c r="AP27" s="9">
+        <f t="shared" si="57"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AM27" s="9">
-        <f t="shared" si="61"/>
+      <c r="AQ27" s="9">
+        <f t="shared" si="57"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AN27" s="9">
-        <f t="shared" si="61"/>
+      <c r="AR27" s="9">
+        <f t="shared" si="57"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AO27" s="9">
-        <f t="shared" si="61"/>
+      <c r="AS27" s="9">
+        <f t="shared" si="57"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AQ27" t="s">
+      <c r="AU27" t="s">
         <v>56</v>
       </c>
-      <c r="AR27" s="5">
-        <f>NPV(AR26,AE20:EL20)</f>
-        <v>302620.97708222189</v>
+      <c r="AV27" s="5">
+        <f>NPV(AV26,AJ20:EP20)</f>
+        <v>317396.68923996866</v>
       </c>
     </row>
-    <row r="28" spans="2:142" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>49</v>
       </c>
@@ -4560,156 +4673,160 @@
         <v>0.87147335423197503</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" ref="H28:R28" si="62">H9/D9-1</f>
+        <f t="shared" ref="H28:R28" si="58">H9/D9-1</f>
         <v>0.73607038123167157</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>0.4813829787234043</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>0.43203883495145634</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>-2.010050251256279E-2</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>-7.6013513513513487E-2</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>3.4111310592459532E-2</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>9.1525423728813449E-2</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>5.9829059829059839E-2</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>0.1882998171846435</v>
       </c>
       <c r="Q28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>0.25173611111111116</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>0.22981366459627339</v>
       </c>
       <c r="S28" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="53"/>
         <v>0.42903225806451606</v>
       </c>
       <c r="T28" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="54"/>
         <v>0.52461538461538471</v>
       </c>
       <c r="U28" s="9">
+        <f t="shared" si="55"/>
+        <v>0.48266296809986131</v>
+      </c>
+      <c r="V28" s="9">
+        <f t="shared" si="56"/>
+        <v>0.51262626262626254</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9">
+        <f>AD9/AC9-1</f>
+        <v>0.32666666666666666</v>
+      </c>
+      <c r="AE28" s="9">
+        <f t="shared" ref="AE28:AS28" si="59">AE9/AD9-1</f>
+        <v>0.45527638190954778</v>
+      </c>
+      <c r="AF28" s="9">
         <f t="shared" si="59"/>
-        <v>0.48266296809986131</v>
-      </c>
-      <c r="V28" s="9">
-        <f t="shared" si="60"/>
-        <v>0.39999999999999991</v>
-      </c>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9">
-        <f>Z9/Y9-1</f>
-        <v>0.32666666666666666</v>
-      </c>
-      <c r="AA28" s="9">
-        <f t="shared" ref="AA28:AO28" si="63">AA9/Z9-1</f>
-        <v>0.45527638190954778</v>
-      </c>
-      <c r="AB28" s="9">
-        <f t="shared" si="63"/>
         <v>0.61325966850828739</v>
       </c>
-      <c r="AC28" s="9">
-        <f t="shared" si="63"/>
+      <c r="AG28" s="9">
+        <f t="shared" si="59"/>
         <v>6.8493150684931781E-3</v>
       </c>
-      <c r="AD28" s="9">
-        <f t="shared" si="63"/>
+      <c r="AH28" s="9">
+        <f t="shared" si="59"/>
         <v>0.18324829931972797</v>
       </c>
-      <c r="AE28" s="9">
-        <f t="shared" si="63"/>
-        <v>0.4569888609414301</v>
-      </c>
-      <c r="AF28" s="9">
-        <f t="shared" si="63"/>
-        <v>0.17999999999999994</v>
-      </c>
-      <c r="AG28" s="9">
-        <f t="shared" si="63"/>
-        <v>9.000000000000008E-2</v>
-      </c>
-      <c r="AH28" s="9">
-        <f t="shared" si="63"/>
-        <v>6.0000000000000053E-2</v>
-      </c>
       <c r="AI28" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="59"/>
+        <v>0.4890406036651096</v>
+      </c>
+      <c r="AJ28" s="9">
+        <f t="shared" si="59"/>
+        <v>0.25</v>
+      </c>
+      <c r="AK28" s="9">
+        <f t="shared" si="59"/>
+        <v>0.1399999999999999</v>
+      </c>
+      <c r="AL28" s="9">
+        <f t="shared" si="59"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="AM28" s="9">
+        <f t="shared" si="59"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AJ28" s="9">
-        <f t="shared" si="63"/>
+      <c r="AN28" s="9">
+        <f t="shared" si="59"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AK28" s="9">
-        <f t="shared" si="63"/>
+      <c r="AO28" s="9">
+        <f t="shared" si="59"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AL28" s="9">
-        <f t="shared" si="63"/>
+      <c r="AP28" s="9">
+        <f t="shared" si="59"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AM28" s="9">
-        <f t="shared" si="63"/>
+      <c r="AQ28" s="9">
+        <f t="shared" si="59"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AN28" s="9">
-        <f t="shared" si="63"/>
+      <c r="AR28" s="9">
+        <f t="shared" si="59"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AO28" s="9">
-        <f t="shared" si="63"/>
+      <c r="AS28" s="9">
+        <f t="shared" si="59"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AQ28" t="s">
+      <c r="AU28" t="s">
         <v>57</v>
       </c>
-      <c r="AR28" s="5">
+      <c r="AV28" s="5">
         <f>Main!D8</f>
-        <v>4023</v>
+        <v>7330</v>
       </c>
     </row>
-    <row r="29" spans="2:142" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>50</v>
       </c>
       <c r="C29" s="9">
-        <f t="shared" ref="C29:F29" si="64">C9/C3</f>
+        <f t="shared" ref="C29:F29" si="60">C9/C3</f>
         <v>9.2597968069666178E-2</v>
       </c>
       <c r="D29" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="60"/>
         <v>8.8571428571428565E-2</v>
       </c>
       <c r="E29" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="60"/>
         <v>8.7178298168328311E-2</v>
       </c>
       <c r="F29" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="60"/>
         <v>8.5370907583920436E-2</v>
       </c>
       <c r="G29" s="9">
@@ -4717,142 +4834,146 @@
         <v>0.10140988618990997</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" ref="H29:R29" si="65">H9/H3</f>
+        <f t="shared" ref="H29:R29" si="61">H9/H3</f>
         <v>9.0381679389312977E-2</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>0.10008984725965858</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>0.10537595999285587</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>0.10928451335699607</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>0.10207128195558873</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>9.9310344827586203E-2</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>0.10440985732814527</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>0.11328339119312991</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>0.11139674378748929</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>0.10573397858923596</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>0.10342125881431183</v>
       </c>
       <c r="S29" s="9">
-        <f t="shared" ref="S29:V29" si="66">S9/S3</f>
+        <f t="shared" ref="S29:V29" si="62">S9/S3</f>
         <v>0.11911804248453886</v>
       </c>
       <c r="T29" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="62"/>
         <v>0.12895250487963567</v>
       </c>
       <c r="U29" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="62"/>
         <v>0.11561756435215229</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="66"/>
-        <v>0.11400768688191855</v>
-      </c>
-      <c r="Y29" s="9">
-        <f t="shared" ref="Y29" si="67">Y9/Y3</f>
+        <f t="shared" si="62"/>
+        <v>0.11665043816942551</v>
+      </c>
+      <c r="W29" s="9"/>
+      <c r="X29" s="9"/>
+      <c r="Y29" s="9"/>
+      <c r="Z29" s="9"/>
+      <c r="AC29" s="9">
+        <f t="shared" ref="AC29" si="63">AC9/AC3</f>
         <v>0.1114247511513891</v>
       </c>
-      <c r="Z29" s="9">
-        <f t="shared" ref="Z29:AO29" si="68">Z9/Z3</f>
+      <c r="AD29" s="9">
+        <f t="shared" ref="AD29:AS29" si="64">AD9/AD3</f>
         <v>0.10191539485813787</v>
       </c>
-      <c r="AA29" s="9">
-        <f t="shared" si="68"/>
+      <c r="AE29" s="9">
+        <f t="shared" si="64"/>
         <v>8.81100158208592E-2</v>
       </c>
-      <c r="AB29" s="9">
-        <f t="shared" si="68"/>
+      <c r="AF29" s="9">
+        <f t="shared" si="64"/>
         <v>9.8978856828100509E-2</v>
       </c>
-      <c r="AC29" s="9">
-        <f t="shared" si="68"/>
+      <c r="AG29" s="9">
+        <f t="shared" si="64"/>
         <v>0.1037037037037037</v>
       </c>
-      <c r="AD29" s="9">
-        <f t="shared" si="68"/>
+      <c r="AH29" s="9">
+        <f t="shared" si="64"/>
         <v>0.10793096761683149</v>
       </c>
-      <c r="AE29" s="9">
-        <f t="shared" si="68"/>
-        <v>0.11892771477996847</v>
-      </c>
-      <c r="AF29" s="9">
-        <f t="shared" si="68"/>
-        <v>0.11409325482956323</v>
-      </c>
-      <c r="AG29" s="9">
-        <f t="shared" si="68"/>
-        <v>0.1081405632732382</v>
-      </c>
-      <c r="AH29" s="9">
-        <f t="shared" si="68"/>
-        <v>0.10420817915421138</v>
-      </c>
       <c r="AI29" s="9">
-        <f t="shared" si="68"/>
-        <v>9.9427987449889746E-2</v>
+        <f t="shared" si="64"/>
+        <v>0.11963393862409423</v>
       </c>
       <c r="AJ29" s="9">
-        <f t="shared" si="68"/>
-        <v>9.6640286867182554E-2</v>
+        <f t="shared" si="64"/>
+        <v>0.11963393862409423</v>
       </c>
       <c r="AK29" s="9">
-        <f t="shared" si="68"/>
-        <v>9.5719903182733199E-2</v>
+        <f t="shared" si="64"/>
+        <v>0.11859364350562386</v>
       </c>
       <c r="AL29" s="9">
-        <f t="shared" si="68"/>
-        <v>9.4808285057183361E-2</v>
+        <f t="shared" si="64"/>
+        <v>0.11643739544188524</v>
       </c>
       <c r="AM29" s="9">
-        <f t="shared" si="68"/>
-        <v>9.3905349009019715E-2</v>
+        <f t="shared" si="64"/>
+        <v>0.11109623051335839</v>
       </c>
       <c r="AN29" s="9">
-        <f t="shared" si="68"/>
-        <v>9.3011012351790948E-2</v>
+        <f t="shared" si="64"/>
+        <v>0.1079813829288717</v>
       </c>
       <c r="AO29" s="9">
-        <f t="shared" si="68"/>
-        <v>9.2125193186535795E-2</v>
-      </c>
-      <c r="AQ29" t="s">
+        <f t="shared" si="64"/>
+        <v>0.10695298880573958</v>
+      </c>
+      <c r="AP29" s="9">
+        <f t="shared" si="64"/>
+        <v>0.10593438891235159</v>
+      </c>
+      <c r="AQ29" s="9">
+        <f t="shared" si="64"/>
+        <v>0.1049254899703292</v>
+      </c>
+      <c r="AR29" s="9">
+        <f t="shared" si="64"/>
+        <v>0.10392619958965939</v>
+      </c>
+      <c r="AS29" s="9">
+        <f t="shared" si="64"/>
+        <v>0.10293642626023405</v>
+      </c>
+      <c r="AU29" t="s">
         <v>58</v>
       </c>
-      <c r="AR29" s="5">
-        <f>AR27+AR28</f>
-        <v>306643.97708222189</v>
+      <c r="AV29" s="5">
+        <f>AV27+AV28</f>
+        <v>324726.68923996866</v>
       </c>
     </row>
-    <row r="30" spans="2:142" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>53</v>
       </c>
@@ -4861,145 +4982,149 @@
         <v>0</v>
       </c>
       <c r="D30" s="9">
-        <f t="shared" ref="D30:R30" si="69">D10/D3</f>
+        <f t="shared" ref="D30:R30" si="65">D10/D3</f>
         <v>0</v>
       </c>
       <c r="E30" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="F30" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="G30" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>4.9770681161882116E-2</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>9.4045801526717557E-2</v>
       </c>
       <c r="I30" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>0.10601976639712489</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>0.10734059653509555</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>9.6768167382776007E-2</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>8.9755551408844933E-2</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>7.7586206896551727E-2</v>
       </c>
       <c r="N30" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>6.8093385214007776E-2</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>7.1624337657591811E-2</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>6.3753213367609252E-2</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>5.1620472210001468E-2</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>4.3353355967615567E-2</v>
       </c>
       <c r="S30" s="9">
-        <f t="shared" ref="S30:V30" si="70">S10/S3</f>
+        <f t="shared" ref="S30:V30" si="66">S10/S3</f>
         <v>4.2484538854530789E-2</v>
       </c>
       <c r="T30" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="66"/>
         <v>4.0078074170461941E-2</v>
       </c>
       <c r="U30" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="66"/>
         <v>3.266277309106641E-2</v>
       </c>
       <c r="V30" s="9">
-        <f t="shared" si="70"/>
-        <v>3.3453770746663981E-2</v>
-      </c>
-      <c r="Y30" s="9">
-        <f t="shared" ref="Y30" si="71">Y10/Y3</f>
+        <f t="shared" si="66"/>
+        <v>2.8919182083739045E-2</v>
+      </c>
+      <c r="W30" s="9"/>
+      <c r="X30" s="9"/>
+      <c r="Y30" s="9"/>
+      <c r="Z30" s="9"/>
+      <c r="AC30" s="9">
+        <f t="shared" ref="AC30" si="67">AC10/AC3</f>
         <v>0</v>
       </c>
-      <c r="Z30" s="9">
-        <f t="shared" ref="Z30:AE30" si="72">Z10/Z3</f>
+      <c r="AD30" s="9">
+        <f t="shared" ref="AD30:AI30" si="68">AD10/AD3</f>
         <v>0</v>
       </c>
-      <c r="AA30" s="9">
-        <f t="shared" si="72"/>
+      <c r="AE30" s="9">
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
-      <c r="AB30" s="9">
-        <f t="shared" si="72"/>
+      <c r="AF30" s="9">
+        <f t="shared" si="68"/>
         <v>8.8979280538960218E-2</v>
       </c>
-      <c r="AC30" s="9">
-        <f t="shared" si="72"/>
+      <c r="AG30" s="9">
+        <f t="shared" si="68"/>
         <v>8.2407407407407401E-2</v>
       </c>
-      <c r="AD30" s="9">
-        <f t="shared" si="72"/>
+      <c r="AH30" s="9">
+        <f t="shared" si="68"/>
         <v>5.6156680240449876E-2</v>
       </c>
-      <c r="AE30" s="9">
-        <f t="shared" si="72"/>
-        <v>3.6702521743874263E-2</v>
-      </c>
-      <c r="AF30" s="9"/>
-      <c r="AG30" s="9"/>
-      <c r="AH30" s="9"/>
-      <c r="AI30" s="9"/>
+      <c r="AI30" s="9">
+        <f t="shared" si="68"/>
+        <v>3.5307023874823179E-2</v>
+      </c>
       <c r="AJ30" s="9"/>
       <c r="AK30" s="9"/>
       <c r="AL30" s="9"/>
       <c r="AM30" s="9"/>
       <c r="AN30" s="9"/>
       <c r="AO30" s="9"/>
-      <c r="AQ30" t="s">
+      <c r="AP30" s="9"/>
+      <c r="AQ30" s="9"/>
+      <c r="AR30" s="9"/>
+      <c r="AS30" s="9"/>
+      <c r="AU30" t="s">
         <v>59</v>
       </c>
-      <c r="AR30" s="4">
-        <f>AR29/AO21</f>
-        <v>188.58793178488432</v>
+      <c r="AV30" s="4">
+        <f>AV29/AS21</f>
+        <v>199.70891097169044</v>
       </c>
     </row>
-    <row r="31" spans="2:142" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>51</v>
       </c>
       <c r="C31" s="9">
-        <f t="shared" ref="C31:F31" si="73">C14/C3</f>
+        <f t="shared" ref="C31:F31" si="69">C14/C3</f>
         <v>0.19216255442670538</v>
       </c>
       <c r="D31" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="69"/>
         <v>0.21584415584415584</v>
       </c>
       <c r="E31" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="69"/>
         <v>0.21980060282865754</v>
       </c>
       <c r="F31" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="69"/>
         <v>0.25010360547036886</v>
       </c>
       <c r="G31" s="9">
@@ -5007,159 +5132,163 @@
         <v>0.16154238151860031</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" ref="H31:R31" si="74">H14/H3</f>
+        <f t="shared" ref="H31:R31" si="70">H14/H3</f>
         <v>8.0305343511450383E-2</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="70"/>
         <v>-1.1500449236298293E-2</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="70"/>
         <v>-2.661189498124665E-2</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="70"/>
         <v>-2.7087614421819541E-2</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="70"/>
         <v>-3.7320395596193321E-3</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="70"/>
         <v>3.8620689655172416E-2</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="70"/>
         <v>5.544747081712062E-2</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="70"/>
         <v>6.5777452950849628E-3</v>
       </c>
       <c r="P31" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="70"/>
         <v>4.6101113967437872E-2</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="70"/>
         <v>0.10617392579557119</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="70"/>
         <v>0.11373726821624446</v>
       </c>
       <c r="S31" s="9">
-        <f t="shared" ref="S31:V31" si="75">S14/S3</f>
+        <f t="shared" ref="S31:V31" si="71">S14/S3</f>
         <v>0.10836246302769562</v>
       </c>
       <c r="T31" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>-1.7436564736499675E-2</v>
       </c>
       <c r="U31" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>0.13735669478693488</v>
       </c>
       <c r="V31" s="9">
-        <f t="shared" si="75"/>
-        <v>0.17222118601719574</v>
-      </c>
-      <c r="Y31" s="9">
-        <f t="shared" ref="Y31" si="76">Y14/Y3</f>
+        <f t="shared" si="71"/>
+        <v>0.17059396299902629</v>
+      </c>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
+      <c r="Y31" s="9"/>
+      <c r="Z31" s="9"/>
+      <c r="AC31" s="9">
+        <f t="shared" ref="AC31" si="72">AC14/AC3</f>
         <v>9.3745357302035356E-2</v>
       </c>
-      <c r="Z31" s="9">
-        <f t="shared" ref="Z31:AO31" si="77">Z14/Z3</f>
+      <c r="AD31" s="9">
+        <f t="shared" ref="AD31:AS31" si="73">AD14/AD3</f>
         <v>0.14022329202089523</v>
       </c>
-      <c r="AA31" s="9">
-        <f t="shared" si="77"/>
+      <c r="AE31" s="9">
+        <f t="shared" si="73"/>
         <v>0.22197882438846295</v>
       </c>
-      <c r="AB31" s="9">
-        <f t="shared" si="77"/>
+      <c r="AF31" s="9">
+        <f t="shared" si="73"/>
         <v>5.3557052667259859E-2</v>
       </c>
-      <c r="AC31" s="9">
-        <f t="shared" si="77"/>
+      <c r="AG31" s="9">
+        <f t="shared" si="73"/>
         <v>1.7680776014109348E-2</v>
       </c>
-      <c r="AD31" s="9">
-        <f t="shared" si="77"/>
+      <c r="AH31" s="9">
+        <f t="shared" si="73"/>
         <v>7.3686251696722896E-2</v>
       </c>
-      <c r="AE31" s="9">
-        <f t="shared" si="77"/>
-        <v>0.1060859589155605</v>
-      </c>
-      <c r="AF31" s="9">
-        <f t="shared" si="77"/>
-        <v>0.22172978373424712</v>
-      </c>
-      <c r="AG31" s="9">
-        <f t="shared" si="77"/>
-        <v>0.26084107294320974</v>
-      </c>
-      <c r="AH31" s="9">
-        <f t="shared" si="77"/>
-        <v>0.28215594301800201</v>
-      </c>
       <c r="AI31" s="9">
-        <f t="shared" si="77"/>
-        <v>0.30591025755846074</v>
+        <f t="shared" si="73"/>
+        <v>0.10664280146655504</v>
       </c>
       <c r="AJ31" s="9">
-        <f t="shared" si="77"/>
-        <v>0.32567596767356599</v>
+        <f t="shared" si="73"/>
+        <v>0.21186593146453431</v>
       </c>
       <c r="AK31" s="9">
-        <f t="shared" si="77"/>
-        <v>0.33001889889057251</v>
+        <f t="shared" si="73"/>
+        <v>0.24632797362108802</v>
       </c>
       <c r="AL31" s="9">
-        <f t="shared" si="77"/>
-        <v>0.33428787316710706</v>
+        <f t="shared" si="73"/>
+        <v>0.2660143446984008</v>
       </c>
       <c r="AM31" s="9">
-        <f t="shared" si="77"/>
-        <v>0.3384842157252842</v>
+        <f t="shared" si="73"/>
+        <v>0.29050909952874931</v>
       </c>
       <c r="AN31" s="9">
-        <f t="shared" si="77"/>
-        <v>0.3426092273399548</v>
+        <f t="shared" si="73"/>
+        <v>0.31074150486867119</v>
       </c>
       <c r="AO31" s="9">
-        <f t="shared" si="77"/>
-        <v>0.34666418479679573</v>
-      </c>
-      <c r="AQ31" t="s">
+        <f t="shared" si="73"/>
+        <v>0.31526089160518356</v>
+      </c>
+      <c r="AP31" s="9">
+        <f t="shared" si="73"/>
+        <v>0.31970398901455394</v>
+      </c>
+      <c r="AQ31" s="9">
+        <f t="shared" si="73"/>
+        <v>0.32407215694844477</v>
+      </c>
+      <c r="AR31" s="9">
+        <f t="shared" si="73"/>
+        <v>0.32836673024494756</v>
+      </c>
+      <c r="AS31" s="9">
+        <f t="shared" si="73"/>
+        <v>0.33258901919657075</v>
+      </c>
+      <c r="AU31" t="s">
         <v>60</v>
       </c>
-      <c r="AR31" s="4">
+      <c r="AV31" s="4">
         <f>Main!D3</f>
-        <v>239.23</v>
+        <v>199.81</v>
       </c>
     </row>
-    <row r="32" spans="2:142" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:146" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>27</v>
       </c>
       <c r="C32" s="9">
-        <f t="shared" ref="C32:F32" si="78">C18/C17</f>
+        <f t="shared" ref="C32:F32" si="74">C18/C17</f>
         <v>0.13862928348909656</v>
       </c>
       <c r="D32" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>0.13763702801461633</v>
       </c>
       <c r="E32" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>8.175473579262213E-2</v>
       </c>
       <c r="F32" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>0.19035743973399832</v>
       </c>
       <c r="G32" s="9">
@@ -5167,159 +5296,163 @@
         <v>0.12611607142857142</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" ref="H32:R32" si="79">H18/H17</f>
+        <f t="shared" ref="H32:R32" si="75">H18/H17</f>
         <v>0.10865191146881288</v>
       </c>
       <c r="I32" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>1.8493150684931507</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>1.1323529411764706</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>-0.10236220472440945</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>11.5</v>
       </c>
       <c r="M32" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>-0.1517509727626459</v>
       </c>
       <c r="N32" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>-0.81593406593406592</v>
       </c>
       <c r="O32" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>-0.8125</v>
       </c>
       <c r="P32" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.13712374581939799</v>
       </c>
       <c r="Q32" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>-3.6635006784260515E-2</v>
       </c>
       <c r="R32" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.47131608548931386</v>
       </c>
       <c r="S32" s="9">
-        <f t="shared" ref="S32:V32" si="80">S18/S17</f>
+        <f t="shared" ref="S32:V32" si="76">S18/S17</f>
         <v>0.14909090909090908</v>
       </c>
       <c r="T32" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="76"/>
         <v>11.27027027027027</v>
       </c>
       <c r="U32" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="76"/>
         <v>0.11634980988593156</v>
       </c>
       <c r="V32" s="9">
-        <f t="shared" si="80"/>
-        <v>0.18</v>
-      </c>
-      <c r="Y32" s="9">
-        <f t="shared" ref="Y32" si="81">Y18/Y17</f>
+        <f t="shared" si="76"/>
+        <v>0.21938283510125361</v>
+      </c>
+      <c r="W32" s="9"/>
+      <c r="X32" s="9"/>
+      <c r="Y32" s="9"/>
+      <c r="Z32" s="9"/>
+      <c r="AC32" s="9">
+        <f t="shared" ref="AC32" si="77">AC18/AC17</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="Z32" s="9">
-        <f t="shared" ref="Z32:AO32" si="82">Z18/Z17</f>
+      <c r="AD32" s="9">
+        <f t="shared" ref="AD32:AS32" si="78">AD18/AD17</f>
         <v>-0.94901960784313721</v>
       </c>
-      <c r="AA32" s="9">
-        <f t="shared" si="82"/>
+      <c r="AE32" s="9">
+        <f t="shared" si="78"/>
         <v>0.13982011447260834</v>
       </c>
-      <c r="AB32" s="9">
-        <f t="shared" si="82"/>
+      <c r="AF32" s="9">
+        <f t="shared" si="78"/>
         <v>-0.10304054054054054</v>
       </c>
-      <c r="AC32" s="9">
-        <f t="shared" si="82"/>
+      <c r="AG32" s="9">
+        <f t="shared" si="78"/>
         <v>-0.7032520325203252</v>
       </c>
-      <c r="AD32" s="9">
-        <f t="shared" si="82"/>
+      <c r="AH32" s="9">
+        <f t="shared" si="78"/>
         <v>0.19155354449472098</v>
       </c>
-      <c r="AE32" s="9">
-        <f t="shared" si="82"/>
-        <v>-6.7048012963564649E-2</v>
-      </c>
-      <c r="AF32" s="9">
-        <f t="shared" si="82"/>
+      <c r="AI32" s="9">
+        <f t="shared" si="78"/>
+        <v>-2.4879227053140097E-2</v>
+      </c>
+      <c r="AJ32" s="9">
+        <f t="shared" si="78"/>
         <v>0.12000000000000001</v>
       </c>
-      <c r="AG32" s="9">
-        <f t="shared" si="82"/>
+      <c r="AK32" s="9">
+        <f t="shared" si="78"/>
+        <v>0.12000000000000001</v>
+      </c>
+      <c r="AL32" s="9">
+        <f t="shared" si="78"/>
+        <v>0.12</v>
+      </c>
+      <c r="AM32" s="9">
+        <f t="shared" si="78"/>
         <v>0.11999999999999998</v>
       </c>
-      <c r="AH32" s="9">
-        <f t="shared" si="82"/>
+      <c r="AN32" s="9">
+        <f t="shared" si="78"/>
         <v>0.12</v>
       </c>
-      <c r="AI32" s="9">
-        <f t="shared" si="82"/>
+      <c r="AO32" s="9">
+        <f t="shared" si="78"/>
         <v>0.12</v>
       </c>
-      <c r="AJ32" s="9">
-        <f t="shared" si="82"/>
-        <v>0.11999999999999998</v>
-      </c>
-      <c r="AK32" s="9">
-        <f t="shared" si="82"/>
-        <v>0.11999999999999998</v>
-      </c>
-      <c r="AL32" s="9">
-        <f t="shared" si="82"/>
+      <c r="AP32" s="9">
+        <f t="shared" si="78"/>
+        <v>0.12000000000000001</v>
+      </c>
+      <c r="AQ32" s="9">
+        <f t="shared" si="78"/>
         <v>0.12</v>
       </c>
-      <c r="AM32" s="9">
-        <f t="shared" si="82"/>
+      <c r="AR32" s="9">
+        <f t="shared" si="78"/>
         <v>0.12</v>
       </c>
-      <c r="AN32" s="9">
-        <f t="shared" si="82"/>
-        <v>0.12000000000000001</v>
-      </c>
-      <c r="AO32" s="9">
-        <f t="shared" si="82"/>
-        <v>0.12000000000000001</v>
-      </c>
-      <c r="AQ32" s="3" t="s">
+      <c r="AS32" s="9">
+        <f t="shared" si="78"/>
+        <v>0.12</v>
+      </c>
+      <c r="AU32" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AR32" s="10">
-        <f>AR30/AR31-1</f>
-        <v>-0.21168778253193865</v>
+      <c r="AV32" s="10">
+        <f>AV30/AV31-1</f>
+        <v>-5.0592577103025782E-4</v>
       </c>
     </row>
-    <row r="33" spans="2:44" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:48" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>52</v>
       </c>
       <c r="C33" s="9">
-        <f t="shared" ref="C33:F33" si="83">C20/C3</f>
+        <f t="shared" ref="C33:F33" si="79">C20/C3</f>
         <v>0.16110304789550073</v>
       </c>
       <c r="D33" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
         <v>0.18441558441558442</v>
       </c>
       <c r="E33" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
         <v>0.21400417342916764</v>
       </c>
       <c r="F33" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
         <v>0.20182345627849149</v>
       </c>
       <c r="G33" s="9">
@@ -5327,138 +5460,142 @@
         <v>0.13351452352641413</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" ref="H33:R33" si="84">H20/H3</f>
+        <f t="shared" ref="H33:R33" si="80">H20/H3</f>
         <v>6.8244274809160302E-2</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>1.1859838274932614E-2</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>3.7506697624575818E-3</v>
       </c>
       <c r="K33" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>-2.5966747618158044E-2</v>
       </c>
       <c r="L33" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>5.0382534054860982E-3</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>5.1551724137931035E-2</v>
       </c>
       <c r="N33" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>0.10813878080415046</v>
       </c>
       <c r="O33" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>2.2473963091540289E-2</v>
       </c>
       <c r="P33" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>4.5415595544130251E-2</v>
       </c>
       <c r="Q33" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>0.11306643202815662</v>
       </c>
       <c r="R33" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>6.2940715591538257E-2</v>
       </c>
       <c r="S33" s="9">
-        <f t="shared" ref="S33:V33" si="85">S20/S3</f>
+        <f t="shared" ref="S33:V33" si="81">S20/S3</f>
         <v>9.5321322936273198E-2</v>
       </c>
       <c r="T33" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="81"/>
         <v>9.9934938191281714E-2</v>
       </c>
       <c r="U33" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="81"/>
         <v>0.12675751676400607</v>
       </c>
       <c r="V33" s="9">
-        <f t="shared" si="85"/>
-        <v>0.14490643318808183</v>
-      </c>
-      <c r="Y33" s="9">
-        <f t="shared" ref="Y33" si="86">Y20/Y3</f>
+        <f t="shared" si="81"/>
+        <v>0.15774099318403115</v>
+      </c>
+      <c r="W33" s="9"/>
+      <c r="X33" s="9"/>
+      <c r="Y33" s="9"/>
+      <c r="Z33" s="9"/>
+      <c r="AC33" s="9">
+        <f t="shared" ref="AC33" si="82">AC20/AC3</f>
         <v>5.0661120190164909E-2</v>
       </c>
-      <c r="Z33" s="9">
-        <f t="shared" ref="Z33:AO33" si="87">Z20/Z3</f>
+      <c r="AD33" s="9">
+        <f t="shared" ref="AD33:AS33" si="83">AD20/AD3</f>
         <v>0.25504455597664655</v>
       </c>
-      <c r="AA33" s="9">
-        <f t="shared" si="87"/>
+      <c r="AE33" s="9">
+        <f t="shared" si="83"/>
         <v>0.19240598758671049</v>
       </c>
-      <c r="AB33" s="9">
-        <f t="shared" si="87"/>
+      <c r="AF33" s="9">
+        <f t="shared" si="83"/>
         <v>5.5929833481632135E-2</v>
       </c>
-      <c r="AC33" s="9">
-        <f t="shared" si="87"/>
+      <c r="AG33" s="9">
+        <f t="shared" si="83"/>
         <v>3.7654320987654324E-2</v>
       </c>
-      <c r="AD33" s="9">
-        <f t="shared" si="87"/>
+      <c r="AH33" s="9">
+        <f t="shared" si="83"/>
         <v>6.3641652123327522E-2</v>
       </c>
-      <c r="AE33" s="9">
-        <f t="shared" si="87"/>
-        <v>0.11903068401327374</v>
-      </c>
-      <c r="AF33" s="9">
-        <f t="shared" si="87"/>
-        <v>0.20046559609070039</v>
-      </c>
-      <c r="AG33" s="9">
-        <f t="shared" si="87"/>
-        <v>0.23487205266328004</v>
-      </c>
-      <c r="AH33" s="9">
-        <f t="shared" si="87"/>
-        <v>0.2535990335872117</v>
-      </c>
       <c r="AI33" s="9">
-        <f t="shared" si="87"/>
-        <v>0.27453922693250982</v>
+        <f t="shared" si="83"/>
+        <v>0.12324258783452179</v>
       </c>
       <c r="AJ33" s="9">
-        <f t="shared" si="87"/>
-        <v>0.29198469175234887</v>
+        <f t="shared" si="83"/>
+        <v>0.19779289702358621</v>
       </c>
       <c r="AK33" s="9">
-        <f t="shared" si="87"/>
-        <v>0.29575094350842762</v>
+        <f t="shared" si="83"/>
+        <v>0.22731630938236236</v>
       </c>
       <c r="AL33" s="9">
-        <f t="shared" si="87"/>
-        <v>0.29945564900232663</v>
+        <f t="shared" si="83"/>
+        <v>0.24415358165617199</v>
       </c>
       <c r="AM33" s="9">
-        <f t="shared" si="87"/>
-        <v>0.3030998103624003</v>
+        <f t="shared" si="83"/>
+        <v>0.26539001057976747</v>
       </c>
       <c r="AN33" s="9">
-        <f t="shared" si="87"/>
-        <v>0.30668441512671463</v>
+        <f t="shared" si="83"/>
+        <v>0.28299371768926834</v>
       </c>
       <c r="AO33" s="9">
-        <f t="shared" si="87"/>
-        <v>0.31021043636589507</v>
-      </c>
-      <c r="AQ33" t="s">
+        <f t="shared" si="83"/>
+        <v>0.28675168460635214</v>
+      </c>
+      <c r="AP33" s="9">
+        <f t="shared" si="83"/>
+        <v>0.29045237042222155</v>
+      </c>
+      <c r="AQ33" s="9">
+        <f t="shared" si="83"/>
+        <v>0.29409656530448275</v>
+      </c>
+      <c r="AR33" s="9">
+        <f t="shared" si="83"/>
+        <v>0.29768505361008984</v>
+      </c>
+      <c r="AS33" s="9">
+        <f t="shared" si="83"/>
+        <v>0.30121861366234531</v>
+      </c>
+      <c r="AU33" t="s">
         <v>62</v>
       </c>
-      <c r="AR33" s="6" t="s">
-        <v>68</v>
+      <c r="AV33" s="6" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
